--- a/l_r/2nd.xlsx
+++ b/l_r/2nd.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PycharmProjects\english\english-study\l_r\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BB0D9314-D972-4289-A721-6B7CEE5E2983}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3DDF0001-4C06-4C55-AA26-1858FD159527}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="480" yWindow="120" windowWidth="15840" windowHeight="15345" firstSheet="1" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="209" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="219" uniqueCount="28">
   <si>
     <t>問題番号</t>
     <rPh sb="0" eb="2">
@@ -152,6 +152,18 @@
   </si>
   <si>
     <t>D</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>C</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>D</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>A</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -3284,14 +3296,14 @@
       </c>
       <c r="C9">
         <f>SUM(reading!C3:C42)</f>
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="D9">
         <v>40</v>
       </c>
       <c r="E9" s="1">
         <f t="shared" ref="E9:E11" si="1">C9/D9</f>
-        <v>0.15</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="10" spans="2:5">
@@ -3975,7 +3987,7 @@
     <row r="1" spans="1:3">
       <c r="C1">
         <f>SUM(C3:C102)</f>
-        <v>6</v>
+        <v>12</v>
       </c>
     </row>
     <row r="2" spans="1:3">
@@ -4113,30 +4125,60 @@
         <f t="shared" si="0"/>
         <v>111</v>
       </c>
+      <c r="B13" t="s">
+        <v>25</v>
+      </c>
+      <c r="C13">
+        <v>1</v>
+      </c>
     </row>
     <row r="14" spans="1:3">
       <c r="A14">
         <f t="shared" si="0"/>
         <v>112</v>
       </c>
+      <c r="B14" t="s">
+        <v>25</v>
+      </c>
+      <c r="C14">
+        <v>1</v>
+      </c>
     </row>
     <row r="15" spans="1:3">
       <c r="A15">
         <f t="shared" si="0"/>
         <v>113</v>
       </c>
+      <c r="B15" t="s">
+        <v>26</v>
+      </c>
+      <c r="C15">
+        <v>0</v>
+      </c>
     </row>
     <row r="16" spans="1:3">
       <c r="A16">
         <f t="shared" si="0"/>
         <v>114</v>
       </c>
+      <c r="B16" t="s">
+        <v>27</v>
+      </c>
+      <c r="C16">
+        <v>0</v>
+      </c>
     </row>
     <row r="17" spans="1:6">
       <c r="A17">
         <f t="shared" si="0"/>
         <v>115</v>
       </c>
+      <c r="B17" t="s">
+        <v>26</v>
+      </c>
+      <c r="C17">
+        <v>1</v>
+      </c>
       <c r="F17" t="s">
         <v>12</v>
       </c>
@@ -4146,6 +4188,12 @@
         <f t="shared" si="0"/>
         <v>116</v>
       </c>
+      <c r="B18" t="s">
+        <v>27</v>
+      </c>
+      <c r="C18">
+        <v>1</v>
+      </c>
       <c r="F18" t="s">
         <v>13</v>
       </c>
@@ -4155,23 +4203,47 @@
         <f t="shared" si="0"/>
         <v>117</v>
       </c>
+      <c r="B19" t="s">
+        <v>25</v>
+      </c>
+      <c r="C19">
+        <v>0</v>
+      </c>
     </row>
     <row r="20" spans="1:6">
       <c r="A20">
         <f t="shared" si="0"/>
         <v>118</v>
       </c>
+      <c r="B20" t="s">
+        <v>25</v>
+      </c>
+      <c r="C20">
+        <v>1</v>
+      </c>
     </row>
     <row r="21" spans="1:6">
       <c r="A21">
         <f t="shared" si="0"/>
         <v>119</v>
       </c>
+      <c r="B21" t="s">
+        <v>26</v>
+      </c>
+      <c r="C21">
+        <v>1</v>
+      </c>
     </row>
     <row r="22" spans="1:6">
       <c r="A22">
         <f t="shared" si="0"/>
         <v>120</v>
+      </c>
+      <c r="B22" t="s">
+        <v>26</v>
+      </c>
+      <c r="C22">
+        <v>0</v>
       </c>
     </row>
     <row r="23" spans="1:6">

--- a/l_r/2nd.xlsx
+++ b/l_r/2nd.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PycharmProjects\english\english-study\l_r\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3DDF0001-4C06-4C55-AA26-1858FD159527}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E9E25317-A0F7-4C69-93E6-D8121A0BDF7C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="480" yWindow="120" windowWidth="15840" windowHeight="15345" firstSheet="1" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="219" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="229" uniqueCount="32">
   <si>
     <t>問題番号</t>
     <rPh sb="0" eb="2">
@@ -164,6 +164,22 @@
   </si>
   <si>
     <t>A</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>C</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>B</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>A</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>D</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -3296,14 +3312,14 @@
       </c>
       <c r="C9">
         <f>SUM(reading!C3:C42)</f>
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="D9">
         <v>40</v>
       </c>
       <c r="E9" s="1">
         <f t="shared" ref="E9:E11" si="1">C9/D9</f>
-        <v>0.3</v>
+        <v>0.47499999999999998</v>
       </c>
     </row>
     <row r="10" spans="2:5">
@@ -3987,7 +4003,7 @@
     <row r="1" spans="1:3">
       <c r="C1">
         <f>SUM(C3:C102)</f>
-        <v>12</v>
+        <v>19</v>
       </c>
     </row>
     <row r="2" spans="1:3">
@@ -4251,24 +4267,48 @@
         <f t="shared" si="0"/>
         <v>121</v>
       </c>
+      <c r="B23" t="s">
+        <v>28</v>
+      </c>
+      <c r="C23">
+        <v>1</v>
+      </c>
     </row>
     <row r="24" spans="1:6">
       <c r="A24">
         <f t="shared" si="0"/>
         <v>122</v>
       </c>
+      <c r="B24" t="s">
+        <v>29</v>
+      </c>
+      <c r="C24">
+        <v>1</v>
+      </c>
     </row>
     <row r="25" spans="1:6">
       <c r="A25">
         <f t="shared" si="0"/>
         <v>123</v>
       </c>
+      <c r="B25" t="s">
+        <v>29</v>
+      </c>
+      <c r="C25">
+        <v>1</v>
+      </c>
     </row>
     <row r="26" spans="1:6">
       <c r="A26">
         <f t="shared" si="0"/>
         <v>124</v>
       </c>
+      <c r="B26" t="s">
+        <v>30</v>
+      </c>
+      <c r="C26">
+        <v>1</v>
+      </c>
       <c r="F26" t="s">
         <v>14</v>
       </c>
@@ -4278,6 +4318,12 @@
         <f t="shared" si="0"/>
         <v>125</v>
       </c>
+      <c r="B27" t="s">
+        <v>30</v>
+      </c>
+      <c r="C27">
+        <v>1</v>
+      </c>
       <c r="F27" t="s">
         <v>14</v>
       </c>
@@ -4287,6 +4333,12 @@
         <f t="shared" si="0"/>
         <v>126</v>
       </c>
+      <c r="B28" t="s">
+        <v>31</v>
+      </c>
+      <c r="C28">
+        <v>1</v>
+      </c>
       <c r="F28" t="s">
         <v>14</v>
       </c>
@@ -4296,23 +4348,47 @@
         <f t="shared" si="0"/>
         <v>127</v>
       </c>
+      <c r="B29" t="s">
+        <v>30</v>
+      </c>
+      <c r="C29">
+        <v>0</v>
+      </c>
     </row>
     <row r="30" spans="1:6">
       <c r="A30">
         <f t="shared" si="0"/>
         <v>128</v>
       </c>
+      <c r="B30" t="s">
+        <v>29</v>
+      </c>
+      <c r="C30">
+        <v>1</v>
+      </c>
     </row>
     <row r="31" spans="1:6">
       <c r="A31">
         <f t="shared" si="0"/>
         <v>129</v>
       </c>
+      <c r="B31" t="s">
+        <v>30</v>
+      </c>
+      <c r="C31">
+        <v>0</v>
+      </c>
     </row>
     <row r="32" spans="1:6">
       <c r="A32">
         <f t="shared" si="0"/>
         <v>130</v>
+      </c>
+      <c r="B32" t="s">
+        <v>29</v>
+      </c>
+      <c r="C32">
+        <v>0</v>
       </c>
     </row>
     <row r="33" spans="1:1">

--- a/l_r/2nd.xlsx
+++ b/l_r/2nd.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PycharmProjects\english\english-study\l_r\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E9E25317-A0F7-4C69-93E6-D8121A0BDF7C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FDF4CD81-25FE-4CFE-A199-CC1240F49C84}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="480" yWindow="120" windowWidth="15840" windowHeight="15345" firstSheet="1" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="480" yWindow="120" windowWidth="15840" windowHeight="15345" firstSheet="1" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="summary" sheetId="3" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="229" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="240" uniqueCount="32">
   <si>
     <t>問題番号</t>
     <rPh sb="0" eb="2">
@@ -3997,6 +3997,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{86A9B22D-A93D-442A-B8E1-1D68266591E9}">
+  <sheetPr filterMode="1"/>
   <dimension ref="A1:F102"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <sheetData>
@@ -4017,7 +4018,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="1:3">
+    <row r="3" spans="1:3" hidden="1">
       <c r="A3">
         <v>101</v>
       </c>
@@ -4028,7 +4029,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:3">
+    <row r="4" spans="1:3" hidden="1">
       <c r="A4">
         <f>A3+1</f>
         <v>102</v>
@@ -4052,7 +4053,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:3">
+    <row r="6" spans="1:3" hidden="1">
       <c r="A6">
         <f t="shared" si="0"/>
         <v>104</v>
@@ -4076,7 +4077,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:3">
+    <row r="8" spans="1:3" hidden="1">
       <c r="A8">
         <f t="shared" si="0"/>
         <v>106</v>
@@ -4112,7 +4113,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:3">
+    <row r="11" spans="1:3" hidden="1">
       <c r="A11">
         <f t="shared" si="0"/>
         <v>109</v>
@@ -4124,7 +4125,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:3">
+    <row r="12" spans="1:3" hidden="1">
       <c r="A12">
         <f t="shared" si="0"/>
         <v>110</v>
@@ -4136,7 +4137,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:3">
+    <row r="13" spans="1:3" hidden="1">
       <c r="A13">
         <f t="shared" si="0"/>
         <v>111</v>
@@ -4148,7 +4149,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:3">
+    <row r="14" spans="1:3" hidden="1">
       <c r="A14">
         <f t="shared" si="0"/>
         <v>112</v>
@@ -4184,7 +4185,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:6">
+    <row r="17" spans="1:6" hidden="1">
       <c r="A17">
         <f t="shared" si="0"/>
         <v>115</v>
@@ -4199,7 +4200,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="18" spans="1:6">
+    <row r="18" spans="1:6" hidden="1">
       <c r="A18">
         <f t="shared" si="0"/>
         <v>116</v>
@@ -4226,7 +4227,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:6">
+    <row r="20" spans="1:6" hidden="1">
       <c r="A20">
         <f t="shared" si="0"/>
         <v>118</v>
@@ -4238,7 +4239,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="21" spans="1:6">
+    <row r="21" spans="1:6" hidden="1">
       <c r="A21">
         <f t="shared" si="0"/>
         <v>119</v>
@@ -4262,7 +4263,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:6">
+    <row r="23" spans="1:6" hidden="1">
       <c r="A23">
         <f t="shared" si="0"/>
         <v>121</v>
@@ -4274,7 +4275,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="24" spans="1:6">
+    <row r="24" spans="1:6" hidden="1">
       <c r="A24">
         <f t="shared" si="0"/>
         <v>122</v>
@@ -4286,7 +4287,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="25" spans="1:6">
+    <row r="25" spans="1:6" hidden="1">
       <c r="A25">
         <f t="shared" si="0"/>
         <v>123</v>
@@ -4298,7 +4299,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="26" spans="1:6">
+    <row r="26" spans="1:6" hidden="1">
       <c r="A26">
         <f t="shared" si="0"/>
         <v>124</v>
@@ -4313,7 +4314,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="27" spans="1:6">
+    <row r="27" spans="1:6" hidden="1">
       <c r="A27">
         <f t="shared" si="0"/>
         <v>125</v>
@@ -4328,7 +4329,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="28" spans="1:6">
+    <row r="28" spans="1:6" hidden="1">
       <c r="A28">
         <f t="shared" si="0"/>
         <v>126</v>
@@ -4355,7 +4356,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:6">
+    <row r="30" spans="1:6" hidden="1">
       <c r="A30">
         <f t="shared" si="0"/>
         <v>128</v>
@@ -4391,428 +4392,434 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:1">
+    <row r="33" spans="1:1" hidden="1">
       <c r="A33">
         <f t="shared" si="0"/>
         <v>131</v>
       </c>
     </row>
-    <row r="34" spans="1:1">
+    <row r="34" spans="1:1" hidden="1">
       <c r="A34">
         <f t="shared" si="0"/>
         <v>132</v>
       </c>
     </row>
-    <row r="35" spans="1:1">
+    <row r="35" spans="1:1" hidden="1">
       <c r="A35">
         <f t="shared" si="0"/>
         <v>133</v>
       </c>
     </row>
-    <row r="36" spans="1:1">
+    <row r="36" spans="1:1" hidden="1">
       <c r="A36">
         <f t="shared" si="0"/>
         <v>134</v>
       </c>
     </row>
-    <row r="37" spans="1:1">
+    <row r="37" spans="1:1" hidden="1">
       <c r="A37">
         <f t="shared" si="0"/>
         <v>135</v>
       </c>
     </row>
-    <row r="38" spans="1:1">
+    <row r="38" spans="1:1" hidden="1">
       <c r="A38">
         <f t="shared" si="0"/>
         <v>136</v>
       </c>
     </row>
-    <row r="39" spans="1:1">
+    <row r="39" spans="1:1" hidden="1">
       <c r="A39">
         <f t="shared" si="0"/>
         <v>137</v>
       </c>
     </row>
-    <row r="40" spans="1:1">
+    <row r="40" spans="1:1" hidden="1">
       <c r="A40">
         <f t="shared" si="0"/>
         <v>138</v>
       </c>
     </row>
-    <row r="41" spans="1:1">
+    <row r="41" spans="1:1" hidden="1">
       <c r="A41">
         <f t="shared" si="0"/>
         <v>139</v>
       </c>
     </row>
-    <row r="42" spans="1:1">
+    <row r="42" spans="1:1" hidden="1">
       <c r="A42">
         <f t="shared" si="0"/>
         <v>140</v>
       </c>
     </row>
-    <row r="43" spans="1:1">
+    <row r="43" spans="1:1" hidden="1">
       <c r="A43">
         <f t="shared" si="0"/>
         <v>141</v>
       </c>
     </row>
-    <row r="44" spans="1:1">
+    <row r="44" spans="1:1" hidden="1">
       <c r="A44">
         <f t="shared" si="0"/>
         <v>142</v>
       </c>
     </row>
-    <row r="45" spans="1:1">
+    <row r="45" spans="1:1" hidden="1">
       <c r="A45">
         <f t="shared" si="0"/>
         <v>143</v>
       </c>
     </row>
-    <row r="46" spans="1:1">
+    <row r="46" spans="1:1" hidden="1">
       <c r="A46">
         <f t="shared" si="0"/>
         <v>144</v>
       </c>
     </row>
-    <row r="47" spans="1:1">
+    <row r="47" spans="1:1" hidden="1">
       <c r="A47">
         <f t="shared" si="0"/>
         <v>145</v>
       </c>
     </row>
-    <row r="48" spans="1:1">
+    <row r="48" spans="1:1" hidden="1">
       <c r="A48">
         <f t="shared" si="0"/>
         <v>146</v>
       </c>
     </row>
-    <row r="49" spans="1:1">
+    <row r="49" spans="1:1" hidden="1">
       <c r="A49">
         <f t="shared" si="0"/>
         <v>147</v>
       </c>
     </row>
-    <row r="50" spans="1:1">
+    <row r="50" spans="1:1" hidden="1">
       <c r="A50">
         <f t="shared" si="0"/>
         <v>148</v>
       </c>
     </row>
-    <row r="51" spans="1:1">
+    <row r="51" spans="1:1" hidden="1">
       <c r="A51">
         <f t="shared" si="0"/>
         <v>149</v>
       </c>
     </row>
-    <row r="52" spans="1:1">
+    <row r="52" spans="1:1" hidden="1">
       <c r="A52">
         <f t="shared" si="0"/>
         <v>150</v>
       </c>
     </row>
-    <row r="53" spans="1:1">
+    <row r="53" spans="1:1" hidden="1">
       <c r="A53">
         <f t="shared" si="0"/>
         <v>151</v>
       </c>
     </row>
-    <row r="54" spans="1:1">
+    <row r="54" spans="1:1" hidden="1">
       <c r="A54">
         <f t="shared" si="0"/>
         <v>152</v>
       </c>
     </row>
-    <row r="55" spans="1:1">
+    <row r="55" spans="1:1" hidden="1">
       <c r="A55">
         <f t="shared" si="0"/>
         <v>153</v>
       </c>
     </row>
-    <row r="56" spans="1:1">
+    <row r="56" spans="1:1" hidden="1">
       <c r="A56">
         <f t="shared" si="0"/>
         <v>154</v>
       </c>
     </row>
-    <row r="57" spans="1:1">
+    <row r="57" spans="1:1" hidden="1">
       <c r="A57">
         <f t="shared" si="0"/>
         <v>155</v>
       </c>
     </row>
-    <row r="58" spans="1:1">
+    <row r="58" spans="1:1" hidden="1">
       <c r="A58">
         <f t="shared" si="0"/>
         <v>156</v>
       </c>
     </row>
-    <row r="59" spans="1:1">
+    <row r="59" spans="1:1" hidden="1">
       <c r="A59">
         <f t="shared" si="0"/>
         <v>157</v>
       </c>
     </row>
-    <row r="60" spans="1:1">
+    <row r="60" spans="1:1" hidden="1">
       <c r="A60">
         <f t="shared" si="0"/>
         <v>158</v>
       </c>
     </row>
-    <row r="61" spans="1:1">
+    <row r="61" spans="1:1" hidden="1">
       <c r="A61">
         <f t="shared" si="0"/>
         <v>159</v>
       </c>
     </row>
-    <row r="62" spans="1:1">
+    <row r="62" spans="1:1" hidden="1">
       <c r="A62">
         <f t="shared" si="0"/>
         <v>160</v>
       </c>
     </row>
-    <row r="63" spans="1:1">
+    <row r="63" spans="1:1" hidden="1">
       <c r="A63">
         <f t="shared" si="0"/>
         <v>161</v>
       </c>
     </row>
-    <row r="64" spans="1:1">
+    <row r="64" spans="1:1" hidden="1">
       <c r="A64">
         <f t="shared" si="0"/>
         <v>162</v>
       </c>
     </row>
-    <row r="65" spans="1:1">
+    <row r="65" spans="1:1" hidden="1">
       <c r="A65">
         <f t="shared" si="0"/>
         <v>163</v>
       </c>
     </row>
-    <row r="66" spans="1:1">
+    <row r="66" spans="1:1" hidden="1">
       <c r="A66">
         <f t="shared" si="0"/>
         <v>164</v>
       </c>
     </row>
-    <row r="67" spans="1:1">
+    <row r="67" spans="1:1" hidden="1">
       <c r="A67">
         <f t="shared" si="0"/>
         <v>165</v>
       </c>
     </row>
-    <row r="68" spans="1:1">
+    <row r="68" spans="1:1" hidden="1">
       <c r="A68">
         <f t="shared" si="0"/>
         <v>166</v>
       </c>
     </row>
-    <row r="69" spans="1:1">
+    <row r="69" spans="1:1" hidden="1">
       <c r="A69">
         <f t="shared" ref="A69:A102" si="1">A68+1</f>
         <v>167</v>
       </c>
     </row>
-    <row r="70" spans="1:1">
+    <row r="70" spans="1:1" hidden="1">
       <c r="A70">
         <f t="shared" si="1"/>
         <v>168</v>
       </c>
     </row>
-    <row r="71" spans="1:1">
+    <row r="71" spans="1:1" hidden="1">
       <c r="A71">
         <f t="shared" si="1"/>
         <v>169</v>
       </c>
     </row>
-    <row r="72" spans="1:1">
+    <row r="72" spans="1:1" hidden="1">
       <c r="A72">
         <f t="shared" si="1"/>
         <v>170</v>
       </c>
     </row>
-    <row r="73" spans="1:1">
+    <row r="73" spans="1:1" hidden="1">
       <c r="A73">
         <f t="shared" si="1"/>
         <v>171</v>
       </c>
     </row>
-    <row r="74" spans="1:1">
+    <row r="74" spans="1:1" hidden="1">
       <c r="A74">
         <f t="shared" si="1"/>
         <v>172</v>
       </c>
     </row>
-    <row r="75" spans="1:1">
+    <row r="75" spans="1:1" hidden="1">
       <c r="A75">
         <f t="shared" si="1"/>
         <v>173</v>
       </c>
     </row>
-    <row r="76" spans="1:1">
+    <row r="76" spans="1:1" hidden="1">
       <c r="A76">
         <f t="shared" si="1"/>
         <v>174</v>
       </c>
     </row>
-    <row r="77" spans="1:1">
+    <row r="77" spans="1:1" hidden="1">
       <c r="A77">
         <f t="shared" si="1"/>
         <v>175</v>
       </c>
     </row>
-    <row r="78" spans="1:1">
+    <row r="78" spans="1:1" hidden="1">
       <c r="A78">
         <f t="shared" si="1"/>
         <v>176</v>
       </c>
     </row>
-    <row r="79" spans="1:1">
+    <row r="79" spans="1:1" hidden="1">
       <c r="A79">
         <f t="shared" si="1"/>
         <v>177</v>
       </c>
     </row>
-    <row r="80" spans="1:1">
+    <row r="80" spans="1:1" hidden="1">
       <c r="A80">
         <f t="shared" si="1"/>
         <v>178</v>
       </c>
     </row>
-    <row r="81" spans="1:1">
+    <row r="81" spans="1:1" hidden="1">
       <c r="A81">
         <f t="shared" si="1"/>
         <v>179</v>
       </c>
     </row>
-    <row r="82" spans="1:1">
+    <row r="82" spans="1:1" hidden="1">
       <c r="A82">
         <f t="shared" si="1"/>
         <v>180</v>
       </c>
     </row>
-    <row r="83" spans="1:1">
+    <row r="83" spans="1:1" hidden="1">
       <c r="A83">
         <f t="shared" si="1"/>
         <v>181</v>
       </c>
     </row>
-    <row r="84" spans="1:1">
+    <row r="84" spans="1:1" hidden="1">
       <c r="A84">
         <f t="shared" si="1"/>
         <v>182</v>
       </c>
     </row>
-    <row r="85" spans="1:1">
+    <row r="85" spans="1:1" hidden="1">
       <c r="A85">
         <f t="shared" si="1"/>
         <v>183</v>
       </c>
     </row>
-    <row r="86" spans="1:1">
+    <row r="86" spans="1:1" hidden="1">
       <c r="A86">
         <f t="shared" si="1"/>
         <v>184</v>
       </c>
     </row>
-    <row r="87" spans="1:1">
+    <row r="87" spans="1:1" hidden="1">
       <c r="A87">
         <f t="shared" si="1"/>
         <v>185</v>
       </c>
     </row>
-    <row r="88" spans="1:1">
+    <row r="88" spans="1:1" hidden="1">
       <c r="A88">
         <f t="shared" si="1"/>
         <v>186</v>
       </c>
     </row>
-    <row r="89" spans="1:1">
+    <row r="89" spans="1:1" hidden="1">
       <c r="A89">
         <f t="shared" si="1"/>
         <v>187</v>
       </c>
     </row>
-    <row r="90" spans="1:1">
+    <row r="90" spans="1:1" hidden="1">
       <c r="A90">
         <f t="shared" si="1"/>
         <v>188</v>
       </c>
     </row>
-    <row r="91" spans="1:1">
+    <row r="91" spans="1:1" hidden="1">
       <c r="A91">
         <f t="shared" si="1"/>
         <v>189</v>
       </c>
     </row>
-    <row r="92" spans="1:1">
+    <row r="92" spans="1:1" hidden="1">
       <c r="A92">
         <f t="shared" si="1"/>
         <v>190</v>
       </c>
     </row>
-    <row r="93" spans="1:1">
+    <row r="93" spans="1:1" hidden="1">
       <c r="A93">
         <f t="shared" si="1"/>
         <v>191</v>
       </c>
     </row>
-    <row r="94" spans="1:1">
+    <row r="94" spans="1:1" hidden="1">
       <c r="A94">
         <f t="shared" si="1"/>
         <v>192</v>
       </c>
     </row>
-    <row r="95" spans="1:1">
+    <row r="95" spans="1:1" hidden="1">
       <c r="A95">
         <f t="shared" si="1"/>
         <v>193</v>
       </c>
     </row>
-    <row r="96" spans="1:1">
+    <row r="96" spans="1:1" hidden="1">
       <c r="A96">
         <f t="shared" si="1"/>
         <v>194</v>
       </c>
     </row>
-    <row r="97" spans="1:1">
+    <row r="97" spans="1:1" hidden="1">
       <c r="A97">
         <f t="shared" si="1"/>
         <v>195</v>
       </c>
     </row>
-    <row r="98" spans="1:1">
+    <row r="98" spans="1:1" hidden="1">
       <c r="A98">
         <f t="shared" si="1"/>
         <v>196</v>
       </c>
     </row>
-    <row r="99" spans="1:1">
+    <row r="99" spans="1:1" hidden="1">
       <c r="A99">
         <f t="shared" si="1"/>
         <v>197</v>
       </c>
     </row>
-    <row r="100" spans="1:1">
+    <row r="100" spans="1:1" hidden="1">
       <c r="A100">
         <f t="shared" si="1"/>
         <v>198</v>
       </c>
     </row>
-    <row r="101" spans="1:1">
+    <row r="101" spans="1:1" hidden="1">
       <c r="A101">
         <f t="shared" si="1"/>
         <v>199</v>
       </c>
     </row>
-    <row r="102" spans="1:1">
+    <row r="102" spans="1:1" hidden="1">
       <c r="A102">
         <f t="shared" si="1"/>
         <v>200</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A2:C102" xr:uid="{86A9B22D-A93D-442A-B8E1-1D68266591E9}"/>
+  <autoFilter ref="A2:C102" xr:uid="{86A9B22D-A93D-442A-B8E1-1D68266591E9}">
+    <filterColumn colId="2">
+      <filters>
+        <filter val="0"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <phoneticPr fontId="1"/>
   <dataValidations count="1">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B3:B102" xr:uid="{507A3D4C-54A2-49AD-8DD6-62E0792701B4}">
@@ -4825,7 +4832,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3C7A3EDD-6597-4754-A609-A225833ECC81}">
-  <dimension ref="A2:H172"/>
+  <dimension ref="A2:H183"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <sheetData>
     <row r="2" spans="1:4">
@@ -6828,6 +6835,127 @@
         <v>11</v>
       </c>
       <c r="C172">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="173" spans="1:3">
+      <c r="A173">
+        <v>103</v>
+      </c>
+      <c r="B173" t="s">
+        <v>11</v>
+      </c>
+      <c r="C173">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="174" spans="1:3">
+      <c r="A174">
+        <v>105</v>
+      </c>
+      <c r="B174" t="s">
+        <v>10</v>
+      </c>
+      <c r="C174">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="175" spans="1:3">
+      <c r="A175">
+        <v>107</v>
+      </c>
+      <c r="B175" t="s">
+        <v>11</v>
+      </c>
+      <c r="C175">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="176" spans="1:3">
+      <c r="A176">
+        <v>108</v>
+      </c>
+      <c r="B176" t="s">
+        <v>8</v>
+      </c>
+      <c r="C176">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="177" spans="1:3">
+      <c r="A177">
+        <v>113</v>
+      </c>
+      <c r="B177" t="s">
+        <v>8</v>
+      </c>
+      <c r="C177">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="178" spans="1:3">
+      <c r="A178">
+        <v>114</v>
+      </c>
+      <c r="B178" t="s">
+        <v>9</v>
+      </c>
+      <c r="C178">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="179" spans="1:3">
+      <c r="A179">
+        <v>117</v>
+      </c>
+      <c r="B179" t="s">
+        <v>10</v>
+      </c>
+      <c r="C179">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="180" spans="1:3">
+      <c r="A180">
+        <v>120</v>
+      </c>
+      <c r="B180" t="s">
+        <v>11</v>
+      </c>
+      <c r="C180">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="181" spans="1:3">
+      <c r="A181">
+        <v>127</v>
+      </c>
+      <c r="B181" t="s">
+        <v>10</v>
+      </c>
+      <c r="C181">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="182" spans="1:3">
+      <c r="A182">
+        <v>129</v>
+      </c>
+      <c r="B182" t="s">
+        <v>11</v>
+      </c>
+      <c r="C182">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="183" spans="1:3">
+      <c r="A183">
+        <v>130</v>
+      </c>
+      <c r="B183" t="s">
+        <v>10</v>
+      </c>
+      <c r="C183">
         <v>1</v>
       </c>
     </row>

--- a/l_r/2nd.xlsx
+++ b/l_r/2nd.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PycharmProjects\english\english-study\l_r\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FDF4CD81-25FE-4CFE-A199-CC1240F49C84}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1DDFA323-CF4B-4C67-98A6-DA23F9D48927}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="480" yWindow="120" windowWidth="15840" windowHeight="15345" firstSheet="1" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-30" yWindow="45" windowWidth="15840" windowHeight="15345" firstSheet="1" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="summary" sheetId="3" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="240" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="252" uniqueCount="36">
   <si>
     <t>問題番号</t>
     <rPh sb="0" eb="2">
@@ -180,6 +180,22 @@
   </si>
   <si>
     <t>D</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>A</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>D</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>B</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>C</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -3312,14 +3328,14 @@
       </c>
       <c r="C9">
         <f>SUM(reading!C3:C42)</f>
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="D9">
         <v>40</v>
       </c>
       <c r="E9" s="1">
         <f t="shared" ref="E9:E11" si="1">C9/D9</f>
-        <v>0.47499999999999998</v>
+        <v>0.67500000000000004</v>
       </c>
     </row>
     <row r="10" spans="2:5">
@@ -3328,14 +3344,14 @@
       </c>
       <c r="C10">
         <f>SUM(reading!C43:C54)</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D10">
         <v>12</v>
       </c>
       <c r="E10" s="1">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>0.16666666666666666</v>
       </c>
     </row>
     <row r="11" spans="2:5">
@@ -3997,14 +4013,13 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{86A9B22D-A93D-442A-B8E1-1D68266591E9}">
-  <sheetPr filterMode="1"/>
   <dimension ref="A1:F102"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <sheetData>
     <row r="1" spans="1:3">
       <c r="C1">
         <f>SUM(C3:C102)</f>
-        <v>19</v>
+        <v>29</v>
       </c>
     </row>
     <row r="2" spans="1:3">
@@ -4018,7 +4033,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="1:3" hidden="1">
+    <row r="3" spans="1:3">
       <c r="A3">
         <v>101</v>
       </c>
@@ -4029,7 +4044,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:3" hidden="1">
+    <row r="4" spans="1:3">
       <c r="A4">
         <f>A3+1</f>
         <v>102</v>
@@ -4053,7 +4068,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:3" hidden="1">
+    <row r="6" spans="1:3">
       <c r="A6">
         <f t="shared" si="0"/>
         <v>104</v>
@@ -4077,7 +4092,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:3" hidden="1">
+    <row r="8" spans="1:3">
       <c r="A8">
         <f t="shared" si="0"/>
         <v>106</v>
@@ -4113,7 +4128,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:3" hidden="1">
+    <row r="11" spans="1:3">
       <c r="A11">
         <f t="shared" si="0"/>
         <v>109</v>
@@ -4125,7 +4140,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:3" hidden="1">
+    <row r="12" spans="1:3">
       <c r="A12">
         <f t="shared" si="0"/>
         <v>110</v>
@@ -4137,7 +4152,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:3" hidden="1">
+    <row r="13" spans="1:3">
       <c r="A13">
         <f t="shared" si="0"/>
         <v>111</v>
@@ -4149,7 +4164,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:3" hidden="1">
+    <row r="14" spans="1:3">
       <c r="A14">
         <f t="shared" si="0"/>
         <v>112</v>
@@ -4185,7 +4200,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:6" hidden="1">
+    <row r="17" spans="1:6">
       <c r="A17">
         <f t="shared" si="0"/>
         <v>115</v>
@@ -4200,7 +4215,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="18" spans="1:6" hidden="1">
+    <row r="18" spans="1:6">
       <c r="A18">
         <f t="shared" si="0"/>
         <v>116</v>
@@ -4227,7 +4242,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:6" hidden="1">
+    <row r="20" spans="1:6">
       <c r="A20">
         <f t="shared" si="0"/>
         <v>118</v>
@@ -4239,7 +4254,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="21" spans="1:6" hidden="1">
+    <row r="21" spans="1:6">
       <c r="A21">
         <f t="shared" si="0"/>
         <v>119</v>
@@ -4263,7 +4278,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:6" hidden="1">
+    <row r="23" spans="1:6">
       <c r="A23">
         <f t="shared" si="0"/>
         <v>121</v>
@@ -4275,7 +4290,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="24" spans="1:6" hidden="1">
+    <row r="24" spans="1:6">
       <c r="A24">
         <f t="shared" si="0"/>
         <v>122</v>
@@ -4287,7 +4302,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="25" spans="1:6" hidden="1">
+    <row r="25" spans="1:6">
       <c r="A25">
         <f t="shared" si="0"/>
         <v>123</v>
@@ -4299,7 +4314,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="26" spans="1:6" hidden="1">
+    <row r="26" spans="1:6">
       <c r="A26">
         <f t="shared" si="0"/>
         <v>124</v>
@@ -4314,7 +4329,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="27" spans="1:6" hidden="1">
+    <row r="27" spans="1:6">
       <c r="A27">
         <f t="shared" si="0"/>
         <v>125</v>
@@ -4329,7 +4344,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="28" spans="1:6" hidden="1">
+    <row r="28" spans="1:6">
       <c r="A28">
         <f t="shared" si="0"/>
         <v>126</v>
@@ -4356,7 +4371,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:6" hidden="1">
+    <row r="30" spans="1:6">
       <c r="A30">
         <f t="shared" si="0"/>
         <v>128</v>
@@ -4392,434 +4407,500 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:1" hidden="1">
+    <row r="33" spans="1:3">
       <c r="A33">
         <f t="shared" si="0"/>
         <v>131</v>
       </c>
-    </row>
-    <row r="34" spans="1:1" hidden="1">
+      <c r="B33" t="s">
+        <v>32</v>
+      </c>
+      <c r="C33">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3">
       <c r="A34">
         <f t="shared" si="0"/>
         <v>132</v>
       </c>
-    </row>
-    <row r="35" spans="1:1" hidden="1">
+      <c r="B34" t="s">
+        <v>33</v>
+      </c>
+      <c r="C34">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3">
       <c r="A35">
         <f t="shared" si="0"/>
         <v>133</v>
       </c>
-    </row>
-    <row r="36" spans="1:1" hidden="1">
+      <c r="B35" t="s">
+        <v>34</v>
+      </c>
+      <c r="C35">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3">
       <c r="A36">
         <f t="shared" si="0"/>
         <v>134</v>
       </c>
-    </row>
-    <row r="37" spans="1:1" hidden="1">
+      <c r="B36" t="s">
+        <v>35</v>
+      </c>
+      <c r="C36">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3">
       <c r="A37">
         <f t="shared" si="0"/>
         <v>135</v>
       </c>
-    </row>
-    <row r="38" spans="1:1" hidden="1">
+      <c r="B37" t="s">
+        <v>35</v>
+      </c>
+      <c r="C37">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3">
       <c r="A38">
         <f t="shared" si="0"/>
         <v>136</v>
       </c>
-    </row>
-    <row r="39" spans="1:1" hidden="1">
+      <c r="B38" t="s">
+        <v>32</v>
+      </c>
+      <c r="C38">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3">
       <c r="A39">
         <f t="shared" si="0"/>
         <v>137</v>
       </c>
-    </row>
-    <row r="40" spans="1:1" hidden="1">
+      <c r="B39" t="s">
+        <v>32</v>
+      </c>
+      <c r="C39">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3">
       <c r="A40">
         <f t="shared" si="0"/>
         <v>138</v>
       </c>
-    </row>
-    <row r="41" spans="1:1" hidden="1">
+      <c r="B40" t="s">
+        <v>33</v>
+      </c>
+      <c r="C40">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3">
       <c r="A41">
         <f t="shared" si="0"/>
         <v>139</v>
       </c>
-    </row>
-    <row r="42" spans="1:1" hidden="1">
+      <c r="B41" t="s">
+        <v>33</v>
+      </c>
+      <c r="C41">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3">
       <c r="A42">
         <f t="shared" si="0"/>
         <v>140</v>
       </c>
-    </row>
-    <row r="43" spans="1:1" hidden="1">
+      <c r="B42" t="s">
+        <v>33</v>
+      </c>
+      <c r="C42">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3">
       <c r="A43">
         <f t="shared" si="0"/>
         <v>141</v>
       </c>
-    </row>
-    <row r="44" spans="1:1" hidden="1">
+      <c r="B43" t="s">
+        <v>34</v>
+      </c>
+      <c r="C43">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3">
       <c r="A44">
         <f t="shared" si="0"/>
         <v>142</v>
       </c>
-    </row>
-    <row r="45" spans="1:1" hidden="1">
+      <c r="B44" t="s">
+        <v>32</v>
+      </c>
+      <c r="C44">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3">
       <c r="A45">
         <f t="shared" si="0"/>
         <v>143</v>
       </c>
     </row>
-    <row r="46" spans="1:1" hidden="1">
+    <row r="46" spans="1:3">
       <c r="A46">
         <f t="shared" si="0"/>
         <v>144</v>
       </c>
     </row>
-    <row r="47" spans="1:1" hidden="1">
+    <row r="47" spans="1:3">
       <c r="A47">
         <f t="shared" si="0"/>
         <v>145</v>
       </c>
     </row>
-    <row r="48" spans="1:1" hidden="1">
+    <row r="48" spans="1:3">
       <c r="A48">
         <f t="shared" si="0"/>
         <v>146</v>
       </c>
     </row>
-    <row r="49" spans="1:1" hidden="1">
+    <row r="49" spans="1:1">
       <c r="A49">
         <f t="shared" si="0"/>
         <v>147</v>
       </c>
     </row>
-    <row r="50" spans="1:1" hidden="1">
+    <row r="50" spans="1:1">
       <c r="A50">
         <f t="shared" si="0"/>
         <v>148</v>
       </c>
     </row>
-    <row r="51" spans="1:1" hidden="1">
+    <row r="51" spans="1:1">
       <c r="A51">
         <f t="shared" si="0"/>
         <v>149</v>
       </c>
     </row>
-    <row r="52" spans="1:1" hidden="1">
+    <row r="52" spans="1:1">
       <c r="A52">
         <f t="shared" si="0"/>
         <v>150</v>
       </c>
     </row>
-    <row r="53" spans="1:1" hidden="1">
+    <row r="53" spans="1:1">
       <c r="A53">
         <f t="shared" si="0"/>
         <v>151</v>
       </c>
     </row>
-    <row r="54" spans="1:1" hidden="1">
+    <row r="54" spans="1:1">
       <c r="A54">
         <f t="shared" si="0"/>
         <v>152</v>
       </c>
     </row>
-    <row r="55" spans="1:1" hidden="1">
+    <row r="55" spans="1:1">
       <c r="A55">
         <f t="shared" si="0"/>
         <v>153</v>
       </c>
     </row>
-    <row r="56" spans="1:1" hidden="1">
+    <row r="56" spans="1:1">
       <c r="A56">
         <f t="shared" si="0"/>
         <v>154</v>
       </c>
     </row>
-    <row r="57" spans="1:1" hidden="1">
+    <row r="57" spans="1:1">
       <c r="A57">
         <f t="shared" si="0"/>
         <v>155</v>
       </c>
     </row>
-    <row r="58" spans="1:1" hidden="1">
+    <row r="58" spans="1:1">
       <c r="A58">
         <f t="shared" si="0"/>
         <v>156</v>
       </c>
     </row>
-    <row r="59" spans="1:1" hidden="1">
+    <row r="59" spans="1:1">
       <c r="A59">
         <f t="shared" si="0"/>
         <v>157</v>
       </c>
     </row>
-    <row r="60" spans="1:1" hidden="1">
+    <row r="60" spans="1:1">
       <c r="A60">
         <f t="shared" si="0"/>
         <v>158</v>
       </c>
     </row>
-    <row r="61" spans="1:1" hidden="1">
+    <row r="61" spans="1:1">
       <c r="A61">
         <f t="shared" si="0"/>
         <v>159</v>
       </c>
     </row>
-    <row r="62" spans="1:1" hidden="1">
+    <row r="62" spans="1:1">
       <c r="A62">
         <f t="shared" si="0"/>
         <v>160</v>
       </c>
     </row>
-    <row r="63" spans="1:1" hidden="1">
+    <row r="63" spans="1:1">
       <c r="A63">
         <f t="shared" si="0"/>
         <v>161</v>
       </c>
     </row>
-    <row r="64" spans="1:1" hidden="1">
+    <row r="64" spans="1:1">
       <c r="A64">
         <f t="shared" si="0"/>
         <v>162</v>
       </c>
     </row>
-    <row r="65" spans="1:1" hidden="1">
+    <row r="65" spans="1:1">
       <c r="A65">
         <f t="shared" si="0"/>
         <v>163</v>
       </c>
     </row>
-    <row r="66" spans="1:1" hidden="1">
+    <row r="66" spans="1:1">
       <c r="A66">
         <f t="shared" si="0"/>
         <v>164</v>
       </c>
     </row>
-    <row r="67" spans="1:1" hidden="1">
+    <row r="67" spans="1:1">
       <c r="A67">
         <f t="shared" si="0"/>
         <v>165</v>
       </c>
     </row>
-    <row r="68" spans="1:1" hidden="1">
+    <row r="68" spans="1:1">
       <c r="A68">
         <f t="shared" si="0"/>
         <v>166</v>
       </c>
     </row>
-    <row r="69" spans="1:1" hidden="1">
+    <row r="69" spans="1:1">
       <c r="A69">
         <f t="shared" ref="A69:A102" si="1">A68+1</f>
         <v>167</v>
       </c>
     </row>
-    <row r="70" spans="1:1" hidden="1">
+    <row r="70" spans="1:1">
       <c r="A70">
         <f t="shared" si="1"/>
         <v>168</v>
       </c>
     </row>
-    <row r="71" spans="1:1" hidden="1">
+    <row r="71" spans="1:1">
       <c r="A71">
         <f t="shared" si="1"/>
         <v>169</v>
       </c>
     </row>
-    <row r="72" spans="1:1" hidden="1">
+    <row r="72" spans="1:1">
       <c r="A72">
         <f t="shared" si="1"/>
         <v>170</v>
       </c>
     </row>
-    <row r="73" spans="1:1" hidden="1">
+    <row r="73" spans="1:1">
       <c r="A73">
         <f t="shared" si="1"/>
         <v>171</v>
       </c>
     </row>
-    <row r="74" spans="1:1" hidden="1">
+    <row r="74" spans="1:1">
       <c r="A74">
         <f t="shared" si="1"/>
         <v>172</v>
       </c>
     </row>
-    <row r="75" spans="1:1" hidden="1">
+    <row r="75" spans="1:1">
       <c r="A75">
         <f t="shared" si="1"/>
         <v>173</v>
       </c>
     </row>
-    <row r="76" spans="1:1" hidden="1">
+    <row r="76" spans="1:1">
       <c r="A76">
         <f t="shared" si="1"/>
         <v>174</v>
       </c>
     </row>
-    <row r="77" spans="1:1" hidden="1">
+    <row r="77" spans="1:1">
       <c r="A77">
         <f t="shared" si="1"/>
         <v>175</v>
       </c>
     </row>
-    <row r="78" spans="1:1" hidden="1">
+    <row r="78" spans="1:1">
       <c r="A78">
         <f t="shared" si="1"/>
         <v>176</v>
       </c>
     </row>
-    <row r="79" spans="1:1" hidden="1">
+    <row r="79" spans="1:1">
       <c r="A79">
         <f t="shared" si="1"/>
         <v>177</v>
       </c>
     </row>
-    <row r="80" spans="1:1" hidden="1">
+    <row r="80" spans="1:1">
       <c r="A80">
         <f t="shared" si="1"/>
         <v>178</v>
       </c>
     </row>
-    <row r="81" spans="1:1" hidden="1">
+    <row r="81" spans="1:1">
       <c r="A81">
         <f t="shared" si="1"/>
         <v>179</v>
       </c>
     </row>
-    <row r="82" spans="1:1" hidden="1">
+    <row r="82" spans="1:1">
       <c r="A82">
         <f t="shared" si="1"/>
         <v>180</v>
       </c>
     </row>
-    <row r="83" spans="1:1" hidden="1">
+    <row r="83" spans="1:1">
       <c r="A83">
         <f t="shared" si="1"/>
         <v>181</v>
       </c>
     </row>
-    <row r="84" spans="1:1" hidden="1">
+    <row r="84" spans="1:1">
       <c r="A84">
         <f t="shared" si="1"/>
         <v>182</v>
       </c>
     </row>
-    <row r="85" spans="1:1" hidden="1">
+    <row r="85" spans="1:1">
       <c r="A85">
         <f t="shared" si="1"/>
         <v>183</v>
       </c>
     </row>
-    <row r="86" spans="1:1" hidden="1">
+    <row r="86" spans="1:1">
       <c r="A86">
         <f t="shared" si="1"/>
         <v>184</v>
       </c>
     </row>
-    <row r="87" spans="1:1" hidden="1">
+    <row r="87" spans="1:1">
       <c r="A87">
         <f t="shared" si="1"/>
         <v>185</v>
       </c>
     </row>
-    <row r="88" spans="1:1" hidden="1">
+    <row r="88" spans="1:1">
       <c r="A88">
         <f t="shared" si="1"/>
         <v>186</v>
       </c>
     </row>
-    <row r="89" spans="1:1" hidden="1">
+    <row r="89" spans="1:1">
       <c r="A89">
         <f t="shared" si="1"/>
         <v>187</v>
       </c>
     </row>
-    <row r="90" spans="1:1" hidden="1">
+    <row r="90" spans="1:1">
       <c r="A90">
         <f t="shared" si="1"/>
         <v>188</v>
       </c>
     </row>
-    <row r="91" spans="1:1" hidden="1">
+    <row r="91" spans="1:1">
       <c r="A91">
         <f t="shared" si="1"/>
         <v>189</v>
       </c>
     </row>
-    <row r="92" spans="1:1" hidden="1">
+    <row r="92" spans="1:1">
       <c r="A92">
         <f t="shared" si="1"/>
         <v>190</v>
       </c>
     </row>
-    <row r="93" spans="1:1" hidden="1">
+    <row r="93" spans="1:1">
       <c r="A93">
         <f t="shared" si="1"/>
         <v>191</v>
       </c>
     </row>
-    <row r="94" spans="1:1" hidden="1">
+    <row r="94" spans="1:1">
       <c r="A94">
         <f t="shared" si="1"/>
         <v>192</v>
       </c>
     </row>
-    <row r="95" spans="1:1" hidden="1">
+    <row r="95" spans="1:1">
       <c r="A95">
         <f t="shared" si="1"/>
         <v>193</v>
       </c>
     </row>
-    <row r="96" spans="1:1" hidden="1">
+    <row r="96" spans="1:1">
       <c r="A96">
         <f t="shared" si="1"/>
         <v>194</v>
       </c>
     </row>
-    <row r="97" spans="1:1" hidden="1">
+    <row r="97" spans="1:1">
       <c r="A97">
         <f t="shared" si="1"/>
         <v>195</v>
       </c>
     </row>
-    <row r="98" spans="1:1" hidden="1">
+    <row r="98" spans="1:1">
       <c r="A98">
         <f t="shared" si="1"/>
         <v>196</v>
       </c>
     </row>
-    <row r="99" spans="1:1" hidden="1">
+    <row r="99" spans="1:1">
       <c r="A99">
         <f t="shared" si="1"/>
         <v>197</v>
       </c>
     </row>
-    <row r="100" spans="1:1" hidden="1">
+    <row r="100" spans="1:1">
       <c r="A100">
         <f t="shared" si="1"/>
         <v>198</v>
       </c>
     </row>
-    <row r="101" spans="1:1" hidden="1">
+    <row r="101" spans="1:1">
       <c r="A101">
         <f t="shared" si="1"/>
         <v>199</v>
       </c>
     </row>
-    <row r="102" spans="1:1" hidden="1">
+    <row r="102" spans="1:1">
       <c r="A102">
         <f t="shared" si="1"/>
         <v>200</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A2:C102" xr:uid="{86A9B22D-A93D-442A-B8E1-1D68266591E9}">
-    <filterColumn colId="2">
-      <filters>
-        <filter val="0"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
+  <autoFilter ref="A2:C102" xr:uid="{86A9B22D-A93D-442A-B8E1-1D68266591E9}"/>
   <phoneticPr fontId="1"/>
   <dataValidations count="1">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B3:B102" xr:uid="{507A3D4C-54A2-49AD-8DD6-62E0792701B4}">

--- a/l_r/2nd.xlsx
+++ b/l_r/2nd.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PycharmProjects\english\english-study\l_r\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1DDFA323-CF4B-4C67-98A6-DA23F9D48927}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{418AC4C2-5A82-4FBC-81DA-48063B8BB30E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-30" yWindow="45" windowWidth="15840" windowHeight="15345" firstSheet="1" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-510" yWindow="0" windowWidth="14550" windowHeight="15585" firstSheet="1" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="summary" sheetId="3" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="252" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="262" uniqueCount="40">
   <si>
     <t>問題番号</t>
     <rPh sb="0" eb="2">
@@ -196,6 +196,22 @@
   </si>
   <si>
     <t>C</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>B</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>D</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>C</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>A</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -3344,14 +3360,14 @@
       </c>
       <c r="C10">
         <f>SUM(reading!C43:C54)</f>
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="D10">
         <v>12</v>
       </c>
       <c r="E10" s="1">
         <f t="shared" si="1"/>
-        <v>0.16666666666666666</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="11" spans="2:5">
@@ -4019,7 +4035,7 @@
     <row r="1" spans="1:3">
       <c r="C1">
         <f>SUM(C3:C102)</f>
-        <v>29</v>
+        <v>36</v>
       </c>
     </row>
     <row r="2" spans="1:3">
@@ -4556,116 +4572,176 @@
         <f t="shared" si="0"/>
         <v>143</v>
       </c>
+      <c r="B45" t="s">
+        <v>36</v>
+      </c>
+      <c r="C45">
+        <v>1</v>
+      </c>
     </row>
     <row r="46" spans="1:3">
       <c r="A46">
         <f t="shared" si="0"/>
         <v>144</v>
       </c>
+      <c r="B46" t="s">
+        <v>37</v>
+      </c>
+      <c r="C46">
+        <v>0</v>
+      </c>
     </row>
     <row r="47" spans="1:3">
       <c r="A47">
         <f t="shared" si="0"/>
         <v>145</v>
       </c>
+      <c r="B47" t="s">
+        <v>37</v>
+      </c>
+      <c r="C47">
+        <v>1</v>
+      </c>
     </row>
     <row r="48" spans="1:3">
       <c r="A48">
         <f t="shared" si="0"/>
         <v>146</v>
       </c>
-    </row>
-    <row r="49" spans="1:1">
+      <c r="B48" t="s">
+        <v>38</v>
+      </c>
+      <c r="C48">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3">
       <c r="A49">
         <f t="shared" si="0"/>
         <v>147</v>
       </c>
-    </row>
-    <row r="50" spans="1:1">
+      <c r="B49" t="s">
+        <v>39</v>
+      </c>
+      <c r="C49">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3">
       <c r="A50">
         <f t="shared" si="0"/>
         <v>148</v>
       </c>
-    </row>
-    <row r="51" spans="1:1">
+      <c r="B50" t="s">
+        <v>38</v>
+      </c>
+      <c r="C50">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3">
       <c r="A51">
         <f t="shared" si="0"/>
         <v>149</v>
       </c>
-    </row>
-    <row r="52" spans="1:1">
+      <c r="B51" t="s">
+        <v>37</v>
+      </c>
+      <c r="C51">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3">
       <c r="A52">
         <f t="shared" si="0"/>
         <v>150</v>
       </c>
-    </row>
-    <row r="53" spans="1:1">
+      <c r="B52" t="s">
+        <v>37</v>
+      </c>
+      <c r="C52">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="53" spans="1:3">
       <c r="A53">
         <f t="shared" si="0"/>
         <v>151</v>
       </c>
-    </row>
-    <row r="54" spans="1:1">
+      <c r="B53" t="s">
+        <v>38</v>
+      </c>
+      <c r="C53">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="54" spans="1:3">
       <c r="A54">
         <f t="shared" si="0"/>
         <v>152</v>
       </c>
-    </row>
-    <row r="55" spans="1:1">
+      <c r="B54" t="s">
+        <v>36</v>
+      </c>
+      <c r="C54">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="55" spans="1:3">
       <c r="A55">
         <f t="shared" si="0"/>
         <v>153</v>
       </c>
     </row>
-    <row r="56" spans="1:1">
+    <row r="56" spans="1:3">
       <c r="A56">
         <f t="shared" si="0"/>
         <v>154</v>
       </c>
     </row>
-    <row r="57" spans="1:1">
+    <row r="57" spans="1:3">
       <c r="A57">
         <f t="shared" si="0"/>
         <v>155</v>
       </c>
     </row>
-    <row r="58" spans="1:1">
+    <row r="58" spans="1:3">
       <c r="A58">
         <f t="shared" si="0"/>
         <v>156</v>
       </c>
     </row>
-    <row r="59" spans="1:1">
+    <row r="59" spans="1:3">
       <c r="A59">
         <f t="shared" si="0"/>
         <v>157</v>
       </c>
     </row>
-    <row r="60" spans="1:1">
+    <row r="60" spans="1:3">
       <c r="A60">
         <f t="shared" si="0"/>
         <v>158</v>
       </c>
     </row>
-    <row r="61" spans="1:1">
+    <row r="61" spans="1:3">
       <c r="A61">
         <f t="shared" si="0"/>
         <v>159</v>
       </c>
     </row>
-    <row r="62" spans="1:1">
+    <row r="62" spans="1:3">
       <c r="A62">
         <f t="shared" si="0"/>
         <v>160</v>
       </c>
     </row>
-    <row r="63" spans="1:1">
+    <row r="63" spans="1:3">
       <c r="A63">
         <f t="shared" si="0"/>
         <v>161</v>
       </c>
     </row>
-    <row r="64" spans="1:1">
+    <row r="64" spans="1:3">
       <c r="A64">
         <f t="shared" si="0"/>
         <v>162</v>

--- a/l_r/2nd.xlsx
+++ b/l_r/2nd.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PycharmProjects\english\english-study\l_r\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{418AC4C2-5A82-4FBC-81DA-48063B8BB30E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6F766B8F-C89A-42C5-A0A7-429037FA3E37}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-510" yWindow="0" windowWidth="14550" windowHeight="15585" firstSheet="1" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="45" windowWidth="15270" windowHeight="15345" firstSheet="1" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="summary" sheetId="3" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="262" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="267" uniqueCount="44">
   <si>
     <t>問題番号</t>
     <rPh sb="0" eb="2">
@@ -212,6 +212,22 @@
   </si>
   <si>
     <t>A</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>B</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>A</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>C</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>D</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -3376,14 +3392,14 @@
       </c>
       <c r="C11">
         <f>SUM(reading!C55:C102)</f>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D11">
         <v>48</v>
       </c>
       <c r="E11" s="1">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>0.10416666666666667</v>
       </c>
     </row>
   </sheetData>
@@ -4035,7 +4051,7 @@
     <row r="1" spans="1:3">
       <c r="C1">
         <f>SUM(C3:C102)</f>
-        <v>36</v>
+        <v>41</v>
       </c>
     </row>
     <row r="2" spans="1:3">
@@ -4692,29 +4708,59 @@
         <f t="shared" si="0"/>
         <v>153</v>
       </c>
+      <c r="B55" t="s">
+        <v>40</v>
+      </c>
+      <c r="C55">
+        <v>1</v>
+      </c>
     </row>
     <row r="56" spans="1:3">
       <c r="A56">
         <f t="shared" si="0"/>
         <v>154</v>
       </c>
+      <c r="B56" t="s">
+        <v>41</v>
+      </c>
+      <c r="C56">
+        <v>1</v>
+      </c>
     </row>
     <row r="57" spans="1:3">
       <c r="A57">
         <f t="shared" si="0"/>
         <v>155</v>
       </c>
+      <c r="B57" t="s">
+        <v>42</v>
+      </c>
+      <c r="C57">
+        <v>1</v>
+      </c>
     </row>
     <row r="58" spans="1:3">
       <c r="A58">
         <f t="shared" si="0"/>
         <v>156</v>
       </c>
+      <c r="B58" t="s">
+        <v>43</v>
+      </c>
+      <c r="C58">
+        <v>1</v>
+      </c>
     </row>
     <row r="59" spans="1:3">
       <c r="A59">
         <f t="shared" si="0"/>
         <v>157</v>
+      </c>
+      <c r="B59" t="s">
+        <v>43</v>
+      </c>
+      <c r="C59">
+        <v>1</v>
       </c>
     </row>
     <row r="60" spans="1:3">

--- a/l_r/2nd.xlsx
+++ b/l_r/2nd.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PycharmProjects\english\english-study\l_r\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6F766B8F-C89A-42C5-A0A7-429037FA3E37}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B3E5E567-1D43-4073-AF53-0349CD21BB3C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="45" windowWidth="15270" windowHeight="15345" firstSheet="1" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="1" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="summary" sheetId="3" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="267" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="273" uniqueCount="47">
   <si>
     <t>問題番号</t>
     <rPh sb="0" eb="2">
@@ -228,6 +228,18 @@
   </si>
   <si>
     <t>D</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>D</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>A</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>B</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -3392,14 +3404,14 @@
       </c>
       <c r="C11">
         <f>SUM(reading!C55:C102)</f>
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="D11">
         <v>48</v>
       </c>
       <c r="E11" s="1">
         <f t="shared" si="1"/>
-        <v>0.10416666666666667</v>
+        <v>0.22916666666666666</v>
       </c>
     </row>
   </sheetData>
@@ -4051,7 +4063,7 @@
     <row r="1" spans="1:3">
       <c r="C1">
         <f>SUM(C3:C102)</f>
-        <v>41</v>
+        <v>47</v>
       </c>
     </row>
     <row r="2" spans="1:3">
@@ -4768,122 +4780,158 @@
         <f t="shared" si="0"/>
         <v>158</v>
       </c>
+      <c r="B60" t="s">
+        <v>44</v>
+      </c>
+      <c r="C60">
+        <v>1</v>
+      </c>
     </row>
     <row r="61" spans="1:3">
       <c r="A61">
         <f t="shared" si="0"/>
         <v>159</v>
       </c>
+      <c r="B61" t="s">
+        <v>45</v>
+      </c>
+      <c r="C61">
+        <v>1</v>
+      </c>
     </row>
     <row r="62" spans="1:3">
       <c r="A62">
         <f t="shared" si="0"/>
         <v>160</v>
       </c>
+      <c r="B62" t="s">
+        <v>46</v>
+      </c>
+      <c r="C62">
+        <v>1</v>
+      </c>
     </row>
     <row r="63" spans="1:3">
       <c r="A63">
         <f t="shared" si="0"/>
         <v>161</v>
       </c>
+      <c r="B63" t="s">
+        <v>44</v>
+      </c>
+      <c r="C63">
+        <v>1</v>
+      </c>
     </row>
     <row r="64" spans="1:3">
       <c r="A64">
         <f t="shared" si="0"/>
         <v>162</v>
       </c>
-    </row>
-    <row r="65" spans="1:1">
+      <c r="B64" t="s">
+        <v>45</v>
+      </c>
+      <c r="C64">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="65" spans="1:3">
       <c r="A65">
         <f t="shared" si="0"/>
         <v>163</v>
       </c>
-    </row>
-    <row r="66" spans="1:1">
+      <c r="B65" t="s">
+        <v>44</v>
+      </c>
+      <c r="C65">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="66" spans="1:3">
       <c r="A66">
         <f t="shared" si="0"/>
         <v>164</v>
       </c>
     </row>
-    <row r="67" spans="1:1">
+    <row r="67" spans="1:3">
       <c r="A67">
         <f t="shared" si="0"/>
         <v>165</v>
       </c>
     </row>
-    <row r="68" spans="1:1">
+    <row r="68" spans="1:3">
       <c r="A68">
         <f t="shared" si="0"/>
         <v>166</v>
       </c>
     </row>
-    <row r="69" spans="1:1">
+    <row r="69" spans="1:3">
       <c r="A69">
         <f t="shared" ref="A69:A102" si="1">A68+1</f>
         <v>167</v>
       </c>
     </row>
-    <row r="70" spans="1:1">
+    <row r="70" spans="1:3">
       <c r="A70">
         <f t="shared" si="1"/>
         <v>168</v>
       </c>
     </row>
-    <row r="71" spans="1:1">
+    <row r="71" spans="1:3">
       <c r="A71">
         <f t="shared" si="1"/>
         <v>169</v>
       </c>
     </row>
-    <row r="72" spans="1:1">
+    <row r="72" spans="1:3">
       <c r="A72">
         <f t="shared" si="1"/>
         <v>170</v>
       </c>
     </row>
-    <row r="73" spans="1:1">
+    <row r="73" spans="1:3">
       <c r="A73">
         <f t="shared" si="1"/>
         <v>171</v>
       </c>
     </row>
-    <row r="74" spans="1:1">
+    <row r="74" spans="1:3">
       <c r="A74">
         <f t="shared" si="1"/>
         <v>172</v>
       </c>
     </row>
-    <row r="75" spans="1:1">
+    <row r="75" spans="1:3">
       <c r="A75">
         <f t="shared" si="1"/>
         <v>173</v>
       </c>
     </row>
-    <row r="76" spans="1:1">
+    <row r="76" spans="1:3">
       <c r="A76">
         <f t="shared" si="1"/>
         <v>174</v>
       </c>
     </row>
-    <row r="77" spans="1:1">
+    <row r="77" spans="1:3">
       <c r="A77">
         <f t="shared" si="1"/>
         <v>175</v>
       </c>
     </row>
-    <row r="78" spans="1:1">
+    <row r="78" spans="1:3">
       <c r="A78">
         <f t="shared" si="1"/>
         <v>176</v>
       </c>
     </row>
-    <row r="79" spans="1:1">
+    <row r="79" spans="1:3">
       <c r="A79">
         <f t="shared" si="1"/>
         <v>177</v>
       </c>
     </row>
-    <row r="80" spans="1:1">
+    <row r="80" spans="1:3">
       <c r="A80">
         <f t="shared" si="1"/>
         <v>178</v>

--- a/l_r/2nd.xlsx
+++ b/l_r/2nd.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PycharmProjects\english\english-study\l_r\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B3E5E567-1D43-4073-AF53-0349CD21BB3C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BFF86925-7DDA-4445-AD07-74233CC89604}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="1" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="225" yWindow="135" windowWidth="15270" windowHeight="15345" firstSheet="1" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="summary" sheetId="3" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="273" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="277" uniqueCount="49">
   <si>
     <t>問題番号</t>
     <rPh sb="0" eb="2">
@@ -236,6 +236,14 @@
   </si>
   <si>
     <t>A</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>B</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>C</t>
     <phoneticPr fontId="1"/>
   </si>
   <si>
@@ -4852,23 +4860,35 @@
         <f t="shared" si="0"/>
         <v>164</v>
       </c>
+      <c r="B66" t="s">
+        <v>47</v>
+      </c>
     </row>
     <row r="67" spans="1:3">
       <c r="A67">
         <f t="shared" si="0"/>
         <v>165</v>
       </c>
+      <c r="B67" t="s">
+        <v>47</v>
+      </c>
     </row>
     <row r="68" spans="1:3">
       <c r="A68">
         <f t="shared" si="0"/>
         <v>166</v>
+      </c>
+      <c r="B68" t="s">
+        <v>48</v>
       </c>
     </row>
     <row r="69" spans="1:3">
       <c r="A69">
         <f t="shared" ref="A69:A102" si="1">A68+1</f>
         <v>167</v>
+      </c>
+      <c r="B69" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="70" spans="1:3">

--- a/l_r/2nd.xlsx
+++ b/l_r/2nd.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PycharmProjects\english\english-study\l_r\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BFF86925-7DDA-4445-AD07-74233CC89604}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4EA25939-AC3D-4167-B217-3941A48B0273}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="225" yWindow="135" windowWidth="15270" windowHeight="15345" firstSheet="1" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="277" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="281" uniqueCount="51">
   <si>
     <t>問題番号</t>
     <rPh sb="0" eb="2">
@@ -248,6 +248,14 @@
   </si>
   <si>
     <t>B</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>B</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>C</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -3412,14 +3420,14 @@
       </c>
       <c r="C11">
         <f>SUM(reading!C55:C102)</f>
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="D11">
         <v>48</v>
       </c>
       <c r="E11" s="1">
         <f t="shared" si="1"/>
-        <v>0.22916666666666666</v>
+        <v>0.39583333333333331</v>
       </c>
     </row>
   </sheetData>
@@ -4071,7 +4079,7 @@
     <row r="1" spans="1:3">
       <c r="C1">
         <f>SUM(C3:C102)</f>
-        <v>47</v>
+        <v>55</v>
       </c>
     </row>
     <row r="2" spans="1:3">
@@ -4863,6 +4871,9 @@
       <c r="B66" t="s">
         <v>47</v>
       </c>
+      <c r="C66">
+        <v>1</v>
+      </c>
     </row>
     <row r="67" spans="1:3">
       <c r="A67">
@@ -4872,6 +4883,9 @@
       <c r="B67" t="s">
         <v>47</v>
       </c>
+      <c r="C67">
+        <v>1</v>
+      </c>
     </row>
     <row r="68" spans="1:3">
       <c r="A68">
@@ -4880,6 +4894,9 @@
       </c>
       <c r="B68" t="s">
         <v>48</v>
+      </c>
+      <c r="C68">
+        <v>1</v>
       </c>
     </row>
     <row r="69" spans="1:3">
@@ -4890,29 +4907,56 @@
       <c r="B69" t="s">
         <v>47</v>
       </c>
+      <c r="C69">
+        <v>1</v>
+      </c>
     </row>
     <row r="70" spans="1:3">
       <c r="A70">
         <f t="shared" si="1"/>
         <v>168</v>
       </c>
+      <c r="B70" t="s">
+        <v>49</v>
+      </c>
+      <c r="C70">
+        <v>1</v>
+      </c>
     </row>
     <row r="71" spans="1:3">
       <c r="A71">
         <f t="shared" si="1"/>
         <v>169</v>
       </c>
+      <c r="B71" t="s">
+        <v>50</v>
+      </c>
+      <c r="C71">
+        <v>1</v>
+      </c>
     </row>
     <row r="72" spans="1:3">
       <c r="A72">
         <f t="shared" si="1"/>
         <v>170</v>
       </c>
+      <c r="B72" t="s">
+        <v>49</v>
+      </c>
+      <c r="C72">
+        <v>1</v>
+      </c>
     </row>
     <row r="73" spans="1:3">
       <c r="A73">
         <f t="shared" si="1"/>
         <v>171</v>
+      </c>
+      <c r="B73" t="s">
+        <v>50</v>
+      </c>
+      <c r="C73">
+        <v>1</v>
       </c>
     </row>
     <row r="74" spans="1:3">

--- a/l_r/2nd.xlsx
+++ b/l_r/2nd.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PycharmProjects\english\english-study\l_r\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4EA25939-AC3D-4167-B217-3941A48B0273}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C625B199-B38E-4D95-BF27-A17621E1303C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="225" yWindow="135" windowWidth="15270" windowHeight="15345" firstSheet="1" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="225" yWindow="135" windowWidth="13950" windowHeight="15345" firstSheet="1" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="summary" sheetId="3" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="281" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="285" uniqueCount="54">
   <si>
     <t>問題番号</t>
     <rPh sb="0" eb="2">
@@ -248,6 +248,18 @@
   </si>
   <si>
     <t>B</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>B</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>C</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>A</t>
     <phoneticPr fontId="1"/>
   </si>
   <si>
@@ -3420,14 +3432,14 @@
       </c>
       <c r="C11">
         <f>SUM(reading!C55:C102)</f>
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="D11">
         <v>48</v>
       </c>
       <c r="E11" s="1">
         <f t="shared" si="1"/>
-        <v>0.39583333333333331</v>
+        <v>0.45833333333333331</v>
       </c>
     </row>
   </sheetData>
@@ -4079,7 +4091,7 @@
     <row r="1" spans="1:3">
       <c r="C1">
         <f>SUM(C3:C102)</f>
-        <v>55</v>
+        <v>58</v>
       </c>
     </row>
     <row r="2" spans="1:3">
@@ -4964,23 +4976,44 @@
         <f t="shared" si="1"/>
         <v>172</v>
       </c>
+      <c r="B74" t="s">
+        <v>51</v>
+      </c>
+      <c r="C74">
+        <v>1</v>
+      </c>
     </row>
     <row r="75" spans="1:3">
       <c r="A75">
         <f t="shared" si="1"/>
         <v>173</v>
       </c>
+      <c r="B75" t="s">
+        <v>51</v>
+      </c>
+      <c r="C75">
+        <v>1</v>
+      </c>
     </row>
     <row r="76" spans="1:3">
       <c r="A76">
         <f t="shared" si="1"/>
         <v>174</v>
       </c>
+      <c r="B76" t="s">
+        <v>52</v>
+      </c>
+      <c r="C76">
+        <v>1</v>
+      </c>
     </row>
     <row r="77" spans="1:3">
       <c r="A77">
         <f t="shared" si="1"/>
         <v>175</v>
+      </c>
+      <c r="B77" t="s">
+        <v>53</v>
       </c>
     </row>
     <row r="78" spans="1:3">

--- a/l_r/2nd.xlsx
+++ b/l_r/2nd.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PycharmProjects\english\english-study\l_r\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C625B199-B38E-4D95-BF27-A17621E1303C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ED9CCFE8-7BB3-4DA3-BFD9-B54F99084489}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="225" yWindow="135" windowWidth="13950" windowHeight="15345" firstSheet="1" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="285" uniqueCount="54">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="290" uniqueCount="57">
   <si>
     <t>問題番号</t>
     <rPh sb="0" eb="2">
@@ -260,6 +260,18 @@
   </si>
   <si>
     <t>A</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>B</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>C</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>B</t>
     <phoneticPr fontId="1"/>
   </si>
   <si>
@@ -3432,14 +3444,14 @@
       </c>
       <c r="C11">
         <f>SUM(reading!C55:C102)</f>
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="D11">
         <v>48</v>
       </c>
       <c r="E11" s="1">
         <f t="shared" si="1"/>
-        <v>0.45833333333333331</v>
+        <v>0.5</v>
       </c>
     </row>
   </sheetData>
@@ -4091,7 +4103,7 @@
     <row r="1" spans="1:3">
       <c r="C1">
         <f>SUM(C3:C102)</f>
-        <v>58</v>
+        <v>60</v>
       </c>
     </row>
     <row r="2" spans="1:3">
@@ -5015,116 +5027,149 @@
       <c r="B77" t="s">
         <v>53</v>
       </c>
+      <c r="C77">
+        <v>0</v>
+      </c>
     </row>
     <row r="78" spans="1:3">
       <c r="A78">
         <f t="shared" si="1"/>
         <v>176</v>
       </c>
+      <c r="B78" t="s">
+        <v>54</v>
+      </c>
+      <c r="C78">
+        <v>0</v>
+      </c>
     </row>
     <row r="79" spans="1:3">
       <c r="A79">
         <f t="shared" si="1"/>
         <v>177</v>
       </c>
+      <c r="B79" t="s">
+        <v>55</v>
+      </c>
+      <c r="C79">
+        <v>0</v>
+      </c>
     </row>
     <row r="80" spans="1:3">
       <c r="A80">
         <f t="shared" si="1"/>
         <v>178</v>
       </c>
-    </row>
-    <row r="81" spans="1:1">
+      <c r="B80" t="s">
+        <v>55</v>
+      </c>
+      <c r="C80">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="81" spans="1:3">
       <c r="A81">
         <f t="shared" si="1"/>
         <v>179</v>
       </c>
-    </row>
-    <row r="82" spans="1:1">
+      <c r="B81" t="s">
+        <v>55</v>
+      </c>
+      <c r="C81">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82" spans="1:3">
       <c r="A82">
         <f t="shared" si="1"/>
         <v>180</v>
       </c>
-    </row>
-    <row r="83" spans="1:1">
+      <c r="B82" t="s">
+        <v>56</v>
+      </c>
+      <c r="C82">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="83" spans="1:3">
       <c r="A83">
         <f t="shared" si="1"/>
         <v>181</v>
       </c>
     </row>
-    <row r="84" spans="1:1">
+    <row r="84" spans="1:3">
       <c r="A84">
         <f t="shared" si="1"/>
         <v>182</v>
       </c>
     </row>
-    <row r="85" spans="1:1">
+    <row r="85" spans="1:3">
       <c r="A85">
         <f t="shared" si="1"/>
         <v>183</v>
       </c>
     </row>
-    <row r="86" spans="1:1">
+    <row r="86" spans="1:3">
       <c r="A86">
         <f t="shared" si="1"/>
         <v>184</v>
       </c>
     </row>
-    <row r="87" spans="1:1">
+    <row r="87" spans="1:3">
       <c r="A87">
         <f t="shared" si="1"/>
         <v>185</v>
       </c>
     </row>
-    <row r="88" spans="1:1">
+    <row r="88" spans="1:3">
       <c r="A88">
         <f t="shared" si="1"/>
         <v>186</v>
       </c>
     </row>
-    <row r="89" spans="1:1">
+    <row r="89" spans="1:3">
       <c r="A89">
         <f t="shared" si="1"/>
         <v>187</v>
       </c>
     </row>
-    <row r="90" spans="1:1">
+    <row r="90" spans="1:3">
       <c r="A90">
         <f t="shared" si="1"/>
         <v>188</v>
       </c>
     </row>
-    <row r="91" spans="1:1">
+    <row r="91" spans="1:3">
       <c r="A91">
         <f t="shared" si="1"/>
         <v>189</v>
       </c>
     </row>
-    <row r="92" spans="1:1">
+    <row r="92" spans="1:3">
       <c r="A92">
         <f t="shared" si="1"/>
         <v>190</v>
       </c>
     </row>
-    <row r="93" spans="1:1">
+    <row r="93" spans="1:3">
       <c r="A93">
         <f t="shared" si="1"/>
         <v>191</v>
       </c>
     </row>
-    <row r="94" spans="1:1">
+    <row r="94" spans="1:3">
       <c r="A94">
         <f t="shared" si="1"/>
         <v>192</v>
       </c>
     </row>
-    <row r="95" spans="1:1">
+    <row r="95" spans="1:3">
       <c r="A95">
         <f t="shared" si="1"/>
         <v>193</v>
       </c>
     </row>
-    <row r="96" spans="1:1">
+    <row r="96" spans="1:3">
       <c r="A96">
         <f t="shared" si="1"/>
         <v>194</v>

--- a/l_r/2nd.xlsx
+++ b/l_r/2nd.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PycharmProjects\english\english-study\l_r\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ED9CCFE8-7BB3-4DA3-BFD9-B54F99084489}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7882953C-BFCA-4D79-9089-A2D83AEA84E0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="225" yWindow="135" windowWidth="13950" windowHeight="15345" firstSheet="1" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="290" uniqueCount="57">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="295" uniqueCount="61">
   <si>
     <t>問題番号</t>
     <rPh sb="0" eb="2">
@@ -280,6 +280,22 @@
   </si>
   <si>
     <t>C</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>B</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>C</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>D</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>A</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -3444,14 +3460,14 @@
       </c>
       <c r="C11">
         <f>SUM(reading!C55:C102)</f>
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="D11">
         <v>48</v>
       </c>
       <c r="E11" s="1">
         <f t="shared" si="1"/>
-        <v>0.5</v>
+        <v>0.60416666666666663</v>
       </c>
     </row>
   </sheetData>
@@ -4103,7 +4119,7 @@
     <row r="1" spans="1:3">
       <c r="C1">
         <f>SUM(C3:C102)</f>
-        <v>60</v>
+        <v>65</v>
       </c>
     </row>
     <row r="2" spans="1:3">
@@ -5096,29 +5112,59 @@
         <f t="shared" si="1"/>
         <v>181</v>
       </c>
+      <c r="B83" t="s">
+        <v>57</v>
+      </c>
+      <c r="C83">
+        <v>1</v>
+      </c>
     </row>
     <row r="84" spans="1:3">
       <c r="A84">
         <f t="shared" si="1"/>
         <v>182</v>
       </c>
+      <c r="B84" t="s">
+        <v>58</v>
+      </c>
+      <c r="C84">
+        <v>1</v>
+      </c>
     </row>
     <row r="85" spans="1:3">
       <c r="A85">
         <f t="shared" si="1"/>
         <v>183</v>
       </c>
+      <c r="B85" t="s">
+        <v>59</v>
+      </c>
+      <c r="C85">
+        <v>1</v>
+      </c>
     </row>
     <row r="86" spans="1:3">
       <c r="A86">
         <f t="shared" si="1"/>
         <v>184</v>
       </c>
+      <c r="B86" t="s">
+        <v>60</v>
+      </c>
+      <c r="C86">
+        <v>1</v>
+      </c>
     </row>
     <row r="87" spans="1:3">
       <c r="A87">
         <f t="shared" si="1"/>
         <v>185</v>
+      </c>
+      <c r="B87" t="s">
+        <v>59</v>
+      </c>
+      <c r="C87">
+        <v>1</v>
       </c>
     </row>
     <row r="88" spans="1:3">

--- a/l_r/2nd.xlsx
+++ b/l_r/2nd.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PycharmProjects\english\english-study\l_r\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7882953C-BFCA-4D79-9089-A2D83AEA84E0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5E3D4D03-31D4-43CB-8A88-63CF1A0A1B8D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="225" yWindow="135" windowWidth="13950" windowHeight="15345" firstSheet="1" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="295" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="300" uniqueCount="65">
   <si>
     <t>問題番号</t>
     <rPh sb="0" eb="2">
@@ -296,6 +296,22 @@
   </si>
   <si>
     <t>A</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>B</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>D</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>A</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>C</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -3460,14 +3476,14 @@
       </c>
       <c r="C11">
         <f>SUM(reading!C55:C102)</f>
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="D11">
         <v>48</v>
       </c>
       <c r="E11" s="1">
         <f t="shared" si="1"/>
-        <v>0.60416666666666663</v>
+        <v>0.66666666666666663</v>
       </c>
     </row>
   </sheetData>
@@ -4119,7 +4135,7 @@
     <row r="1" spans="1:3">
       <c r="C1">
         <f>SUM(C3:C102)</f>
-        <v>65</v>
+        <v>68</v>
       </c>
     </row>
     <row r="2" spans="1:3">
@@ -5172,29 +5188,59 @@
         <f t="shared" si="1"/>
         <v>186</v>
       </c>
+      <c r="B88" t="s">
+        <v>61</v>
+      </c>
+      <c r="C88">
+        <v>0</v>
+      </c>
     </row>
     <row r="89" spans="1:3">
       <c r="A89">
         <f t="shared" si="1"/>
         <v>187</v>
       </c>
+      <c r="B89" t="s">
+        <v>62</v>
+      </c>
+      <c r="C89">
+        <v>1</v>
+      </c>
     </row>
     <row r="90" spans="1:3">
       <c r="A90">
         <f t="shared" si="1"/>
         <v>188</v>
       </c>
+      <c r="B90" t="s">
+        <v>63</v>
+      </c>
+      <c r="C90">
+        <v>1</v>
+      </c>
     </row>
     <row r="91" spans="1:3">
       <c r="A91">
         <f t="shared" si="1"/>
         <v>189</v>
       </c>
+      <c r="B91" t="s">
+        <v>64</v>
+      </c>
+      <c r="C91">
+        <v>1</v>
+      </c>
     </row>
     <row r="92" spans="1:3">
       <c r="A92">
         <f t="shared" si="1"/>
         <v>190</v>
+      </c>
+      <c r="B92" t="s">
+        <v>62</v>
+      </c>
+      <c r="C92">
+        <v>0</v>
       </c>
     </row>
     <row r="93" spans="1:3">

--- a/l_r/2nd.xlsx
+++ b/l_r/2nd.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PycharmProjects\english\english-study\l_r\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5E3D4D03-31D4-43CB-8A88-63CF1A0A1B8D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3A8BA6CD-ABC3-410F-BAD1-9F9EE1CDA58D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="225" yWindow="135" windowWidth="13950" windowHeight="15345" firstSheet="1" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="300" uniqueCount="65">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="305" uniqueCount="69">
   <si>
     <t>問題番号</t>
     <rPh sb="0" eb="2">
@@ -312,6 +312,22 @@
   </si>
   <si>
     <t>C</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>D</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>C</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>A</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>B</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -3476,14 +3492,14 @@
       </c>
       <c r="C11">
         <f>SUM(reading!C55:C102)</f>
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="D11">
         <v>48</v>
       </c>
       <c r="E11" s="1">
         <f t="shared" si="1"/>
-        <v>0.66666666666666663</v>
+        <v>0.77083333333333337</v>
       </c>
     </row>
   </sheetData>
@@ -4135,7 +4151,7 @@
     <row r="1" spans="1:3">
       <c r="C1">
         <f>SUM(C3:C102)</f>
-        <v>68</v>
+        <v>73</v>
       </c>
     </row>
     <row r="2" spans="1:3">
@@ -5248,56 +5264,86 @@
         <f t="shared" si="1"/>
         <v>191</v>
       </c>
+      <c r="B93" t="s">
+        <v>65</v>
+      </c>
+      <c r="C93">
+        <v>1</v>
+      </c>
     </row>
     <row r="94" spans="1:3">
       <c r="A94">
         <f t="shared" si="1"/>
         <v>192</v>
       </c>
+      <c r="B94" t="s">
+        <v>66</v>
+      </c>
+      <c r="C94">
+        <v>1</v>
+      </c>
     </row>
     <row r="95" spans="1:3">
       <c r="A95">
         <f t="shared" si="1"/>
         <v>193</v>
       </c>
+      <c r="B95" t="s">
+        <v>68</v>
+      </c>
+      <c r="C95">
+        <v>1</v>
+      </c>
     </row>
     <row r="96" spans="1:3">
       <c r="A96">
         <f t="shared" si="1"/>
         <v>194</v>
       </c>
-    </row>
-    <row r="97" spans="1:1">
+      <c r="B96" t="s">
+        <v>65</v>
+      </c>
+      <c r="C96">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="97" spans="1:3">
       <c r="A97">
         <f t="shared" si="1"/>
         <v>195</v>
       </c>
-    </row>
-    <row r="98" spans="1:1">
+      <c r="B97" t="s">
+        <v>67</v>
+      </c>
+      <c r="C97">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="98" spans="1:3">
       <c r="A98">
         <f t="shared" si="1"/>
         <v>196</v>
       </c>
     </row>
-    <row r="99" spans="1:1">
+    <row r="99" spans="1:3">
       <c r="A99">
         <f t="shared" si="1"/>
         <v>197</v>
       </c>
     </row>
-    <row r="100" spans="1:1">
+    <row r="100" spans="1:3">
       <c r="A100">
         <f t="shared" si="1"/>
         <v>198</v>
       </c>
     </row>
-    <row r="101" spans="1:1">
+    <row r="101" spans="1:3">
       <c r="A101">
         <f t="shared" si="1"/>
         <v>199</v>
       </c>
     </row>
-    <row r="102" spans="1:1">
+    <row r="102" spans="1:3">
       <c r="A102">
         <f t="shared" si="1"/>
         <v>200</v>

--- a/l_r/2nd.xlsx
+++ b/l_r/2nd.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PycharmProjects\english\english-study\l_r\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3A8BA6CD-ABC3-410F-BAD1-9F9EE1CDA58D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{977A8DC1-2C98-4866-A56E-7139A1E5D3AD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="225" yWindow="135" windowWidth="13950" windowHeight="15345" firstSheet="1" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="305" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="310" uniqueCount="72">
   <si>
     <t>問題番号</t>
     <rPh sb="0" eb="2">
@@ -328,6 +328,18 @@
   </si>
   <si>
     <t>B</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>C</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>B</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>D</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -3492,14 +3504,14 @@
       </c>
       <c r="C11">
         <f>SUM(reading!C55:C102)</f>
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="D11">
         <v>48</v>
       </c>
       <c r="E11" s="1">
         <f t="shared" si="1"/>
-        <v>0.77083333333333337</v>
+        <v>0.85416666666666663</v>
       </c>
     </row>
   </sheetData>
@@ -4151,7 +4163,7 @@
     <row r="1" spans="1:3">
       <c r="C1">
         <f>SUM(C3:C102)</f>
-        <v>73</v>
+        <v>77</v>
       </c>
     </row>
     <row r="2" spans="1:3">
@@ -5324,29 +5336,59 @@
         <f t="shared" si="1"/>
         <v>196</v>
       </c>
+      <c r="B98" t="s">
+        <v>69</v>
+      </c>
+      <c r="C98">
+        <v>0</v>
+      </c>
     </row>
     <row r="99" spans="1:3">
       <c r="A99">
         <f t="shared" si="1"/>
         <v>197</v>
       </c>
+      <c r="B99" t="s">
+        <v>70</v>
+      </c>
+      <c r="C99">
+        <v>1</v>
+      </c>
     </row>
     <row r="100" spans="1:3">
       <c r="A100">
         <f t="shared" si="1"/>
         <v>198</v>
       </c>
+      <c r="B100" t="s">
+        <v>70</v>
+      </c>
+      <c r="C100">
+        <v>1</v>
+      </c>
     </row>
     <row r="101" spans="1:3">
       <c r="A101">
         <f t="shared" si="1"/>
         <v>199</v>
       </c>
+      <c r="B101" t="s">
+        <v>71</v>
+      </c>
+      <c r="C101">
+        <v>1</v>
+      </c>
     </row>
     <row r="102" spans="1:3">
       <c r="A102">
         <f t="shared" si="1"/>
         <v>200</v>
+      </c>
+      <c r="B102" t="s">
+        <v>70</v>
+      </c>
+      <c r="C102">
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/l_r/2nd.xlsx
+++ b/l_r/2nd.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PycharmProjects\english\english-study\l_r\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{977A8DC1-2C98-4866-A56E-7139A1E5D3AD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D16F77BC-F8A1-415D-8160-7975FFB181BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="225" yWindow="135" windowWidth="13950" windowHeight="15345" firstSheet="1" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2505" yWindow="75" windowWidth="14880" windowHeight="15345" firstSheet="1" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="summary" sheetId="3" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="310" uniqueCount="72">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="317" uniqueCount="72">
   <si>
     <t>問題番号</t>
     <rPh sb="0" eb="2">
@@ -4157,6 +4157,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{86A9B22D-A93D-442A-B8E1-1D68266591E9}">
+  <sheetPr filterMode="1"/>
   <dimension ref="A1:F102"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <sheetData>
@@ -4177,7 +4178,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="1:3">
+    <row r="3" spans="1:3" hidden="1">
       <c r="A3">
         <v>101</v>
       </c>
@@ -4188,7 +4189,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:3">
+    <row r="4" spans="1:3" hidden="1">
       <c r="A4">
         <f>A3+1</f>
         <v>102</v>
@@ -4212,7 +4213,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:3">
+    <row r="6" spans="1:3" hidden="1">
       <c r="A6">
         <f t="shared" si="0"/>
         <v>104</v>
@@ -4236,7 +4237,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:3">
+    <row r="8" spans="1:3" hidden="1">
       <c r="A8">
         <f t="shared" si="0"/>
         <v>106</v>
@@ -4272,7 +4273,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:3">
+    <row r="11" spans="1:3" hidden="1">
       <c r="A11">
         <f t="shared" si="0"/>
         <v>109</v>
@@ -4284,7 +4285,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:3">
+    <row r="12" spans="1:3" hidden="1">
       <c r="A12">
         <f t="shared" si="0"/>
         <v>110</v>
@@ -4296,7 +4297,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:3">
+    <row r="13" spans="1:3" hidden="1">
       <c r="A13">
         <f t="shared" si="0"/>
         <v>111</v>
@@ -4308,7 +4309,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:3">
+    <row r="14" spans="1:3" hidden="1">
       <c r="A14">
         <f t="shared" si="0"/>
         <v>112</v>
@@ -4344,7 +4345,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:6">
+    <row r="17" spans="1:6" hidden="1">
       <c r="A17">
         <f t="shared" si="0"/>
         <v>115</v>
@@ -4359,7 +4360,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="18" spans="1:6">
+    <row r="18" spans="1:6" hidden="1">
       <c r="A18">
         <f t="shared" si="0"/>
         <v>116</v>
@@ -4386,7 +4387,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:6">
+    <row r="20" spans="1:6" hidden="1">
       <c r="A20">
         <f t="shared" si="0"/>
         <v>118</v>
@@ -4398,7 +4399,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="21" spans="1:6">
+    <row r="21" spans="1:6" hidden="1">
       <c r="A21">
         <f t="shared" si="0"/>
         <v>119</v>
@@ -4422,7 +4423,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:6">
+    <row r="23" spans="1:6" hidden="1">
       <c r="A23">
         <f t="shared" si="0"/>
         <v>121</v>
@@ -4434,7 +4435,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="24" spans="1:6">
+    <row r="24" spans="1:6" hidden="1">
       <c r="A24">
         <f t="shared" si="0"/>
         <v>122</v>
@@ -4446,7 +4447,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="25" spans="1:6">
+    <row r="25" spans="1:6" hidden="1">
       <c r="A25">
         <f t="shared" si="0"/>
         <v>123</v>
@@ -4458,7 +4459,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="26" spans="1:6">
+    <row r="26" spans="1:6" hidden="1">
       <c r="A26">
         <f t="shared" si="0"/>
         <v>124</v>
@@ -4473,7 +4474,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="27" spans="1:6">
+    <row r="27" spans="1:6" hidden="1">
       <c r="A27">
         <f t="shared" si="0"/>
         <v>125</v>
@@ -4488,7 +4489,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="28" spans="1:6">
+    <row r="28" spans="1:6" hidden="1">
       <c r="A28">
         <f t="shared" si="0"/>
         <v>126</v>
@@ -4515,7 +4516,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:6">
+    <row r="30" spans="1:6" hidden="1">
       <c r="A30">
         <f t="shared" si="0"/>
         <v>128</v>
@@ -4551,7 +4552,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:3">
+    <row r="33" spans="1:3" hidden="1">
       <c r="A33">
         <f t="shared" si="0"/>
         <v>131</v>
@@ -4563,7 +4564,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="34" spans="1:3">
+    <row r="34" spans="1:3" hidden="1">
       <c r="A34">
         <f t="shared" si="0"/>
         <v>132</v>
@@ -4575,7 +4576,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="35" spans="1:3">
+    <row r="35" spans="1:3" hidden="1">
       <c r="A35">
         <f t="shared" si="0"/>
         <v>133</v>
@@ -4587,7 +4588,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="36" spans="1:3">
+    <row r="36" spans="1:3" hidden="1">
       <c r="A36">
         <f t="shared" si="0"/>
         <v>134</v>
@@ -4599,7 +4600,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="37" spans="1:3">
+    <row r="37" spans="1:3" hidden="1">
       <c r="A37">
         <f t="shared" si="0"/>
         <v>135</v>
@@ -4623,7 +4624,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:3">
+    <row r="39" spans="1:3" hidden="1">
       <c r="A39">
         <f t="shared" si="0"/>
         <v>137</v>
@@ -4635,7 +4636,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="40" spans="1:3">
+    <row r="40" spans="1:3" hidden="1">
       <c r="A40">
         <f t="shared" si="0"/>
         <v>138</v>
@@ -4647,7 +4648,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="41" spans="1:3">
+    <row r="41" spans="1:3" hidden="1">
       <c r="A41">
         <f t="shared" si="0"/>
         <v>139</v>
@@ -4671,7 +4672,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="43" spans="1:3">
+    <row r="43" spans="1:3" hidden="1">
       <c r="A43">
         <f t="shared" si="0"/>
         <v>141</v>
@@ -4683,7 +4684,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="44" spans="1:3">
+    <row r="44" spans="1:3" hidden="1">
       <c r="A44">
         <f t="shared" si="0"/>
         <v>142</v>
@@ -4695,7 +4696,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="45" spans="1:3">
+    <row r="45" spans="1:3" hidden="1">
       <c r="A45">
         <f t="shared" si="0"/>
         <v>143</v>
@@ -4719,7 +4720,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="1:3">
+    <row r="47" spans="1:3" hidden="1">
       <c r="A47">
         <f t="shared" si="0"/>
         <v>145</v>
@@ -4731,7 +4732,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="48" spans="1:3">
+    <row r="48" spans="1:3" hidden="1">
       <c r="A48">
         <f t="shared" si="0"/>
         <v>146</v>
@@ -4743,7 +4744,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="49" spans="1:3">
+    <row r="49" spans="1:3" hidden="1">
       <c r="A49">
         <f t="shared" si="0"/>
         <v>147</v>
@@ -4779,7 +4780,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="52" spans="1:3">
+    <row r="52" spans="1:3" hidden="1">
       <c r="A52">
         <f t="shared" si="0"/>
         <v>150</v>
@@ -4791,7 +4792,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="53" spans="1:3">
+    <row r="53" spans="1:3" hidden="1">
       <c r="A53">
         <f t="shared" si="0"/>
         <v>151</v>
@@ -4803,7 +4804,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="54" spans="1:3">
+    <row r="54" spans="1:3" hidden="1">
       <c r="A54">
         <f t="shared" si="0"/>
         <v>152</v>
@@ -4815,7 +4816,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="55" spans="1:3">
+    <row r="55" spans="1:3" hidden="1">
       <c r="A55">
         <f t="shared" si="0"/>
         <v>153</v>
@@ -4827,7 +4828,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="56" spans="1:3">
+    <row r="56" spans="1:3" hidden="1">
       <c r="A56">
         <f t="shared" si="0"/>
         <v>154</v>
@@ -4839,7 +4840,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="57" spans="1:3">
+    <row r="57" spans="1:3" hidden="1">
       <c r="A57">
         <f t="shared" si="0"/>
         <v>155</v>
@@ -4851,7 +4852,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="58" spans="1:3">
+    <row r="58" spans="1:3" hidden="1">
       <c r="A58">
         <f t="shared" si="0"/>
         <v>156</v>
@@ -4863,7 +4864,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="59" spans="1:3">
+    <row r="59" spans="1:3" hidden="1">
       <c r="A59">
         <f t="shared" si="0"/>
         <v>157</v>
@@ -4875,7 +4876,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="60" spans="1:3">
+    <row r="60" spans="1:3" hidden="1">
       <c r="A60">
         <f t="shared" si="0"/>
         <v>158</v>
@@ -4887,7 +4888,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="61" spans="1:3">
+    <row r="61" spans="1:3" hidden="1">
       <c r="A61">
         <f t="shared" si="0"/>
         <v>159</v>
@@ -4899,7 +4900,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="62" spans="1:3">
+    <row r="62" spans="1:3" hidden="1">
       <c r="A62">
         <f t="shared" si="0"/>
         <v>160</v>
@@ -4911,7 +4912,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="63" spans="1:3">
+    <row r="63" spans="1:3" hidden="1">
       <c r="A63">
         <f t="shared" si="0"/>
         <v>161</v>
@@ -4923,7 +4924,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="64" spans="1:3">
+    <row r="64" spans="1:3" hidden="1">
       <c r="A64">
         <f t="shared" si="0"/>
         <v>162</v>
@@ -4935,7 +4936,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="65" spans="1:3">
+    <row r="65" spans="1:3" hidden="1">
       <c r="A65">
         <f t="shared" si="0"/>
         <v>163</v>
@@ -4947,7 +4948,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="66" spans="1:3">
+    <row r="66" spans="1:3" hidden="1">
       <c r="A66">
         <f t="shared" si="0"/>
         <v>164</v>
@@ -4959,7 +4960,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="67" spans="1:3">
+    <row r="67" spans="1:3" hidden="1">
       <c r="A67">
         <f t="shared" si="0"/>
         <v>165</v>
@@ -4971,7 +4972,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="68" spans="1:3">
+    <row r="68" spans="1:3" hidden="1">
       <c r="A68">
         <f t="shared" si="0"/>
         <v>166</v>
@@ -4983,7 +4984,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="69" spans="1:3">
+    <row r="69" spans="1:3" hidden="1">
       <c r="A69">
         <f t="shared" ref="A69:A102" si="1">A68+1</f>
         <v>167</v>
@@ -4995,7 +4996,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="70" spans="1:3">
+    <row r="70" spans="1:3" hidden="1">
       <c r="A70">
         <f t="shared" si="1"/>
         <v>168</v>
@@ -5007,7 +5008,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="71" spans="1:3">
+    <row r="71" spans="1:3" hidden="1">
       <c r="A71">
         <f t="shared" si="1"/>
         <v>169</v>
@@ -5019,7 +5020,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="72" spans="1:3">
+    <row r="72" spans="1:3" hidden="1">
       <c r="A72">
         <f t="shared" si="1"/>
         <v>170</v>
@@ -5031,7 +5032,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="73" spans="1:3">
+    <row r="73" spans="1:3" hidden="1">
       <c r="A73">
         <f t="shared" si="1"/>
         <v>171</v>
@@ -5043,7 +5044,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="74" spans="1:3">
+    <row r="74" spans="1:3" hidden="1">
       <c r="A74">
         <f t="shared" si="1"/>
         <v>172</v>
@@ -5055,7 +5056,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="75" spans="1:3">
+    <row r="75" spans="1:3" hidden="1">
       <c r="A75">
         <f t="shared" si="1"/>
         <v>173</v>
@@ -5067,7 +5068,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="76" spans="1:3">
+    <row r="76" spans="1:3" hidden="1">
       <c r="A76">
         <f t="shared" si="1"/>
         <v>174</v>
@@ -5115,7 +5116,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="80" spans="1:3">
+    <row r="80" spans="1:3" hidden="1">
       <c r="A80">
         <f t="shared" si="1"/>
         <v>178</v>
@@ -5139,7 +5140,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="82" spans="1:3">
+    <row r="82" spans="1:3" hidden="1">
       <c r="A82">
         <f t="shared" si="1"/>
         <v>180</v>
@@ -5151,7 +5152,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="83" spans="1:3">
+    <row r="83" spans="1:3" hidden="1">
       <c r="A83">
         <f t="shared" si="1"/>
         <v>181</v>
@@ -5163,7 +5164,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="84" spans="1:3">
+    <row r="84" spans="1:3" hidden="1">
       <c r="A84">
         <f t="shared" si="1"/>
         <v>182</v>
@@ -5175,7 +5176,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="85" spans="1:3">
+    <row r="85" spans="1:3" hidden="1">
       <c r="A85">
         <f t="shared" si="1"/>
         <v>183</v>
@@ -5187,7 +5188,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="86" spans="1:3">
+    <row r="86" spans="1:3" hidden="1">
       <c r="A86">
         <f t="shared" si="1"/>
         <v>184</v>
@@ -5199,7 +5200,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="87" spans="1:3">
+    <row r="87" spans="1:3" hidden="1">
       <c r="A87">
         <f t="shared" si="1"/>
         <v>185</v>
@@ -5223,7 +5224,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="89" spans="1:3">
+    <row r="89" spans="1:3" hidden="1">
       <c r="A89">
         <f t="shared" si="1"/>
         <v>187</v>
@@ -5235,7 +5236,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="90" spans="1:3">
+    <row r="90" spans="1:3" hidden="1">
       <c r="A90">
         <f t="shared" si="1"/>
         <v>188</v>
@@ -5247,7 +5248,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="91" spans="1:3">
+    <row r="91" spans="1:3" hidden="1">
       <c r="A91">
         <f t="shared" si="1"/>
         <v>189</v>
@@ -5271,7 +5272,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="93" spans="1:3">
+    <row r="93" spans="1:3" hidden="1">
       <c r="A93">
         <f t="shared" si="1"/>
         <v>191</v>
@@ -5283,7 +5284,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="94" spans="1:3">
+    <row r="94" spans="1:3" hidden="1">
       <c r="A94">
         <f t="shared" si="1"/>
         <v>192</v>
@@ -5295,7 +5296,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="95" spans="1:3">
+    <row r="95" spans="1:3" hidden="1">
       <c r="A95">
         <f t="shared" si="1"/>
         <v>193</v>
@@ -5307,7 +5308,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="96" spans="1:3">
+    <row r="96" spans="1:3" hidden="1">
       <c r="A96">
         <f t="shared" si="1"/>
         <v>194</v>
@@ -5319,7 +5320,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="97" spans="1:3">
+    <row r="97" spans="1:3" hidden="1">
       <c r="A97">
         <f t="shared" si="1"/>
         <v>195</v>
@@ -5343,7 +5344,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="99" spans="1:3">
+    <row r="99" spans="1:3" hidden="1">
       <c r="A99">
         <f t="shared" si="1"/>
         <v>197</v>
@@ -5355,7 +5356,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="100" spans="1:3">
+    <row r="100" spans="1:3" hidden="1">
       <c r="A100">
         <f t="shared" si="1"/>
         <v>198</v>
@@ -5367,7 +5368,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="101" spans="1:3">
+    <row r="101" spans="1:3" hidden="1">
       <c r="A101">
         <f t="shared" si="1"/>
         <v>199</v>
@@ -5379,7 +5380,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="102" spans="1:3">
+    <row r="102" spans="1:3" hidden="1">
       <c r="A102">
         <f t="shared" si="1"/>
         <v>200</v>
@@ -5392,7 +5393,13 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A2:C102" xr:uid="{86A9B22D-A93D-442A-B8E1-1D68266591E9}"/>
+  <autoFilter ref="A2:C102" xr:uid="{86A9B22D-A93D-442A-B8E1-1D68266591E9}">
+    <filterColumn colId="2">
+      <filters>
+        <filter val="0"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <phoneticPr fontId="1"/>
   <dataValidations count="1">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B3:B102" xr:uid="{507A3D4C-54A2-49AD-8DD6-62E0792701B4}">
@@ -5405,7 +5412,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3C7A3EDD-6597-4754-A609-A225833ECC81}">
-  <dimension ref="A2:H183"/>
+  <dimension ref="A2:H190"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <sheetData>
     <row r="2" spans="1:4">
@@ -7532,10 +7539,87 @@
         <v>1</v>
       </c>
     </row>
+    <row r="184" spans="1:3">
+      <c r="A184">
+        <v>103</v>
+      </c>
+      <c r="B184" t="s">
+        <v>11</v>
+      </c>
+      <c r="C184">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="185" spans="1:3">
+      <c r="A185">
+        <v>105</v>
+      </c>
+      <c r="B185" t="s">
+        <v>9</v>
+      </c>
+      <c r="C185">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="186" spans="1:3">
+      <c r="A186">
+        <v>107</v>
+      </c>
+      <c r="B186" t="s">
+        <v>11</v>
+      </c>
+      <c r="C186">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="187" spans="1:3">
+      <c r="A187">
+        <v>108</v>
+      </c>
+      <c r="B187" t="s">
+        <v>9</v>
+      </c>
+      <c r="C187">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="188" spans="1:3">
+      <c r="A188">
+        <v>113</v>
+      </c>
+      <c r="B188" t="s">
+        <v>8</v>
+      </c>
+      <c r="C188">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="189" spans="1:3">
+      <c r="A189">
+        <v>114</v>
+      </c>
+      <c r="B189" t="s">
+        <v>9</v>
+      </c>
+      <c r="C189">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="190" spans="1:3">
+      <c r="A190">
+        <v>117</v>
+      </c>
+      <c r="B190" t="s">
+        <v>9</v>
+      </c>
+      <c r="C190">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1"/>
-  <dataValidations disablePrompts="1" count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B56:B59 B41:B50 B20:B32 B3:B17" xr:uid="{D8C212E3-0513-4E96-9660-7E8BB94F20D2}">
+  <dataValidations count="1">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B56:B59 B41:B50 B20:B32 B3:B17 B184:B190" xr:uid="{D8C212E3-0513-4E96-9660-7E8BB94F20D2}">
       <formula1>"A,B,C,D"</formula1>
     </dataValidation>
   </dataValidations>

--- a/l_r/2nd.xlsx
+++ b/l_r/2nd.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PycharmProjects\english\english-study\l_r\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D16F77BC-F8A1-415D-8160-7975FFB181BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6A8C7F5E-1D83-425B-9B8C-B427D5F636CD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="2505" yWindow="75" windowWidth="14880" windowHeight="15345" firstSheet="1" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="317" uniqueCount="72">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="329" uniqueCount="74">
   <si>
     <t>問題番号</t>
     <rPh sb="0" eb="2">
@@ -340,6 +340,17 @@
   </si>
   <si>
     <t>D</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>consolidate</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>集中する</t>
+    <rPh sb="0" eb="2">
+      <t>シュウチュウ</t>
+    </rPh>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -5412,7 +5423,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3C7A3EDD-6597-4754-A609-A225833ECC81}">
-  <dimension ref="A2:H190"/>
+  <dimension ref="A2:H198"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <sheetData>
     <row r="2" spans="1:4">
@@ -7614,6 +7625,106 @@
       </c>
       <c r="C190">
         <v>0</v>
+      </c>
+    </row>
+    <row r="191" spans="1:3">
+      <c r="A191">
+        <v>120</v>
+      </c>
+      <c r="B191" t="s">
+        <v>8</v>
+      </c>
+      <c r="C191">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="192" spans="1:3">
+      <c r="A192">
+        <v>127</v>
+      </c>
+      <c r="B192" t="s">
+        <v>11</v>
+      </c>
+      <c r="C192">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="193" spans="1:6">
+      <c r="A193">
+        <v>129</v>
+      </c>
+      <c r="B193" t="s">
+        <v>9</v>
+      </c>
+      <c r="C193">
+        <v>0</v>
+      </c>
+      <c r="E193" t="s">
+        <v>72</v>
+      </c>
+      <c r="F193" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="194" spans="1:6">
+      <c r="A194">
+        <v>130</v>
+      </c>
+      <c r="B194" t="s">
+        <v>10</v>
+      </c>
+      <c r="C194">
+        <v>1</v>
+      </c>
+      <c r="E194" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="195" spans="1:6">
+      <c r="A195">
+        <v>135</v>
+      </c>
+      <c r="B195" t="s">
+        <v>10</v>
+      </c>
+      <c r="C195">
+        <v>1</v>
+      </c>
+      <c r="E195" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="196" spans="1:6">
+      <c r="A196">
+        <v>136</v>
+      </c>
+      <c r="B196" t="s">
+        <v>9</v>
+      </c>
+      <c r="C196">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="197" spans="1:6">
+      <c r="A197">
+        <v>137</v>
+      </c>
+      <c r="B197" t="s">
+        <v>10</v>
+      </c>
+      <c r="C197">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="198" spans="1:6">
+      <c r="A198">
+        <v>138</v>
+      </c>
+      <c r="B198" t="s">
+        <v>11</v>
+      </c>
+      <c r="C198">
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/l_r/2nd.xlsx
+++ b/l_r/2nd.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PycharmProjects\english\english-study\l_r\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6A8C7F5E-1D83-425B-9B8C-B427D5F636CD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6E9897F9-209E-40FB-9748-D91B30031C6E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2505" yWindow="75" windowWidth="14880" windowHeight="15345" firstSheet="1" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="930" yWindow="30" windowWidth="14880" windowHeight="15345" firstSheet="1" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="summary" sheetId="3" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="329" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="340" uniqueCount="74">
   <si>
     <t>問題番号</t>
     <rPh sb="0" eb="2">
@@ -5412,7 +5412,7 @@
     </filterColumn>
   </autoFilter>
   <phoneticPr fontId="1"/>
-  <dataValidations count="1">
+  <dataValidations disablePrompts="1" count="1">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B3:B102" xr:uid="{507A3D4C-54A2-49AD-8DD6-62E0792701B4}">
       <formula1>"A,B,C,D"</formula1>
     </dataValidation>
@@ -5423,7 +5423,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3C7A3EDD-6597-4754-A609-A225833ECC81}">
-  <dimension ref="A2:H198"/>
+  <dimension ref="A2:H209"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <sheetData>
     <row r="2" spans="1:4">
@@ -7727,10 +7727,131 @@
         <v>1</v>
       </c>
     </row>
+    <row r="199" spans="1:6">
+      <c r="A199">
+        <v>103</v>
+      </c>
+      <c r="B199" t="s">
+        <v>11</v>
+      </c>
+      <c r="C199">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="200" spans="1:6">
+      <c r="A200">
+        <v>105</v>
+      </c>
+      <c r="B200" t="s">
+        <v>10</v>
+      </c>
+      <c r="C200">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="201" spans="1:6">
+      <c r="A201">
+        <v>107</v>
+      </c>
+      <c r="B201" t="s">
+        <v>11</v>
+      </c>
+      <c r="C201">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="202" spans="1:6">
+      <c r="A202">
+        <v>108</v>
+      </c>
+      <c r="B202" t="s">
+        <v>8</v>
+      </c>
+      <c r="C202">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="203" spans="1:6">
+      <c r="A203">
+        <v>113</v>
+      </c>
+      <c r="B203" t="s">
+        <v>8</v>
+      </c>
+      <c r="C203">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="204" spans="1:6">
+      <c r="A204">
+        <v>114</v>
+      </c>
+      <c r="B204" t="s">
+        <v>9</v>
+      </c>
+      <c r="C204">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="205" spans="1:6">
+      <c r="A205">
+        <v>117</v>
+      </c>
+      <c r="B205" t="s">
+        <v>11</v>
+      </c>
+      <c r="C205">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="206" spans="1:6">
+      <c r="A206">
+        <v>120</v>
+      </c>
+      <c r="B206" t="s">
+        <v>9</v>
+      </c>
+      <c r="C206">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="207" spans="1:6">
+      <c r="A207">
+        <v>127</v>
+      </c>
+      <c r="B207" t="s">
+        <v>10</v>
+      </c>
+      <c r="C207">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="208" spans="1:6">
+      <c r="A208">
+        <v>129</v>
+      </c>
+      <c r="B208" t="s">
+        <v>11</v>
+      </c>
+      <c r="C208">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="209" spans="1:3">
+      <c r="A209">
+        <v>130</v>
+      </c>
+      <c r="B209" t="s">
+        <v>10</v>
+      </c>
+      <c r="C209">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1"/>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B56:B59 B41:B50 B20:B32 B3:B17 B184:B190" xr:uid="{D8C212E3-0513-4E96-9660-7E8BB94F20D2}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B56:B59 B41:B50 B20:B32 B3:B17 B184:B190 B199:B209" xr:uid="{D8C212E3-0513-4E96-9660-7E8BB94F20D2}">
       <formula1>"A,B,C,D"</formula1>
     </dataValidation>
   </dataValidations>

--- a/l_r/2nd.xlsx
+++ b/l_r/2nd.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PycharmProjects\english\english-study\l_r\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6E9897F9-209E-40FB-9748-D91B30031C6E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{53005741-071E-42DE-BC05-5E52C49E6D4D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="930" yWindow="30" windowWidth="14880" windowHeight="15345" firstSheet="1" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="285" yWindow="45" windowWidth="14880" windowHeight="15345" firstSheet="1" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="summary" sheetId="3" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="340" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="344" uniqueCount="74">
   <si>
     <t>問題番号</t>
     <rPh sb="0" eb="2">
@@ -5423,7 +5423,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3C7A3EDD-6597-4754-A609-A225833ECC81}">
-  <dimension ref="A2:H209"/>
+  <dimension ref="A2:H213"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <sheetData>
     <row r="2" spans="1:4">
@@ -7845,6 +7845,53 @@
         <v>10</v>
       </c>
       <c r="C209">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="210" spans="1:3">
+      <c r="A210">
+        <v>135</v>
+      </c>
+      <c r="B210" t="s">
+        <v>10</v>
+      </c>
+      <c r="C210">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="211" spans="1:3">
+      <c r="A211">
+        <f>A210+1</f>
+        <v>136</v>
+      </c>
+      <c r="B211" t="s">
+        <v>9</v>
+      </c>
+      <c r="C211">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="212" spans="1:3">
+      <c r="A212">
+        <f t="shared" ref="A212:A213" si="9">A211+1</f>
+        <v>137</v>
+      </c>
+      <c r="B212" t="s">
+        <v>8</v>
+      </c>
+      <c r="C212">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="213" spans="1:3">
+      <c r="A213">
+        <f t="shared" si="9"/>
+        <v>138</v>
+      </c>
+      <c r="B213" t="s">
+        <v>11</v>
+      </c>
+      <c r="C213">
         <v>1</v>
       </c>
     </row>

--- a/l_r/2nd.xlsx
+++ b/l_r/2nd.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PycharmProjects\english\english-study\l_r\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{53005741-071E-42DE-BC05-5E52C49E6D4D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DB449803-FD94-47C1-B4EE-ABA77341F71D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="285" yWindow="45" windowWidth="14880" windowHeight="15345" firstSheet="1" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="344" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="352" uniqueCount="74">
   <si>
     <t>問題番号</t>
     <rPh sb="0" eb="2">
@@ -5423,7 +5423,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3C7A3EDD-6597-4754-A609-A225833ECC81}">
-  <dimension ref="A2:H213"/>
+  <dimension ref="A2:H221"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <sheetData>
     <row r="2" spans="1:4">
@@ -7873,7 +7873,7 @@
     </row>
     <row r="212" spans="1:3">
       <c r="A212">
-        <f t="shared" ref="A212:A213" si="9">A211+1</f>
+        <f t="shared" ref="A212:A221" si="9">A211+1</f>
         <v>137</v>
       </c>
       <c r="B212" t="s">
@@ -7892,6 +7892,102 @@
         <v>11</v>
       </c>
       <c r="C213">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="214" spans="1:3">
+      <c r="A214">
+        <f t="shared" si="9"/>
+        <v>139</v>
+      </c>
+      <c r="B214" t="s">
+        <v>11</v>
+      </c>
+      <c r="C214">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="215" spans="1:3">
+      <c r="A215">
+        <f t="shared" si="9"/>
+        <v>140</v>
+      </c>
+      <c r="B215" t="s">
+        <v>11</v>
+      </c>
+      <c r="C215">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="216" spans="1:3">
+      <c r="A216">
+        <f t="shared" si="9"/>
+        <v>141</v>
+      </c>
+      <c r="B216" t="s">
+        <v>9</v>
+      </c>
+      <c r="C216">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="217" spans="1:3">
+      <c r="A217">
+        <f t="shared" si="9"/>
+        <v>142</v>
+      </c>
+      <c r="B217" t="s">
+        <v>8</v>
+      </c>
+      <c r="C217">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="218" spans="1:3">
+      <c r="A218">
+        <f t="shared" si="9"/>
+        <v>143</v>
+      </c>
+      <c r="B218" t="s">
+        <v>9</v>
+      </c>
+      <c r="C218">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="219" spans="1:3">
+      <c r="A219">
+        <f t="shared" si="9"/>
+        <v>144</v>
+      </c>
+      <c r="B219" t="s">
+        <v>11</v>
+      </c>
+      <c r="C219">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="220" spans="1:3">
+      <c r="A220">
+        <f t="shared" si="9"/>
+        <v>145</v>
+      </c>
+      <c r="B220" t="s">
+        <v>11</v>
+      </c>
+      <c r="C220">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="221" spans="1:3">
+      <c r="A221">
+        <f t="shared" si="9"/>
+        <v>146</v>
+      </c>
+      <c r="B221" t="s">
+        <v>10</v>
+      </c>
+      <c r="C221">
         <v>1</v>
       </c>
     </row>

--- a/l_r/2nd.xlsx
+++ b/l_r/2nd.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PycharmProjects\english\english-study\l_r\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DB449803-FD94-47C1-B4EE-ABA77341F71D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D52D9230-1F28-49BA-B6A2-AB795EB03BFB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="285" yWindow="45" windowWidth="14880" windowHeight="15345" firstSheet="1" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="405" yWindow="525" windowWidth="21600" windowHeight="11295" firstSheet="1" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="summary" sheetId="3" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="352" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="356" uniqueCount="74">
   <si>
     <t>問題番号</t>
     <rPh sb="0" eb="2">
@@ -5423,7 +5423,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3C7A3EDD-6597-4754-A609-A225833ECC81}">
-  <dimension ref="A2:H221"/>
+  <dimension ref="A2:H225"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <sheetData>
     <row r="2" spans="1:4">
@@ -7988,6 +7988,50 @@
         <v>10</v>
       </c>
       <c r="C221">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="222" spans="1:3">
+      <c r="A222">
+        <v>147</v>
+      </c>
+      <c r="B222" t="s">
+        <v>8</v>
+      </c>
+      <c r="C222">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="223" spans="1:3">
+      <c r="A223">
+        <v>148</v>
+      </c>
+      <c r="B223" t="s">
+        <v>11</v>
+      </c>
+      <c r="C223">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="224" spans="1:3">
+      <c r="A224">
+        <v>149</v>
+      </c>
+      <c r="B224" t="s">
+        <v>10</v>
+      </c>
+      <c r="C224">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="225" spans="1:3">
+      <c r="A225">
+        <v>150</v>
+      </c>
+      <c r="B225" t="s">
+        <v>11</v>
+      </c>
+      <c r="C225">
         <v>1</v>
       </c>
     </row>

--- a/l_r/2nd.xlsx
+++ b/l_r/2nd.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PycharmProjects\english\english-study\l_r\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D52D9230-1F28-49BA-B6A2-AB795EB03BFB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9D9AA3AD-6D93-4CDB-95D8-89F94C48F5E9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="405" yWindow="525" windowWidth="21600" windowHeight="11295" firstSheet="1" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="16650" yWindow="0" windowWidth="21600" windowHeight="15585" firstSheet="1" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="summary" sheetId="3" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="356" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="359" uniqueCount="74">
   <si>
     <t>問題番号</t>
     <rPh sb="0" eb="2">
@@ -5423,7 +5423,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3C7A3EDD-6597-4754-A609-A225833ECC81}">
-  <dimension ref="A2:H225"/>
+  <dimension ref="A2:H228"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <sheetData>
     <row r="2" spans="1:4">
@@ -8032,6 +8032,39 @@
         <v>11</v>
       </c>
       <c r="C225">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="226" spans="1:3">
+      <c r="A226">
+        <v>155</v>
+      </c>
+      <c r="B226" t="s">
+        <v>10</v>
+      </c>
+      <c r="C226">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="227" spans="1:3">
+      <c r="A227">
+        <v>156</v>
+      </c>
+      <c r="B227" t="s">
+        <v>11</v>
+      </c>
+      <c r="C227">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="228" spans="1:3">
+      <c r="A228">
+        <v>157</v>
+      </c>
+      <c r="B228" t="s">
+        <v>11</v>
+      </c>
+      <c r="C228">
         <v>1</v>
       </c>
     </row>

--- a/l_r/2nd.xlsx
+++ b/l_r/2nd.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PycharmProjects\english\english-study\l_r\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9D9AA3AD-6D93-4CDB-95D8-89F94C48F5E9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{19585290-ECF3-4A64-9BE2-8B50DBBC452D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="16650" yWindow="0" windowWidth="21600" windowHeight="15585" firstSheet="1" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="165" yWindow="0" windowWidth="15450" windowHeight="15585" firstSheet="1" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="summary" sheetId="3" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="359" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="362" uniqueCount="74">
   <si>
     <t>問題番号</t>
     <rPh sb="0" eb="2">
@@ -5423,7 +5423,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3C7A3EDD-6597-4754-A609-A225833ECC81}">
-  <dimension ref="A2:H228"/>
+  <dimension ref="A2:H231"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <sheetData>
     <row r="2" spans="1:4">
@@ -8065,6 +8065,39 @@
         <v>11</v>
       </c>
       <c r="C228">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="229" spans="1:3">
+      <c r="A229">
+        <v>158</v>
+      </c>
+      <c r="B229" t="s">
+        <v>11</v>
+      </c>
+      <c r="C229">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="230" spans="1:3">
+      <c r="A230">
+        <v>159</v>
+      </c>
+      <c r="B230" t="s">
+        <v>8</v>
+      </c>
+      <c r="C230">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="231" spans="1:3">
+      <c r="A231">
+        <v>160</v>
+      </c>
+      <c r="B231" t="s">
+        <v>9</v>
+      </c>
+      <c r="C231">
         <v>1</v>
       </c>
     </row>

--- a/l_r/2nd.xlsx
+++ b/l_r/2nd.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PycharmProjects\english\english-study\l_r\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{19585290-ECF3-4A64-9BE2-8B50DBBC452D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{27FBC568-150A-4498-8F9B-D4187B72832C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="165" yWindow="0" windowWidth="15450" windowHeight="15585" firstSheet="1" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="5085" yWindow="0" windowWidth="11445" windowHeight="15585" firstSheet="1" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="summary" sheetId="3" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="362" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="366" uniqueCount="74">
   <si>
     <t>問題番号</t>
     <rPh sb="0" eb="2">
@@ -5423,7 +5423,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3C7A3EDD-6597-4754-A609-A225833ECC81}">
-  <dimension ref="A2:H231"/>
+  <dimension ref="A2:H235"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <sheetData>
     <row r="2" spans="1:4">
@@ -8098,6 +8098,53 @@
         <v>9</v>
       </c>
       <c r="C231">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="232" spans="1:3">
+      <c r="A232">
+        <v>164</v>
+      </c>
+      <c r="B232" t="s">
+        <v>10</v>
+      </c>
+      <c r="C232">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="233" spans="1:3">
+      <c r="A233">
+        <f>A232+1</f>
+        <v>165</v>
+      </c>
+      <c r="B233" t="s">
+        <v>10</v>
+      </c>
+      <c r="C233">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="234" spans="1:3">
+      <c r="A234">
+        <f t="shared" ref="A234:A235" si="10">A233+1</f>
+        <v>166</v>
+      </c>
+      <c r="B234" t="s">
+        <v>9</v>
+      </c>
+      <c r="C234">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="235" spans="1:3">
+      <c r="A235">
+        <f t="shared" si="10"/>
+        <v>167</v>
+      </c>
+      <c r="B235" t="s">
+        <v>10</v>
+      </c>
+      <c r="C235">
         <v>1</v>
       </c>
     </row>

--- a/l_r/2nd.xlsx
+++ b/l_r/2nd.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PycharmProjects\english\english-study\l_r\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{27FBC568-150A-4498-8F9B-D4187B72832C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AA22F9D7-0636-40AB-8ADA-AF811C9474EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5085" yWindow="0" windowWidth="11445" windowHeight="15585" firstSheet="1" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="14205" yWindow="0" windowWidth="13260" windowHeight="15585" firstSheet="1" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="summary" sheetId="3" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="366" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="370" uniqueCount="74">
   <si>
     <t>問題番号</t>
     <rPh sb="0" eb="2">
@@ -5423,7 +5423,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3C7A3EDD-6597-4754-A609-A225833ECC81}">
-  <dimension ref="A2:H235"/>
+  <dimension ref="A2:H239"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <sheetData>
     <row r="2" spans="1:4">
@@ -8126,7 +8126,7 @@
     </row>
     <row r="234" spans="1:3">
       <c r="A234">
-        <f t="shared" ref="A234:A235" si="10">A233+1</f>
+        <f t="shared" ref="A234:A239" si="10">A233+1</f>
         <v>166</v>
       </c>
       <c r="B234" t="s">
@@ -8145,6 +8145,53 @@
         <v>10</v>
       </c>
       <c r="C235">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="236" spans="1:3">
+      <c r="A236">
+        <v>168</v>
+      </c>
+      <c r="B236" t="s">
+        <v>9</v>
+      </c>
+      <c r="C236">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="237" spans="1:3">
+      <c r="A237">
+        <f t="shared" si="10"/>
+        <v>169</v>
+      </c>
+      <c r="B237" t="s">
+        <v>9</v>
+      </c>
+      <c r="C237">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="238" spans="1:3">
+      <c r="A238">
+        <f t="shared" si="10"/>
+        <v>170</v>
+      </c>
+      <c r="B238" t="s">
+        <v>9</v>
+      </c>
+      <c r="C238">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="239" spans="1:3">
+      <c r="A239">
+        <f t="shared" si="10"/>
+        <v>171</v>
+      </c>
+      <c r="B239" t="s">
+        <v>10</v>
+      </c>
+      <c r="C239">
         <v>1</v>
       </c>
     </row>

--- a/l_r/2nd.xlsx
+++ b/l_r/2nd.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PycharmProjects\english\english-study\l_r\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AA22F9D7-0636-40AB-8ADA-AF811C9474EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{92C45128-DBE8-4F6E-B3A7-DA7C227C41DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="14205" yWindow="0" windowWidth="13260" windowHeight="15585" firstSheet="1" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1425" yWindow="0" windowWidth="13260" windowHeight="15585" firstSheet="1" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="summary" sheetId="3" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="370" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="374" uniqueCount="74">
   <si>
     <t>問題番号</t>
     <rPh sb="0" eb="2">
@@ -5423,7 +5423,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3C7A3EDD-6597-4754-A609-A225833ECC81}">
-  <dimension ref="A2:H239"/>
+  <dimension ref="A2:H243"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <sheetData>
     <row r="2" spans="1:4">
@@ -8126,7 +8126,7 @@
     </row>
     <row r="234" spans="1:3">
       <c r="A234">
-        <f t="shared" ref="A234:A239" si="10">A233+1</f>
+        <f t="shared" ref="A234:A243" si="10">A233+1</f>
         <v>166</v>
       </c>
       <c r="B234" t="s">
@@ -8192,6 +8192,53 @@
         <v>10</v>
       </c>
       <c r="C239">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="240" spans="1:3">
+      <c r="A240">
+        <v>172</v>
+      </c>
+      <c r="B240" t="s">
+        <v>8</v>
+      </c>
+      <c r="C240">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="241" spans="1:3">
+      <c r="A241">
+        <f t="shared" si="10"/>
+        <v>173</v>
+      </c>
+      <c r="B241" t="s">
+        <v>8</v>
+      </c>
+      <c r="C241">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="242" spans="1:3">
+      <c r="A242">
+        <f t="shared" si="10"/>
+        <v>174</v>
+      </c>
+      <c r="B242" t="s">
+        <v>9</v>
+      </c>
+      <c r="C242">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="243" spans="1:3">
+      <c r="A243">
+        <f t="shared" si="10"/>
+        <v>175</v>
+      </c>
+      <c r="B243" t="s">
+        <v>10</v>
+      </c>
+      <c r="C243">
         <v>1</v>
       </c>
     </row>

--- a/l_r/2nd.xlsx
+++ b/l_r/2nd.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PycharmProjects\english\english-study\l_r\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{92C45128-DBE8-4F6E-B3A7-DA7C227C41DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B1A7ABE1-9C01-4B5B-8AF7-AC383DF4E48E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1425" yWindow="0" windowWidth="13260" windowHeight="15585" firstSheet="1" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="10605" yWindow="0" windowWidth="15855" windowHeight="15585" firstSheet="1" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="summary" sheetId="3" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="374" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="379" uniqueCount="74">
   <si>
     <t>問題番号</t>
     <rPh sb="0" eb="2">
@@ -5423,7 +5423,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3C7A3EDD-6597-4754-A609-A225833ECC81}">
-  <dimension ref="A2:H243"/>
+  <dimension ref="A2:H248"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <sheetData>
     <row r="2" spans="1:4">
@@ -8126,7 +8126,7 @@
     </row>
     <row r="234" spans="1:3">
       <c r="A234">
-        <f t="shared" ref="A234:A243" si="10">A233+1</f>
+        <f t="shared" ref="A234:A248" si="10">A233+1</f>
         <v>166</v>
       </c>
       <c r="B234" t="s">
@@ -8239,6 +8239,66 @@
         <v>10</v>
       </c>
       <c r="C243">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="244" spans="1:3">
+      <c r="A244">
+        <f t="shared" si="10"/>
+        <v>176</v>
+      </c>
+      <c r="B244" t="s">
+        <v>11</v>
+      </c>
+      <c r="C244">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="245" spans="1:3">
+      <c r="A245">
+        <f t="shared" si="10"/>
+        <v>177</v>
+      </c>
+      <c r="B245" t="s">
+        <v>10</v>
+      </c>
+      <c r="C245">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="246" spans="1:3">
+      <c r="A246">
+        <f t="shared" si="10"/>
+        <v>178</v>
+      </c>
+      <c r="B246" t="s">
+        <v>9</v>
+      </c>
+      <c r="C246">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="247" spans="1:3">
+      <c r="A247">
+        <f t="shared" si="10"/>
+        <v>179</v>
+      </c>
+      <c r="B247" t="s">
+        <v>11</v>
+      </c>
+      <c r="C247">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="248" spans="1:3">
+      <c r="A248">
+        <f t="shared" si="10"/>
+        <v>180</v>
+      </c>
+      <c r="B248" t="s">
+        <v>10</v>
+      </c>
+      <c r="C248">
         <v>1</v>
       </c>
     </row>

--- a/l_r/2nd.xlsx
+++ b/l_r/2nd.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PycharmProjects\english\english-study\l_r\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B1A7ABE1-9C01-4B5B-8AF7-AC383DF4E48E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CC837F98-4B9E-4BA5-A2A5-EB0D985BBEA1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="10605" yWindow="0" windowWidth="15855" windowHeight="15585" firstSheet="1" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="600" yWindow="0" windowWidth="13260" windowHeight="15585" firstSheet="1" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="summary" sheetId="3" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="379" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="384" uniqueCount="74">
   <si>
     <t>問題番号</t>
     <rPh sb="0" eb="2">
@@ -5423,7 +5423,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3C7A3EDD-6597-4754-A609-A225833ECC81}">
-  <dimension ref="A2:H248"/>
+  <dimension ref="A2:H253"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <sheetData>
     <row r="2" spans="1:4">
@@ -8126,7 +8126,7 @@
     </row>
     <row r="234" spans="1:3">
       <c r="A234">
-        <f t="shared" ref="A234:A248" si="10">A233+1</f>
+        <f t="shared" ref="A234:A253" si="10">A233+1</f>
         <v>166</v>
       </c>
       <c r="B234" t="s">
@@ -8299,6 +8299,66 @@
         <v>10</v>
       </c>
       <c r="C248">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="249" spans="1:3">
+      <c r="A249">
+        <f t="shared" si="10"/>
+        <v>181</v>
+      </c>
+      <c r="B249" t="s">
+        <v>9</v>
+      </c>
+      <c r="C249">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="250" spans="1:3">
+      <c r="A250">
+        <f t="shared" si="10"/>
+        <v>182</v>
+      </c>
+      <c r="B250" t="s">
+        <v>11</v>
+      </c>
+      <c r="C250">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="251" spans="1:3">
+      <c r="A251">
+        <f t="shared" si="10"/>
+        <v>183</v>
+      </c>
+      <c r="B251" t="s">
+        <v>8</v>
+      </c>
+      <c r="C251">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="252" spans="1:3">
+      <c r="A252">
+        <f t="shared" si="10"/>
+        <v>184</v>
+      </c>
+      <c r="B252" t="s">
+        <v>11</v>
+      </c>
+      <c r="C252">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="253" spans="1:3">
+      <c r="A253">
+        <f t="shared" si="10"/>
+        <v>185</v>
+      </c>
+      <c r="B253" t="s">
+        <v>10</v>
+      </c>
+      <c r="C253">
         <v>1</v>
       </c>
     </row>

--- a/l_r/2nd.xlsx
+++ b/l_r/2nd.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PycharmProjects\english\english-study\l_r\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CC837F98-4B9E-4BA5-A2A5-EB0D985BBEA1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{98FED299-7DB2-40E0-814E-287E44CC7B96}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="600" yWindow="0" windowWidth="13260" windowHeight="15585" firstSheet="1" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="600" yWindow="0" windowWidth="14850" windowHeight="15585" firstSheet="1" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="summary" sheetId="3" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="384" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="389" uniqueCount="74">
   <si>
     <t>問題番号</t>
     <rPh sb="0" eb="2">
@@ -5423,7 +5423,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3C7A3EDD-6597-4754-A609-A225833ECC81}">
-  <dimension ref="A2:H253"/>
+  <dimension ref="A2:H258"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <sheetData>
     <row r="2" spans="1:4">
@@ -8126,7 +8126,7 @@
     </row>
     <row r="234" spans="1:3">
       <c r="A234">
-        <f t="shared" ref="A234:A253" si="10">A233+1</f>
+        <f t="shared" ref="A234:A258" si="10">A233+1</f>
         <v>166</v>
       </c>
       <c r="B234" t="s">
@@ -8359,6 +8359,66 @@
         <v>10</v>
       </c>
       <c r="C253">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="254" spans="1:3">
+      <c r="A254">
+        <f t="shared" si="10"/>
+        <v>186</v>
+      </c>
+      <c r="B254" t="s">
+        <v>10</v>
+      </c>
+      <c r="C254">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="255" spans="1:3">
+      <c r="A255">
+        <f t="shared" si="10"/>
+        <v>187</v>
+      </c>
+      <c r="B255" t="s">
+        <v>11</v>
+      </c>
+      <c r="C255">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="256" spans="1:3">
+      <c r="A256">
+        <f t="shared" si="10"/>
+        <v>188</v>
+      </c>
+      <c r="B256" t="s">
+        <v>8</v>
+      </c>
+      <c r="C256">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="257" spans="1:3">
+      <c r="A257">
+        <f t="shared" si="10"/>
+        <v>189</v>
+      </c>
+      <c r="B257" t="s">
+        <v>10</v>
+      </c>
+      <c r="C257">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="258" spans="1:3">
+      <c r="A258">
+        <f t="shared" si="10"/>
+        <v>190</v>
+      </c>
+      <c r="B258" t="s">
+        <v>9</v>
+      </c>
+      <c r="C258">
         <v>1</v>
       </c>
     </row>

--- a/l_r/2nd.xlsx
+++ b/l_r/2nd.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PycharmProjects\english\english-study\l_r\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{98FED299-7DB2-40E0-814E-287E44CC7B96}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B9EC3333-BF14-4ADD-8780-080E15610D94}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="600" yWindow="0" windowWidth="14850" windowHeight="15585" firstSheet="1" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="600" yWindow="900" windowWidth="14850" windowHeight="13710" firstSheet="1" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="summary" sheetId="3" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="389" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="394" uniqueCount="74">
   <si>
     <t>問題番号</t>
     <rPh sb="0" eb="2">
@@ -5423,7 +5423,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3C7A3EDD-6597-4754-A609-A225833ECC81}">
-  <dimension ref="A2:H258"/>
+  <dimension ref="A2:H263"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <sheetData>
     <row r="2" spans="1:4">
@@ -8126,7 +8126,7 @@
     </row>
     <row r="234" spans="1:3">
       <c r="A234">
-        <f t="shared" ref="A234:A258" si="10">A233+1</f>
+        <f t="shared" ref="A234:A263" si="10">A233+1</f>
         <v>166</v>
       </c>
       <c r="B234" t="s">
@@ -8419,6 +8419,66 @@
         <v>9</v>
       </c>
       <c r="C258">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="259" spans="1:3">
+      <c r="A259">
+        <f t="shared" si="10"/>
+        <v>191</v>
+      </c>
+      <c r="B259" t="s">
+        <v>11</v>
+      </c>
+      <c r="C259">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="260" spans="1:3">
+      <c r="A260">
+        <f t="shared" si="10"/>
+        <v>192</v>
+      </c>
+      <c r="B260" t="s">
+        <v>10</v>
+      </c>
+      <c r="C260">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="261" spans="1:3">
+      <c r="A261">
+        <f t="shared" si="10"/>
+        <v>193</v>
+      </c>
+      <c r="B261" t="s">
+        <v>9</v>
+      </c>
+      <c r="C261">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="262" spans="1:3">
+      <c r="A262">
+        <f t="shared" si="10"/>
+        <v>194</v>
+      </c>
+      <c r="B262" t="s">
+        <v>11</v>
+      </c>
+      <c r="C262">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="263" spans="1:3">
+      <c r="A263">
+        <f t="shared" si="10"/>
+        <v>195</v>
+      </c>
+      <c r="B263" t="s">
+        <v>8</v>
+      </c>
+      <c r="C263">
         <v>1</v>
       </c>
     </row>

--- a/l_r/2nd.xlsx
+++ b/l_r/2nd.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PycharmProjects\english\english-study\l_r\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B9EC3333-BF14-4ADD-8780-080E15610D94}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{23BE156E-2703-4ABA-8EFD-9E1913FA093A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="600" yWindow="900" windowWidth="14850" windowHeight="13710" firstSheet="1" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-135" yWindow="615" windowWidth="14850" windowHeight="13710" firstSheet="1" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="summary" sheetId="3" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="394" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="399" uniqueCount="74">
   <si>
     <t>問題番号</t>
     <rPh sb="0" eb="2">
@@ -5423,7 +5423,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3C7A3EDD-6597-4754-A609-A225833ECC81}">
-  <dimension ref="A2:H263"/>
+  <dimension ref="A2:H268"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <sheetData>
     <row r="2" spans="1:4">
@@ -8126,7 +8126,7 @@
     </row>
     <row r="234" spans="1:3">
       <c r="A234">
-        <f t="shared" ref="A234:A263" si="10">A233+1</f>
+        <f t="shared" ref="A234:A268" si="10">A233+1</f>
         <v>166</v>
       </c>
       <c r="B234" t="s">
@@ -8479,6 +8479,66 @@
         <v>8</v>
       </c>
       <c r="C263">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="264" spans="1:3">
+      <c r="A264">
+        <f t="shared" si="10"/>
+        <v>196</v>
+      </c>
+      <c r="B264" t="s">
+        <v>8</v>
+      </c>
+      <c r="C264">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="265" spans="1:3">
+      <c r="A265">
+        <f t="shared" si="10"/>
+        <v>197</v>
+      </c>
+      <c r="B265" t="s">
+        <v>9</v>
+      </c>
+      <c r="C265">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="266" spans="1:3">
+      <c r="A266">
+        <f t="shared" si="10"/>
+        <v>198</v>
+      </c>
+      <c r="B266" t="s">
+        <v>8</v>
+      </c>
+      <c r="C266">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="267" spans="1:3">
+      <c r="A267">
+        <f t="shared" si="10"/>
+        <v>199</v>
+      </c>
+      <c r="B267" t="s">
+        <v>11</v>
+      </c>
+      <c r="C267">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="268" spans="1:3">
+      <c r="A268">
+        <f t="shared" si="10"/>
+        <v>200</v>
+      </c>
+      <c r="B268" t="s">
+        <v>9</v>
+      </c>
+      <c r="C268">
         <v>1</v>
       </c>
     </row>

--- a/l_r/2nd.xlsx
+++ b/l_r/2nd.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PycharmProjects\english\english-study\l_r\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{23BE156E-2703-4ABA-8EFD-9E1913FA093A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{357AE396-09F5-4B9F-8736-549DA5E8D943}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-135" yWindow="615" windowWidth="14850" windowHeight="13710" firstSheet="1" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="1" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="summary" sheetId="3" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="399" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="409" uniqueCount="74">
   <si>
     <t>問題番号</t>
     <rPh sb="0" eb="2">
@@ -5423,7 +5423,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3C7A3EDD-6597-4754-A609-A225833ECC81}">
-  <dimension ref="A2:H268"/>
+  <dimension ref="A2:H278"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <sheetData>
     <row r="2" spans="1:4">
@@ -8126,7 +8126,7 @@
     </row>
     <row r="234" spans="1:3">
       <c r="A234">
-        <f t="shared" ref="A234:A268" si="10">A233+1</f>
+        <f t="shared" ref="A234:A279" si="10">A233+1</f>
         <v>166</v>
       </c>
       <c r="B234" t="s">
@@ -8539,6 +8539,125 @@
         <v>9</v>
       </c>
       <c r="C268">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="269" spans="1:3">
+      <c r="A269">
+        <v>101</v>
+      </c>
+      <c r="B269" t="s">
+        <v>9</v>
+      </c>
+      <c r="C269">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="270" spans="1:3">
+      <c r="A270">
+        <f t="shared" si="10"/>
+        <v>102</v>
+      </c>
+      <c r="B270" t="s">
+        <v>8</v>
+      </c>
+      <c r="C270">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="271" spans="1:3">
+      <c r="A271">
+        <f t="shared" si="10"/>
+        <v>103</v>
+      </c>
+      <c r="B271" t="s">
+        <v>11</v>
+      </c>
+      <c r="C271">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="272" spans="1:3">
+      <c r="A272">
+        <f t="shared" si="10"/>
+        <v>104</v>
+      </c>
+      <c r="B272" t="s">
+        <v>8</v>
+      </c>
+      <c r="C272">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="273" spans="1:3">
+      <c r="A273">
+        <f t="shared" si="10"/>
+        <v>105</v>
+      </c>
+      <c r="B273" t="s">
+        <v>9</v>
+      </c>
+      <c r="C273">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="274" spans="1:3">
+      <c r="A274">
+        <f t="shared" si="10"/>
+        <v>106</v>
+      </c>
+      <c r="B274" t="s">
+        <v>9</v>
+      </c>
+      <c r="C274">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="275" spans="1:3">
+      <c r="A275">
+        <f t="shared" si="10"/>
+        <v>107</v>
+      </c>
+      <c r="B275" t="s">
+        <v>11</v>
+      </c>
+      <c r="C275">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="276" spans="1:3">
+      <c r="A276">
+        <f t="shared" si="10"/>
+        <v>108</v>
+      </c>
+      <c r="B276" t="s">
+        <v>8</v>
+      </c>
+      <c r="C276">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="277" spans="1:3">
+      <c r="A277">
+        <f t="shared" si="10"/>
+        <v>109</v>
+      </c>
+      <c r="B277" t="s">
+        <v>10</v>
+      </c>
+      <c r="C277">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="278" spans="1:3">
+      <c r="A278">
+        <f t="shared" si="10"/>
+        <v>110</v>
+      </c>
+      <c r="B278" t="s">
+        <v>9</v>
+      </c>
+      <c r="C278">
         <v>1</v>
       </c>
     </row>

--- a/l_r/2nd.xlsx
+++ b/l_r/2nd.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PycharmProjects\english\english-study\l_r\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{357AE396-09F5-4B9F-8736-549DA5E8D943}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{88B99EA7-31B9-4E4D-BCCB-415AB8031618}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="1" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="105" yWindow="0" windowWidth="13830" windowHeight="15585" firstSheet="1" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="summary" sheetId="3" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="409" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="419" uniqueCount="74">
   <si>
     <t>問題番号</t>
     <rPh sb="0" eb="2">
@@ -5423,7 +5423,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3C7A3EDD-6597-4754-A609-A225833ECC81}">
-  <dimension ref="A2:H278"/>
+  <dimension ref="A2:H288"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <sheetData>
     <row r="2" spans="1:4">
@@ -8126,7 +8126,7 @@
     </row>
     <row r="234" spans="1:3">
       <c r="A234">
-        <f t="shared" ref="A234:A279" si="10">A233+1</f>
+        <f t="shared" ref="A234:A297" si="10">A233+1</f>
         <v>166</v>
       </c>
       <c r="B234" t="s">
@@ -8658,6 +8658,126 @@
         <v>9</v>
       </c>
       <c r="C278">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="279" spans="1:3">
+      <c r="A279">
+        <f t="shared" si="10"/>
+        <v>111</v>
+      </c>
+      <c r="B279" t="s">
+        <v>10</v>
+      </c>
+      <c r="C279">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="280" spans="1:3">
+      <c r="A280">
+        <f t="shared" si="10"/>
+        <v>112</v>
+      </c>
+      <c r="B280" t="s">
+        <v>10</v>
+      </c>
+      <c r="C280">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="281" spans="1:3">
+      <c r="A281">
+        <f t="shared" si="10"/>
+        <v>113</v>
+      </c>
+      <c r="B281" t="s">
+        <v>8</v>
+      </c>
+      <c r="C281">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="282" spans="1:3">
+      <c r="A282">
+        <f t="shared" si="10"/>
+        <v>114</v>
+      </c>
+      <c r="B282" t="s">
+        <v>8</v>
+      </c>
+      <c r="C282">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="283" spans="1:3">
+      <c r="A283">
+        <f t="shared" si="10"/>
+        <v>115</v>
+      </c>
+      <c r="B283" t="s">
+        <v>11</v>
+      </c>
+      <c r="C283">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="284" spans="1:3">
+      <c r="A284">
+        <f t="shared" si="10"/>
+        <v>116</v>
+      </c>
+      <c r="B284" t="s">
+        <v>9</v>
+      </c>
+      <c r="C284">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="285" spans="1:3">
+      <c r="A285">
+        <f t="shared" si="10"/>
+        <v>117</v>
+      </c>
+      <c r="B285" t="s">
+        <v>8</v>
+      </c>
+      <c r="C285">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="286" spans="1:3">
+      <c r="A286">
+        <f t="shared" si="10"/>
+        <v>118</v>
+      </c>
+      <c r="B286" t="s">
+        <v>10</v>
+      </c>
+      <c r="C286">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="287" spans="1:3">
+      <c r="A287">
+        <f t="shared" si="10"/>
+        <v>119</v>
+      </c>
+      <c r="B287" t="s">
+        <v>11</v>
+      </c>
+      <c r="C287">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="288" spans="1:3">
+      <c r="A288">
+        <f t="shared" si="10"/>
+        <v>120</v>
+      </c>
+      <c r="B288" t="s">
+        <v>9</v>
+      </c>
+      <c r="C288">
         <v>1</v>
       </c>
     </row>

--- a/l_r/2nd.xlsx
+++ b/l_r/2nd.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PycharmProjects\english\english-study\l_r\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{88B99EA7-31B9-4E4D-BCCB-415AB8031618}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A129CD9D-56F0-441D-9148-0EE8F0951B64}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="105" yWindow="0" windowWidth="13830" windowHeight="15585" firstSheet="1" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="17565" yWindow="345" windowWidth="14295" windowHeight="13710" firstSheet="1" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="summary" sheetId="3" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="419" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="429" uniqueCount="74">
   <si>
     <t>問題番号</t>
     <rPh sb="0" eb="2">
@@ -5423,7 +5423,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3C7A3EDD-6597-4754-A609-A225833ECC81}">
-  <dimension ref="A2:H288"/>
+  <dimension ref="A2:H298"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <sheetData>
     <row r="2" spans="1:4">
@@ -8779,6 +8779,126 @@
       </c>
       <c r="C288">
         <v>1</v>
+      </c>
+    </row>
+    <row r="289" spans="1:3">
+      <c r="A289">
+        <f t="shared" si="10"/>
+        <v>121</v>
+      </c>
+      <c r="B289" t="s">
+        <v>10</v>
+      </c>
+      <c r="C289">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="290" spans="1:3">
+      <c r="A290">
+        <f t="shared" si="10"/>
+        <v>122</v>
+      </c>
+      <c r="B290" t="s">
+        <v>9</v>
+      </c>
+      <c r="C290">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="291" spans="1:3">
+      <c r="A291">
+        <f t="shared" si="10"/>
+        <v>123</v>
+      </c>
+      <c r="B291" t="s">
+        <v>10</v>
+      </c>
+      <c r="C291">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="292" spans="1:3">
+      <c r="A292">
+        <f t="shared" si="10"/>
+        <v>124</v>
+      </c>
+      <c r="B292" t="s">
+        <v>8</v>
+      </c>
+      <c r="C292">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="293" spans="1:3">
+      <c r="A293">
+        <f t="shared" si="10"/>
+        <v>125</v>
+      </c>
+      <c r="B293" t="s">
+        <v>8</v>
+      </c>
+      <c r="C293">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="294" spans="1:3">
+      <c r="A294">
+        <f t="shared" si="10"/>
+        <v>126</v>
+      </c>
+      <c r="B294" t="s">
+        <v>10</v>
+      </c>
+      <c r="C294">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="295" spans="1:3">
+      <c r="A295">
+        <f t="shared" si="10"/>
+        <v>127</v>
+      </c>
+      <c r="B295" t="s">
+        <v>10</v>
+      </c>
+      <c r="C295">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="296" spans="1:3">
+      <c r="A296">
+        <f t="shared" si="10"/>
+        <v>128</v>
+      </c>
+      <c r="B296" t="s">
+        <v>9</v>
+      </c>
+      <c r="C296">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="297" spans="1:3">
+      <c r="A297">
+        <f t="shared" si="10"/>
+        <v>129</v>
+      </c>
+      <c r="B297" t="s">
+        <v>8</v>
+      </c>
+      <c r="C297">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="298" spans="1:3">
+      <c r="A298">
+        <f t="shared" ref="A298" si="11">A297+1</f>
+        <v>130</v>
+      </c>
+      <c r="B298" t="s">
+        <v>9</v>
+      </c>
+      <c r="C298">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/l_r/2nd.xlsx
+++ b/l_r/2nd.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PycharmProjects\english\english-study\l_r\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A129CD9D-56F0-441D-9148-0EE8F0951B64}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{564D9FF5-0E2F-4DE4-B1AD-65AAD4EA6E32}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="17565" yWindow="345" windowWidth="14295" windowHeight="13710" firstSheet="1" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="630" yWindow="540" windowWidth="14295" windowHeight="13710" firstSheet="1" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="summary" sheetId="3" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="429" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="437" uniqueCount="74">
   <si>
     <t>問題番号</t>
     <rPh sb="0" eb="2">
@@ -5423,7 +5423,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3C7A3EDD-6597-4754-A609-A225833ECC81}">
-  <dimension ref="A2:H298"/>
+  <dimension ref="A2:H306"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <sheetData>
     <row r="2" spans="1:4">
@@ -8891,7 +8891,7 @@
     </row>
     <row r="298" spans="1:3">
       <c r="A298">
-        <f t="shared" ref="A298" si="11">A297+1</f>
+        <f t="shared" ref="A298:A308" si="11">A297+1</f>
         <v>130</v>
       </c>
       <c r="B298" t="s">
@@ -8899,6 +8899,102 @@
       </c>
       <c r="C298">
         <v>0</v>
+      </c>
+    </row>
+    <row r="299" spans="1:3">
+      <c r="A299">
+        <f t="shared" si="11"/>
+        <v>131</v>
+      </c>
+      <c r="B299" t="s">
+        <v>8</v>
+      </c>
+      <c r="C299">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="300" spans="1:3">
+      <c r="A300">
+        <f t="shared" si="11"/>
+        <v>132</v>
+      </c>
+      <c r="B300" t="s">
+        <v>11</v>
+      </c>
+      <c r="C300">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="301" spans="1:3">
+      <c r="A301">
+        <f t="shared" si="11"/>
+        <v>133</v>
+      </c>
+      <c r="B301" t="s">
+        <v>9</v>
+      </c>
+      <c r="C301">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="302" spans="1:3">
+      <c r="A302">
+        <f t="shared" si="11"/>
+        <v>134</v>
+      </c>
+      <c r="B302" t="s">
+        <v>10</v>
+      </c>
+      <c r="C302">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="303" spans="1:3">
+      <c r="A303">
+        <f t="shared" si="11"/>
+        <v>135</v>
+      </c>
+      <c r="B303" t="s">
+        <v>10</v>
+      </c>
+      <c r="C303">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="304" spans="1:3">
+      <c r="A304">
+        <f t="shared" si="11"/>
+        <v>136</v>
+      </c>
+      <c r="B304" t="s">
+        <v>9</v>
+      </c>
+      <c r="C304">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="305" spans="1:3">
+      <c r="A305">
+        <f t="shared" si="11"/>
+        <v>137</v>
+      </c>
+      <c r="B305" t="s">
+        <v>8</v>
+      </c>
+      <c r="C305">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="306" spans="1:3">
+      <c r="A306">
+        <f t="shared" si="11"/>
+        <v>138</v>
+      </c>
+      <c r="B306" t="s">
+        <v>11</v>
+      </c>
+      <c r="C306">
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/l_r/2nd.xlsx
+++ b/l_r/2nd.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PycharmProjects\english\english-study\l_r\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{564D9FF5-0E2F-4DE4-B1AD-65AAD4EA6E32}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{13E93EDA-375F-4183-9F72-A63DC4E81C73}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="630" yWindow="540" windowWidth="14295" windowHeight="13710" firstSheet="1" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="195" yWindow="0" windowWidth="14295" windowHeight="13710" firstSheet="1" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="summary" sheetId="3" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="437" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="445" uniqueCount="74">
   <si>
     <t>問題番号</t>
     <rPh sb="0" eb="2">
@@ -5423,7 +5423,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3C7A3EDD-6597-4754-A609-A225833ECC81}">
-  <dimension ref="A2:H306"/>
+  <dimension ref="A2:H314"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <sheetData>
     <row r="2" spans="1:4">
@@ -8891,7 +8891,7 @@
     </row>
     <row r="298" spans="1:3">
       <c r="A298">
-        <f t="shared" ref="A298:A308" si="11">A297+1</f>
+        <f t="shared" ref="A298:A319" si="11">A297+1</f>
         <v>130</v>
       </c>
       <c r="B298" t="s">
@@ -8994,6 +8994,102 @@
         <v>11</v>
       </c>
       <c r="C306">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="307" spans="1:3">
+      <c r="A307">
+        <f t="shared" si="11"/>
+        <v>139</v>
+      </c>
+      <c r="B307" t="s">
+        <v>11</v>
+      </c>
+      <c r="C307">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="308" spans="1:3">
+      <c r="A308">
+        <f t="shared" si="11"/>
+        <v>140</v>
+      </c>
+      <c r="B308" t="s">
+        <v>10</v>
+      </c>
+      <c r="C308">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="309" spans="1:3">
+      <c r="A309">
+        <f t="shared" si="11"/>
+        <v>141</v>
+      </c>
+      <c r="B309" t="s">
+        <v>9</v>
+      </c>
+      <c r="C309">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="310" spans="1:3">
+      <c r="A310">
+        <f t="shared" si="11"/>
+        <v>142</v>
+      </c>
+      <c r="B310" t="s">
+        <v>8</v>
+      </c>
+      <c r="C310">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="311" spans="1:3">
+      <c r="A311">
+        <f t="shared" si="11"/>
+        <v>143</v>
+      </c>
+      <c r="B311" t="s">
+        <v>9</v>
+      </c>
+      <c r="C311">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="312" spans="1:3">
+      <c r="A312">
+        <f t="shared" si="11"/>
+        <v>144</v>
+      </c>
+      <c r="B312" t="s">
+        <v>11</v>
+      </c>
+      <c r="C312">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="313" spans="1:3">
+      <c r="A313">
+        <f t="shared" si="11"/>
+        <v>145</v>
+      </c>
+      <c r="B313" t="s">
+        <v>11</v>
+      </c>
+      <c r="C313">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="314" spans="1:3">
+      <c r="A314">
+        <f t="shared" si="11"/>
+        <v>146</v>
+      </c>
+      <c r="B314" t="s">
+        <v>10</v>
+      </c>
+      <c r="C314">
         <v>1</v>
       </c>
     </row>

--- a/l_r/2nd.xlsx
+++ b/l_r/2nd.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30228"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PycharmProjects\english\english-study\l_r\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{13E93EDA-375F-4183-9F72-A63DC4E81C73}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3AA9D7F5-93B4-4878-8C06-8568C25D85F7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="195" yWindow="0" windowWidth="14295" windowHeight="13710" firstSheet="1" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="270" yWindow="60" windowWidth="15330" windowHeight="14310" firstSheet="1" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="summary" sheetId="3" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="445" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="453" uniqueCount="74">
   <si>
     <t>問題番号</t>
     <rPh sb="0" eb="2">
@@ -5423,7 +5423,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3C7A3EDD-6597-4754-A609-A225833ECC81}">
-  <dimension ref="A2:H314"/>
+  <dimension ref="A2:H322"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <sheetData>
     <row r="2" spans="1:4">
@@ -8891,7 +8891,7 @@
     </row>
     <row r="298" spans="1:3">
       <c r="A298">
-        <f t="shared" ref="A298:A319" si="11">A297+1</f>
+        <f t="shared" ref="A298:A322" si="11">A297+1</f>
         <v>130</v>
       </c>
       <c r="B298" t="s">
@@ -9090,6 +9090,101 @@
         <v>10</v>
       </c>
       <c r="C314">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="315" spans="1:3">
+      <c r="A315">
+        <v>131</v>
+      </c>
+      <c r="B315" t="s">
+        <v>8</v>
+      </c>
+      <c r="C315">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="316" spans="1:3">
+      <c r="A316">
+        <f t="shared" si="11"/>
+        <v>132</v>
+      </c>
+      <c r="B316" t="s">
+        <v>11</v>
+      </c>
+      <c r="C316">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="317" spans="1:3">
+      <c r="A317">
+        <f t="shared" si="11"/>
+        <v>133</v>
+      </c>
+      <c r="B317" t="s">
+        <v>9</v>
+      </c>
+      <c r="C317">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="318" spans="1:3">
+      <c r="A318">
+        <f t="shared" si="11"/>
+        <v>134</v>
+      </c>
+      <c r="B318" t="s">
+        <v>11</v>
+      </c>
+      <c r="C318">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="319" spans="1:3">
+      <c r="A319">
+        <f t="shared" si="11"/>
+        <v>135</v>
+      </c>
+      <c r="B319" t="s">
+        <v>10</v>
+      </c>
+      <c r="C319">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="320" spans="1:3">
+      <c r="A320">
+        <f t="shared" si="11"/>
+        <v>136</v>
+      </c>
+      <c r="B320" t="s">
+        <v>8</v>
+      </c>
+      <c r="C320">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="321" spans="1:3">
+      <c r="A321">
+        <f t="shared" si="11"/>
+        <v>137</v>
+      </c>
+      <c r="B321" t="s">
+        <v>8</v>
+      </c>
+      <c r="C321">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="322" spans="1:3">
+      <c r="A322">
+        <f t="shared" si="11"/>
+        <v>138</v>
+      </c>
+      <c r="B322" t="s">
+        <v>11</v>
+      </c>
+      <c r="C322">
         <v>1</v>
       </c>
     </row>

--- a/l_r/2nd.xlsx
+++ b/l_r/2nd.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PycharmProjects\english\english-study\l_r\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3AA9D7F5-93B4-4878-8C06-8568C25D85F7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A531C35C-D1AB-491F-9E67-9070F7448652}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="270" yWindow="60" windowWidth="15330" windowHeight="14310" firstSheet="1" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="13800" yWindow="0" windowWidth="15330" windowHeight="15585" firstSheet="1" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="summary" sheetId="3" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="453" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="461" uniqueCount="74">
   <si>
     <t>問題番号</t>
     <rPh sb="0" eb="2">
@@ -5423,7 +5423,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3C7A3EDD-6597-4754-A609-A225833ECC81}">
-  <dimension ref="A2:H322"/>
+  <dimension ref="A2:H330"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <sheetData>
     <row r="2" spans="1:4">
@@ -8891,7 +8891,7 @@
     </row>
     <row r="298" spans="1:3">
       <c r="A298">
-        <f t="shared" ref="A298:A322" si="11">A297+1</f>
+        <f t="shared" ref="A298:A330" si="11">A297+1</f>
         <v>130</v>
       </c>
       <c r="B298" t="s">
@@ -9185,6 +9185,102 @@
         <v>11</v>
       </c>
       <c r="C322">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="323" spans="1:3">
+      <c r="A323">
+        <f t="shared" si="11"/>
+        <v>139</v>
+      </c>
+      <c r="B323" t="s">
+        <v>11</v>
+      </c>
+      <c r="C323">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="324" spans="1:3">
+      <c r="A324">
+        <f t="shared" si="11"/>
+        <v>140</v>
+      </c>
+      <c r="B324" t="s">
+        <v>10</v>
+      </c>
+      <c r="C324">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="325" spans="1:3">
+      <c r="A325">
+        <f t="shared" si="11"/>
+        <v>141</v>
+      </c>
+      <c r="B325" t="s">
+        <v>9</v>
+      </c>
+      <c r="C325">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="326" spans="1:3">
+      <c r="A326">
+        <f t="shared" si="11"/>
+        <v>142</v>
+      </c>
+      <c r="B326" t="s">
+        <v>8</v>
+      </c>
+      <c r="C326">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="327" spans="1:3">
+      <c r="A327">
+        <f t="shared" si="11"/>
+        <v>143</v>
+      </c>
+      <c r="B327" t="s">
+        <v>9</v>
+      </c>
+      <c r="C327">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="328" spans="1:3">
+      <c r="A328">
+        <f t="shared" si="11"/>
+        <v>144</v>
+      </c>
+      <c r="B328" t="s">
+        <v>11</v>
+      </c>
+      <c r="C328">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="329" spans="1:3">
+      <c r="A329">
+        <f t="shared" si="11"/>
+        <v>145</v>
+      </c>
+      <c r="B329" t="s">
+        <v>11</v>
+      </c>
+      <c r="C329">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="330" spans="1:3">
+      <c r="A330">
+        <f t="shared" si="11"/>
+        <v>146</v>
+      </c>
+      <c r="B330" t="s">
+        <v>10</v>
+      </c>
+      <c r="C330">
         <v>1</v>
       </c>
     </row>

--- a/l_r/2nd.xlsx
+++ b/l_r/2nd.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PycharmProjects\english\english-study\l_r\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A531C35C-D1AB-491F-9E67-9070F7448652}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{73C5F376-694D-42CB-8BFB-E2A4BFEB08D1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="13800" yWindow="0" windowWidth="15330" windowHeight="15585" firstSheet="1" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="7710" yWindow="1170" windowWidth="15330" windowHeight="14310" firstSheet="1" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="summary" sheetId="3" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="461" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="467" uniqueCount="74">
   <si>
     <t>問題番号</t>
     <rPh sb="0" eb="2">
@@ -5423,7 +5423,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3C7A3EDD-6597-4754-A609-A225833ECC81}">
-  <dimension ref="A2:H330"/>
+  <dimension ref="A2:H336"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <sheetData>
     <row r="2" spans="1:4">
@@ -8891,7 +8891,7 @@
     </row>
     <row r="298" spans="1:3">
       <c r="A298">
-        <f t="shared" ref="A298:A330" si="11">A297+1</f>
+        <f t="shared" ref="A298:A336" si="11">A297+1</f>
         <v>130</v>
       </c>
       <c r="B298" t="s">
@@ -9281,6 +9281,78 @@
         <v>10</v>
       </c>
       <c r="C330">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="331" spans="1:3">
+      <c r="A331">
+        <f t="shared" si="11"/>
+        <v>147</v>
+      </c>
+      <c r="B331" t="s">
+        <v>8</v>
+      </c>
+      <c r="C331">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="332" spans="1:3">
+      <c r="A332">
+        <f t="shared" si="11"/>
+        <v>148</v>
+      </c>
+      <c r="B332" t="s">
+        <v>10</v>
+      </c>
+      <c r="C332">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="333" spans="1:3">
+      <c r="A333">
+        <f t="shared" si="11"/>
+        <v>149</v>
+      </c>
+      <c r="B333" t="s">
+        <v>11</v>
+      </c>
+      <c r="C333">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="334" spans="1:3">
+      <c r="A334">
+        <f t="shared" si="11"/>
+        <v>150</v>
+      </c>
+      <c r="B334" t="s">
+        <v>11</v>
+      </c>
+      <c r="C334">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="335" spans="1:3">
+      <c r="A335">
+        <f t="shared" si="11"/>
+        <v>151</v>
+      </c>
+      <c r="B335" t="s">
+        <v>10</v>
+      </c>
+      <c r="C335">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="336" spans="1:3">
+      <c r="A336">
+        <f t="shared" si="11"/>
+        <v>152</v>
+      </c>
+      <c r="B336" t="s">
+        <v>9</v>
+      </c>
+      <c r="C336">
         <v>1</v>
       </c>
     </row>

--- a/l_r/2nd.xlsx
+++ b/l_r/2nd.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PycharmProjects\english\english-study\l_r\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{73C5F376-694D-42CB-8BFB-E2A4BFEB08D1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9F154FC4-A082-40AE-843C-E66A4D257CFB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="7710" yWindow="1170" windowWidth="15330" windowHeight="14310" firstSheet="1" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="390" yWindow="390" windowWidth="21600" windowHeight="11295" firstSheet="1" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="summary" sheetId="3" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="467" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="475" uniqueCount="74">
   <si>
     <t>問題番号</t>
     <rPh sb="0" eb="2">
@@ -5423,7 +5423,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3C7A3EDD-6597-4754-A609-A225833ECC81}">
-  <dimension ref="A2:H336"/>
+  <dimension ref="A2:H344"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <sheetData>
     <row r="2" spans="1:4">
@@ -8891,7 +8891,7 @@
     </row>
     <row r="298" spans="1:3">
       <c r="A298">
-        <f t="shared" ref="A298:A336" si="11">A297+1</f>
+        <f t="shared" ref="A298:A344" si="11">A297+1</f>
         <v>130</v>
       </c>
       <c r="B298" t="s">
@@ -9353,6 +9353,102 @@
         <v>9</v>
       </c>
       <c r="C336">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="337" spans="1:3">
+      <c r="A337">
+        <f t="shared" si="11"/>
+        <v>153</v>
+      </c>
+      <c r="B337" t="s">
+        <v>9</v>
+      </c>
+      <c r="C337">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="338" spans="1:3">
+      <c r="A338">
+        <f t="shared" si="11"/>
+        <v>154</v>
+      </c>
+      <c r="B338" t="s">
+        <v>9</v>
+      </c>
+      <c r="C338">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="339" spans="1:3">
+      <c r="A339">
+        <f t="shared" si="11"/>
+        <v>155</v>
+      </c>
+      <c r="B339" t="s">
+        <v>10</v>
+      </c>
+      <c r="C339">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="340" spans="1:3">
+      <c r="A340">
+        <f t="shared" si="11"/>
+        <v>156</v>
+      </c>
+      <c r="B340" t="s">
+        <v>11</v>
+      </c>
+      <c r="C340">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="341" spans="1:3">
+      <c r="A341">
+        <f t="shared" si="11"/>
+        <v>157</v>
+      </c>
+      <c r="B341" t="s">
+        <v>11</v>
+      </c>
+      <c r="C341">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="342" spans="1:3">
+      <c r="A342">
+        <f t="shared" si="11"/>
+        <v>158</v>
+      </c>
+      <c r="B342" t="s">
+        <v>11</v>
+      </c>
+      <c r="C342">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="343" spans="1:3">
+      <c r="A343">
+        <f t="shared" si="11"/>
+        <v>159</v>
+      </c>
+      <c r="B343" t="s">
+        <v>8</v>
+      </c>
+      <c r="C343">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="344" spans="1:3">
+      <c r="A344">
+        <f t="shared" si="11"/>
+        <v>160</v>
+      </c>
+      <c r="B344" t="s">
+        <v>9</v>
+      </c>
+      <c r="C344">
         <v>1</v>
       </c>
     </row>

--- a/l_r/2nd.xlsx
+++ b/l_r/2nd.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PycharmProjects\english\english-study\l_r\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9F154FC4-A082-40AE-843C-E66A4D257CFB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4A5534D0-ED98-4BFE-92FD-39B2D5A19AB5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="390" yWindow="390" windowWidth="21600" windowHeight="11295" firstSheet="1" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="5925" yWindow="3540" windowWidth="21600" windowHeight="11295" firstSheet="1" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="summary" sheetId="3" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="475" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="488" uniqueCount="76">
   <si>
     <t>問題番号</t>
     <rPh sb="0" eb="2">
@@ -350,6 +350,17 @@
     <t>集中する</t>
     <rPh sb="0" eb="2">
       <t>シュウチュウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>retreat</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>後退</t>
+    <rPh sb="0" eb="2">
+      <t>コウタイ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -5423,7 +5434,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3C7A3EDD-6597-4754-A609-A225833ECC81}">
-  <dimension ref="A2:H344"/>
+  <dimension ref="A2:H355"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <sheetData>
     <row r="2" spans="1:4">
@@ -8891,7 +8902,7 @@
     </row>
     <row r="298" spans="1:3">
       <c r="A298">
-        <f t="shared" ref="A298:A344" si="11">A297+1</f>
+        <f t="shared" ref="A298:A355" si="11">A297+1</f>
         <v>130</v>
       </c>
       <c r="B298" t="s">
@@ -9356,7 +9367,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="337" spans="1:3">
+    <row r="337" spans="1:8">
       <c r="A337">
         <f t="shared" si="11"/>
         <v>153</v>
@@ -9368,7 +9379,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="338" spans="1:3">
+    <row r="338" spans="1:8">
       <c r="A338">
         <f t="shared" si="11"/>
         <v>154</v>
@@ -9380,7 +9391,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="339" spans="1:3">
+    <row r="339" spans="1:8">
       <c r="A339">
         <f t="shared" si="11"/>
         <v>155</v>
@@ -9392,7 +9403,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="340" spans="1:3">
+    <row r="340" spans="1:8">
       <c r="A340">
         <f t="shared" si="11"/>
         <v>156</v>
@@ -9404,7 +9415,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="341" spans="1:3">
+    <row r="341" spans="1:8">
       <c r="A341">
         <f t="shared" si="11"/>
         <v>157</v>
@@ -9416,7 +9427,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="342" spans="1:3">
+    <row r="342" spans="1:8">
       <c r="A342">
         <f t="shared" si="11"/>
         <v>158</v>
@@ -9428,7 +9439,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="343" spans="1:3">
+    <row r="343" spans="1:8">
       <c r="A343">
         <f t="shared" si="11"/>
         <v>159</v>
@@ -9440,7 +9451,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="344" spans="1:3">
+    <row r="344" spans="1:8">
       <c r="A344">
         <f t="shared" si="11"/>
         <v>160</v>
@@ -9449,6 +9460,144 @@
         <v>9</v>
       </c>
       <c r="C344">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="345" spans="1:8">
+      <c r="A345">
+        <f t="shared" si="11"/>
+        <v>161</v>
+      </c>
+      <c r="B345" t="s">
+        <v>11</v>
+      </c>
+      <c r="C345">
+        <v>1</v>
+      </c>
+      <c r="G345" t="s">
+        <v>74</v>
+      </c>
+      <c r="H345" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="346" spans="1:8">
+      <c r="A346">
+        <f t="shared" si="11"/>
+        <v>162</v>
+      </c>
+      <c r="B346" t="s">
+        <v>8</v>
+      </c>
+      <c r="C346">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="347" spans="1:8">
+      <c r="A347">
+        <f t="shared" si="11"/>
+        <v>163</v>
+      </c>
+      <c r="B347" t="s">
+        <v>11</v>
+      </c>
+      <c r="C347">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="348" spans="1:8">
+      <c r="A348">
+        <f t="shared" si="11"/>
+        <v>164</v>
+      </c>
+      <c r="B348" t="s">
+        <v>10</v>
+      </c>
+      <c r="C348">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="349" spans="1:8">
+      <c r="A349">
+        <f t="shared" si="11"/>
+        <v>165</v>
+      </c>
+      <c r="B349" t="s">
+        <v>10</v>
+      </c>
+      <c r="C349">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="350" spans="1:8">
+      <c r="A350">
+        <f t="shared" si="11"/>
+        <v>166</v>
+      </c>
+      <c r="B350" t="s">
+        <v>9</v>
+      </c>
+      <c r="C350">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="351" spans="1:8">
+      <c r="A351">
+        <f t="shared" si="11"/>
+        <v>167</v>
+      </c>
+      <c r="B351" t="s">
+        <v>9</v>
+      </c>
+      <c r="C351">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="352" spans="1:8">
+      <c r="A352">
+        <f t="shared" si="11"/>
+        <v>168</v>
+      </c>
+      <c r="B352" t="s">
+        <v>9</v>
+      </c>
+      <c r="C352">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="353" spans="1:3">
+      <c r="A353">
+        <f t="shared" si="11"/>
+        <v>169</v>
+      </c>
+      <c r="B353" t="s">
+        <v>10</v>
+      </c>
+      <c r="C353">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="354" spans="1:3">
+      <c r="A354">
+        <f t="shared" si="11"/>
+        <v>170</v>
+      </c>
+      <c r="B354" t="s">
+        <v>9</v>
+      </c>
+      <c r="C354">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="355" spans="1:3">
+      <c r="A355">
+        <f t="shared" si="11"/>
+        <v>171</v>
+      </c>
+      <c r="B355" t="s">
+        <v>10</v>
+      </c>
+      <c r="C355">
         <v>1</v>
       </c>
     </row>

--- a/l_r/2nd.xlsx
+++ b/l_r/2nd.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PycharmProjects\english\english-study\l_r\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4A5534D0-ED98-4BFE-92FD-39B2D5A19AB5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AEE4ACEF-A398-43C2-A418-B7E81E296F18}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5925" yWindow="3540" windowWidth="21600" windowHeight="11295" firstSheet="1" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="7380" yWindow="1425" windowWidth="21600" windowHeight="11295" firstSheet="1" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="summary" sheetId="3" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="488" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="497" uniqueCount="76">
   <si>
     <t>問題番号</t>
     <rPh sb="0" eb="2">
@@ -5434,7 +5434,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3C7A3EDD-6597-4754-A609-A225833ECC81}">
-  <dimension ref="A2:H355"/>
+  <dimension ref="A2:H364"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <sheetData>
     <row r="2" spans="1:4">
@@ -8902,7 +8902,7 @@
     </row>
     <row r="298" spans="1:3">
       <c r="A298">
-        <f t="shared" ref="A298:A355" si="11">A297+1</f>
+        <f t="shared" ref="A298:A361" si="11">A297+1</f>
         <v>130</v>
       </c>
       <c r="B298" t="s">
@@ -9598,6 +9598,114 @@
         <v>10</v>
       </c>
       <c r="C355">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="356" spans="1:3">
+      <c r="A356">
+        <f t="shared" si="11"/>
+        <v>172</v>
+      </c>
+      <c r="B356" t="s">
+        <v>8</v>
+      </c>
+      <c r="C356">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="357" spans="1:3">
+      <c r="A357">
+        <f t="shared" si="11"/>
+        <v>173</v>
+      </c>
+      <c r="B357" t="s">
+        <v>8</v>
+      </c>
+      <c r="C357">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="358" spans="1:3">
+      <c r="A358">
+        <f t="shared" si="11"/>
+        <v>174</v>
+      </c>
+      <c r="B358" t="s">
+        <v>9</v>
+      </c>
+      <c r="C358">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="359" spans="1:3">
+      <c r="A359">
+        <f t="shared" si="11"/>
+        <v>175</v>
+      </c>
+      <c r="B359" t="s">
+        <v>10</v>
+      </c>
+      <c r="C359">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="360" spans="1:3">
+      <c r="A360">
+        <f t="shared" si="11"/>
+        <v>176</v>
+      </c>
+      <c r="B360" t="s">
+        <v>8</v>
+      </c>
+      <c r="C360">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="361" spans="1:3">
+      <c r="A361">
+        <f t="shared" si="11"/>
+        <v>177</v>
+      </c>
+      <c r="B361" t="s">
+        <v>8</v>
+      </c>
+      <c r="C361">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="362" spans="1:3">
+      <c r="A362">
+        <f t="shared" ref="A362:A364" si="12">A361+1</f>
+        <v>178</v>
+      </c>
+      <c r="B362" t="s">
+        <v>11</v>
+      </c>
+      <c r="C362">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="363" spans="1:3">
+      <c r="A363">
+        <f t="shared" si="12"/>
+        <v>179</v>
+      </c>
+      <c r="B363" t="s">
+        <v>8</v>
+      </c>
+      <c r="C363">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="364" spans="1:3">
+      <c r="A364">
+        <f t="shared" si="12"/>
+        <v>180</v>
+      </c>
+      <c r="B364" t="s">
+        <v>10</v>
+      </c>
+      <c r="C364">
         <v>1</v>
       </c>
     </row>

--- a/l_r/2nd.xlsx
+++ b/l_r/2nd.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PycharmProjects\english\english-study\l_r\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AEE4ACEF-A398-43C2-A418-B7E81E296F18}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4856C5D5-A239-44A7-A26F-AC8CA2409541}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="7380" yWindow="1425" windowWidth="21600" windowHeight="11295" firstSheet="1" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="6810" yWindow="2760" windowWidth="21600" windowHeight="11295" firstSheet="1" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="summary" sheetId="3" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="497" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="502" uniqueCount="76">
   <si>
     <t>問題番号</t>
     <rPh sb="0" eb="2">
@@ -5434,7 +5434,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3C7A3EDD-6597-4754-A609-A225833ECC81}">
-  <dimension ref="A2:H364"/>
+  <dimension ref="A2:H369"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <sheetData>
     <row r="2" spans="1:4">
@@ -9675,7 +9675,7 @@
     </row>
     <row r="362" spans="1:3">
       <c r="A362">
-        <f t="shared" ref="A362:A364" si="12">A361+1</f>
+        <f t="shared" ref="A362:A369" si="12">A361+1</f>
         <v>178</v>
       </c>
       <c r="B362" t="s">
@@ -9706,6 +9706,66 @@
         <v>10</v>
       </c>
       <c r="C364">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="365" spans="1:3">
+      <c r="A365">
+        <f t="shared" si="12"/>
+        <v>181</v>
+      </c>
+      <c r="B365" t="s">
+        <v>10</v>
+      </c>
+      <c r="C365">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="366" spans="1:3">
+      <c r="A366">
+        <f t="shared" si="12"/>
+        <v>182</v>
+      </c>
+      <c r="B366" t="s">
+        <v>11</v>
+      </c>
+      <c r="C366">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="367" spans="1:3">
+      <c r="A367">
+        <f t="shared" si="12"/>
+        <v>183</v>
+      </c>
+      <c r="B367" t="s">
+        <v>8</v>
+      </c>
+      <c r="C367">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="368" spans="1:3">
+      <c r="A368">
+        <f t="shared" si="12"/>
+        <v>184</v>
+      </c>
+      <c r="B368" t="s">
+        <v>8</v>
+      </c>
+      <c r="C368">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="369" spans="1:3">
+      <c r="A369">
+        <f t="shared" si="12"/>
+        <v>185</v>
+      </c>
+      <c r="B369" t="s">
+        <v>9</v>
+      </c>
+      <c r="C369">
         <v>1</v>
       </c>
     </row>

--- a/l_r/2nd.xlsx
+++ b/l_r/2nd.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PycharmProjects\english\english-study\l_r\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4856C5D5-A239-44A7-A26F-AC8CA2409541}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A0199984-E88D-4CD2-844C-7586790361E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="6810" yWindow="2760" windowWidth="21600" windowHeight="11295" firstSheet="1" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="1" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="summary" sheetId="3" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="502" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="507" uniqueCount="76">
   <si>
     <t>問題番号</t>
     <rPh sb="0" eb="2">
@@ -5434,7 +5434,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3C7A3EDD-6597-4754-A609-A225833ECC81}">
-  <dimension ref="A2:H369"/>
+  <dimension ref="A2:H374"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <sheetData>
     <row r="2" spans="1:4">
@@ -9675,7 +9675,7 @@
     </row>
     <row r="362" spans="1:3">
       <c r="A362">
-        <f t="shared" ref="A362:A369" si="12">A361+1</f>
+        <f t="shared" ref="A362:A374" si="12">A361+1</f>
         <v>178</v>
       </c>
       <c r="B362" t="s">
@@ -9766,6 +9766,66 @@
         <v>9</v>
       </c>
       <c r="C369">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="370" spans="1:3">
+      <c r="A370">
+        <f t="shared" si="12"/>
+        <v>186</v>
+      </c>
+      <c r="B370" t="s">
+        <v>10</v>
+      </c>
+      <c r="C370">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="371" spans="1:3">
+      <c r="A371">
+        <f t="shared" si="12"/>
+        <v>187</v>
+      </c>
+      <c r="B371" t="s">
+        <v>11</v>
+      </c>
+      <c r="C371">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="372" spans="1:3">
+      <c r="A372">
+        <f t="shared" si="12"/>
+        <v>188</v>
+      </c>
+      <c r="B372" t="s">
+        <v>8</v>
+      </c>
+      <c r="C372">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="373" spans="1:3">
+      <c r="A373">
+        <f t="shared" si="12"/>
+        <v>189</v>
+      </c>
+      <c r="B373" t="s">
+        <v>10</v>
+      </c>
+      <c r="C373">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="374" spans="1:3">
+      <c r="A374">
+        <f t="shared" si="12"/>
+        <v>190</v>
+      </c>
+      <c r="B374" t="s">
+        <v>9</v>
+      </c>
+      <c r="C374">
         <v>1</v>
       </c>
     </row>

--- a/l_r/2nd.xlsx
+++ b/l_r/2nd.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PycharmProjects\english\english-study\l_r\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A0199984-E88D-4CD2-844C-7586790361E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A16127A5-0A73-4A28-B3C9-F42CB5B7EE98}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="1" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="507" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="512" uniqueCount="76">
   <si>
     <t>問題番号</t>
     <rPh sb="0" eb="2">
@@ -5434,7 +5434,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3C7A3EDD-6597-4754-A609-A225833ECC81}">
-  <dimension ref="A2:H374"/>
+  <dimension ref="A2:H379"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <sheetData>
     <row r="2" spans="1:4">
@@ -9675,7 +9675,7 @@
     </row>
     <row r="362" spans="1:3">
       <c r="A362">
-        <f t="shared" ref="A362:A374" si="12">A361+1</f>
+        <f t="shared" ref="A362:A379" si="12">A361+1</f>
         <v>178</v>
       </c>
       <c r="B362" t="s">
@@ -9826,6 +9826,66 @@
         <v>9</v>
       </c>
       <c r="C374">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="375" spans="1:3">
+      <c r="A375">
+        <f t="shared" si="12"/>
+        <v>191</v>
+      </c>
+      <c r="B375" t="s">
+        <v>11</v>
+      </c>
+      <c r="C375">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="376" spans="1:3">
+      <c r="A376">
+        <f t="shared" si="12"/>
+        <v>192</v>
+      </c>
+      <c r="B376" t="s">
+        <v>10</v>
+      </c>
+      <c r="C376">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="377" spans="1:3">
+      <c r="A377">
+        <f t="shared" si="12"/>
+        <v>193</v>
+      </c>
+      <c r="B377" t="s">
+        <v>10</v>
+      </c>
+      <c r="C377">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="378" spans="1:3">
+      <c r="A378">
+        <f t="shared" si="12"/>
+        <v>194</v>
+      </c>
+      <c r="B378" t="s">
+        <v>9</v>
+      </c>
+      <c r="C378">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="379" spans="1:3">
+      <c r="A379">
+        <f t="shared" si="12"/>
+        <v>195</v>
+      </c>
+      <c r="B379" t="s">
+        <v>8</v>
+      </c>
+      <c r="C379">
         <v>1</v>
       </c>
     </row>

--- a/l_r/2nd.xlsx
+++ b/l_r/2nd.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PycharmProjects\english\english-study\l_r\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A16127A5-0A73-4A28-B3C9-F42CB5B7EE98}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D7AF2E7B-4852-476B-8216-81ABA76688B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="1" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="885" yWindow="0" windowWidth="15630" windowHeight="15585" firstSheet="1" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="summary" sheetId="3" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="512" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="517" uniqueCount="76">
   <si>
     <t>問題番号</t>
     <rPh sb="0" eb="2">
@@ -5434,7 +5434,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3C7A3EDD-6597-4754-A609-A225833ECC81}">
-  <dimension ref="A2:H379"/>
+  <dimension ref="A2:H384"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <sheetData>
     <row r="2" spans="1:4">
@@ -9675,7 +9675,7 @@
     </row>
     <row r="362" spans="1:3">
       <c r="A362">
-        <f t="shared" ref="A362:A379" si="12">A361+1</f>
+        <f t="shared" ref="A362:A384" si="12">A361+1</f>
         <v>178</v>
       </c>
       <c r="B362" t="s">
@@ -9886,6 +9886,66 @@
         <v>8</v>
       </c>
       <c r="C379">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="380" spans="1:3">
+      <c r="A380">
+        <f t="shared" si="12"/>
+        <v>196</v>
+      </c>
+      <c r="B380" t="s">
+        <v>8</v>
+      </c>
+      <c r="C380">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="381" spans="1:3">
+      <c r="A381">
+        <f t="shared" si="12"/>
+        <v>197</v>
+      </c>
+      <c r="B381" t="s">
+        <v>10</v>
+      </c>
+      <c r="C381">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="382" spans="1:3">
+      <c r="A382">
+        <f t="shared" si="12"/>
+        <v>198</v>
+      </c>
+      <c r="B382" t="s">
+        <v>9</v>
+      </c>
+      <c r="C382">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="383" spans="1:3">
+      <c r="A383">
+        <f t="shared" si="12"/>
+        <v>199</v>
+      </c>
+      <c r="B383" t="s">
+        <v>11</v>
+      </c>
+      <c r="C383">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="384" spans="1:3">
+      <c r="A384">
+        <f t="shared" si="12"/>
+        <v>200</v>
+      </c>
+      <c r="B384" t="s">
+        <v>9</v>
+      </c>
+      <c r="C384">
         <v>1</v>
       </c>
     </row>

--- a/l_r/2nd.xlsx
+++ b/l_r/2nd.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PycharmProjects\english\english-study\l_r\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D7AF2E7B-4852-476B-8216-81ABA76688B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A4CA966C-15B5-496F-9F83-7331FDC83283}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="885" yWindow="0" windowWidth="15630" windowHeight="15585" firstSheet="1" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="885" yWindow="0" windowWidth="15810" windowHeight="15585" firstSheet="1" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="summary" sheetId="3" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="517" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="527" uniqueCount="76">
   <si>
     <t>問題番号</t>
     <rPh sb="0" eb="2">
@@ -5434,7 +5434,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3C7A3EDD-6597-4754-A609-A225833ECC81}">
-  <dimension ref="A2:H384"/>
+  <dimension ref="A2:H394"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <sheetData>
     <row r="2" spans="1:4">
@@ -9675,7 +9675,7 @@
     </row>
     <row r="362" spans="1:3">
       <c r="A362">
-        <f t="shared" ref="A362:A384" si="12">A361+1</f>
+        <f t="shared" ref="A362:A395" si="12">A361+1</f>
         <v>178</v>
       </c>
       <c r="B362" t="s">
@@ -9946,6 +9946,125 @@
         <v>9</v>
       </c>
       <c r="C384">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="385" spans="1:3">
+      <c r="A385">
+        <v>101</v>
+      </c>
+      <c r="B385" t="s">
+        <v>10</v>
+      </c>
+      <c r="C385">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="386" spans="1:3">
+      <c r="A386">
+        <f t="shared" si="12"/>
+        <v>102</v>
+      </c>
+      <c r="B386" t="s">
+        <v>11</v>
+      </c>
+      <c r="C386">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="387" spans="1:3">
+      <c r="A387">
+        <f t="shared" si="12"/>
+        <v>103</v>
+      </c>
+      <c r="B387" t="s">
+        <v>10</v>
+      </c>
+      <c r="C387">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="388" spans="1:3">
+      <c r="A388">
+        <f t="shared" si="12"/>
+        <v>104</v>
+      </c>
+      <c r="B388" t="s">
+        <v>9</v>
+      </c>
+      <c r="C388">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="389" spans="1:3">
+      <c r="A389">
+        <f t="shared" si="12"/>
+        <v>105</v>
+      </c>
+      <c r="B389" t="s">
+        <v>9</v>
+      </c>
+      <c r="C389">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="390" spans="1:3">
+      <c r="A390">
+        <f t="shared" si="12"/>
+        <v>106</v>
+      </c>
+      <c r="B390" t="s">
+        <v>9</v>
+      </c>
+      <c r="C390">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="391" spans="1:3">
+      <c r="A391">
+        <f t="shared" si="12"/>
+        <v>107</v>
+      </c>
+      <c r="B391" t="s">
+        <v>10</v>
+      </c>
+      <c r="C391">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="392" spans="1:3">
+      <c r="A392">
+        <f t="shared" si="12"/>
+        <v>108</v>
+      </c>
+      <c r="B392" t="s">
+        <v>8</v>
+      </c>
+      <c r="C392">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="393" spans="1:3">
+      <c r="A393">
+        <f t="shared" si="12"/>
+        <v>109</v>
+      </c>
+      <c r="B393" t="s">
+        <v>10</v>
+      </c>
+      <c r="C393">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="394" spans="1:3">
+      <c r="A394">
+        <f t="shared" si="12"/>
+        <v>110</v>
+      </c>
+      <c r="B394" t="s">
+        <v>9</v>
+      </c>
+      <c r="C394">
         <v>1</v>
       </c>
     </row>

--- a/l_r/2nd.xlsx
+++ b/l_r/2nd.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PycharmProjects\english\english-study\l_r\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A4CA966C-15B5-496F-9F83-7331FDC83283}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2C1764EB-6E90-4564-9CEC-5E27158BDDF7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="885" yWindow="0" windowWidth="15810" windowHeight="15585" firstSheet="1" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="6105" yWindow="0" windowWidth="21600" windowHeight="15585" firstSheet="1" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="summary" sheetId="3" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="527" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="547" uniqueCount="83">
   <si>
     <t>問題番号</t>
     <rPh sb="0" eb="2">
@@ -362,6 +362,34 @@
     <rPh sb="0" eb="2">
       <t>コウタイ</t>
     </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>C</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>A</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>D</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>C</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>B</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>A</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>D</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -5434,7 +5462,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3C7A3EDD-6597-4754-A609-A225833ECC81}">
-  <dimension ref="A2:H394"/>
+  <dimension ref="A2:H414"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <sheetData>
     <row r="2" spans="1:4">
@@ -9675,7 +9703,7 @@
     </row>
     <row r="362" spans="1:3">
       <c r="A362">
-        <f t="shared" ref="A362:A395" si="12">A361+1</f>
+        <f t="shared" ref="A362:A414" si="12">A361+1</f>
         <v>178</v>
       </c>
       <c r="B362" t="s">
@@ -10065,6 +10093,246 @@
         <v>9</v>
       </c>
       <c r="C394">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="395" spans="1:3">
+      <c r="A395">
+        <f t="shared" si="12"/>
+        <v>111</v>
+      </c>
+      <c r="B395" t="s">
+        <v>76</v>
+      </c>
+      <c r="C395">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="396" spans="1:3">
+      <c r="A396">
+        <f t="shared" si="12"/>
+        <v>112</v>
+      </c>
+      <c r="B396" t="s">
+        <v>76</v>
+      </c>
+      <c r="C396">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="397" spans="1:3">
+      <c r="A397">
+        <f t="shared" si="12"/>
+        <v>113</v>
+      </c>
+      <c r="B397" t="s">
+        <v>77</v>
+      </c>
+      <c r="C397">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="398" spans="1:3">
+      <c r="A398">
+        <f t="shared" si="12"/>
+        <v>114</v>
+      </c>
+      <c r="B398" t="s">
+        <v>77</v>
+      </c>
+      <c r="C398">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="399" spans="1:3">
+      <c r="A399">
+        <f t="shared" si="12"/>
+        <v>115</v>
+      </c>
+      <c r="B399" t="s">
+        <v>78</v>
+      </c>
+      <c r="C399">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="400" spans="1:3">
+      <c r="A400">
+        <f t="shared" si="12"/>
+        <v>116</v>
+      </c>
+      <c r="B400" t="s">
+        <v>77</v>
+      </c>
+      <c r="C400">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="401" spans="1:3">
+      <c r="A401">
+        <f t="shared" si="12"/>
+        <v>117</v>
+      </c>
+      <c r="B401" t="s">
+        <v>77</v>
+      </c>
+      <c r="C401">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="402" spans="1:3">
+      <c r="A402">
+        <f t="shared" si="12"/>
+        <v>118</v>
+      </c>
+      <c r="B402" t="s">
+        <v>76</v>
+      </c>
+      <c r="C402">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="403" spans="1:3">
+      <c r="A403">
+        <f t="shared" si="12"/>
+        <v>119</v>
+      </c>
+      <c r="B403" t="s">
+        <v>76</v>
+      </c>
+      <c r="C403">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="404" spans="1:3">
+      <c r="A404">
+        <f t="shared" si="12"/>
+        <v>120</v>
+      </c>
+      <c r="B404" t="s">
+        <v>78</v>
+      </c>
+      <c r="C404">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="405" spans="1:3">
+      <c r="A405">
+        <f t="shared" si="12"/>
+        <v>121</v>
+      </c>
+      <c r="B405" t="s">
+        <v>79</v>
+      </c>
+      <c r="C405">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="406" spans="1:3">
+      <c r="A406">
+        <f t="shared" si="12"/>
+        <v>122</v>
+      </c>
+      <c r="B406" t="s">
+        <v>80</v>
+      </c>
+      <c r="C406">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="407" spans="1:3">
+      <c r="A407">
+        <f t="shared" si="12"/>
+        <v>123</v>
+      </c>
+      <c r="B407" t="s">
+        <v>80</v>
+      </c>
+      <c r="C407">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="408" spans="1:3">
+      <c r="A408">
+        <f t="shared" si="12"/>
+        <v>124</v>
+      </c>
+      <c r="B408" t="s">
+        <v>81</v>
+      </c>
+      <c r="C408">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="409" spans="1:3">
+      <c r="A409">
+        <f t="shared" si="12"/>
+        <v>125</v>
+      </c>
+      <c r="B409" t="s">
+        <v>81</v>
+      </c>
+      <c r="C409">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="410" spans="1:3">
+      <c r="A410">
+        <f t="shared" si="12"/>
+        <v>126</v>
+      </c>
+      <c r="B410" t="s">
+        <v>79</v>
+      </c>
+      <c r="C410">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="411" spans="1:3">
+      <c r="A411">
+        <f t="shared" si="12"/>
+        <v>127</v>
+      </c>
+      <c r="B411" t="s">
+        <v>80</v>
+      </c>
+      <c r="C411">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="412" spans="1:3">
+      <c r="A412">
+        <f t="shared" si="12"/>
+        <v>128</v>
+      </c>
+      <c r="B412" t="s">
+        <v>80</v>
+      </c>
+      <c r="C412">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="413" spans="1:3">
+      <c r="A413">
+        <f t="shared" si="12"/>
+        <v>129</v>
+      </c>
+      <c r="B413" t="s">
+        <v>82</v>
+      </c>
+      <c r="C413">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="414" spans="1:3">
+      <c r="A414">
+        <f t="shared" si="12"/>
+        <v>130</v>
+      </c>
+      <c r="B414" t="s">
+        <v>79</v>
+      </c>
+      <c r="C414">
         <v>1</v>
       </c>
     </row>

--- a/l_r/2nd.xlsx
+++ b/l_r/2nd.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PycharmProjects\english\english-study\l_r\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2C1764EB-6E90-4564-9CEC-5E27158BDDF7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E36A3CF2-8DDC-4D79-9188-0C550DE9E7BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="6105" yWindow="0" windowWidth="21600" windowHeight="15585" firstSheet="1" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1380" yWindow="630" windowWidth="21600" windowHeight="14385" firstSheet="1" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="summary" sheetId="3" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="547" uniqueCount="83">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="557" uniqueCount="87">
   <si>
     <t>問題番号</t>
     <rPh sb="0" eb="2">
@@ -392,6 +392,22 @@
     <t>D</t>
     <phoneticPr fontId="1"/>
   </si>
+  <si>
+    <t>C</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>A</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>D</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>B</t>
+    <phoneticPr fontId="1"/>
+  </si>
 </sst>
 </file>
 
@@ -413,12 +429,18 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -433,9 +455,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="標準" xfId="0" builtinId="0"/>
@@ -5462,7 +5485,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3C7A3EDD-6597-4754-A609-A225833ECC81}">
-  <dimension ref="A2:H414"/>
+  <dimension ref="A2:H424"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <sheetData>
     <row r="2" spans="1:4">
@@ -9703,7 +9726,7 @@
     </row>
     <row r="362" spans="1:3">
       <c r="A362">
-        <f t="shared" ref="A362:A414" si="12">A361+1</f>
+        <f t="shared" ref="A362:A425" si="12">A361+1</f>
         <v>178</v>
       </c>
       <c r="B362" t="s">
@@ -10333,6 +10356,125 @@
         <v>79</v>
       </c>
       <c r="C414">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="415" spans="1:3">
+      <c r="A415">
+        <v>101</v>
+      </c>
+      <c r="B415" t="s">
+        <v>83</v>
+      </c>
+      <c r="C415">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="416" spans="1:3">
+      <c r="A416">
+        <f t="shared" si="12"/>
+        <v>102</v>
+      </c>
+      <c r="B416" t="s">
+        <v>84</v>
+      </c>
+      <c r="C416">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="417" spans="1:3">
+      <c r="A417">
+        <f t="shared" si="12"/>
+        <v>103</v>
+      </c>
+      <c r="B417" t="s">
+        <v>85</v>
+      </c>
+      <c r="C417">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="418" spans="1:3">
+      <c r="A418" s="2">
+        <f t="shared" si="12"/>
+        <v>104</v>
+      </c>
+      <c r="B418" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="C418" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="419" spans="1:3">
+      <c r="A419" s="2">
+        <f t="shared" si="12"/>
+        <v>105</v>
+      </c>
+      <c r="B419" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="C419" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="420" spans="1:3">
+      <c r="A420" s="2">
+        <f t="shared" si="12"/>
+        <v>106</v>
+      </c>
+      <c r="B420" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="C420" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="421" spans="1:3">
+      <c r="A421" s="2">
+        <f t="shared" si="12"/>
+        <v>107</v>
+      </c>
+      <c r="B421" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="C421" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="422" spans="1:3">
+      <c r="A422" s="2">
+        <f t="shared" si="12"/>
+        <v>108</v>
+      </c>
+      <c r="B422" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="C422" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="423" spans="1:3">
+      <c r="A423">
+        <f t="shared" si="12"/>
+        <v>109</v>
+      </c>
+      <c r="B423" t="s">
+        <v>83</v>
+      </c>
+      <c r="C423">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="424" spans="1:3">
+      <c r="A424">
+        <f t="shared" si="12"/>
+        <v>110</v>
+      </c>
+      <c r="B424" t="s">
+        <v>86</v>
+      </c>
+      <c r="C424">
         <v>1</v>
       </c>
     </row>

--- a/l_r/2nd.xlsx
+++ b/l_r/2nd.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PycharmProjects\english\english-study\l_r\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E36A3CF2-8DDC-4D79-9188-0C550DE9E7BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{29C57A3F-DA83-4590-9A3E-976FCE2013BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1380" yWindow="630" windowWidth="21600" windowHeight="14385" firstSheet="1" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-270" yWindow="480" windowWidth="21600" windowHeight="14385" firstSheet="1" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="summary" sheetId="3" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="557" uniqueCount="87">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="567" uniqueCount="91">
   <si>
     <t>問題番号</t>
     <rPh sb="0" eb="2">
@@ -408,6 +408,22 @@
     <t>B</t>
     <phoneticPr fontId="1"/>
   </si>
+  <si>
+    <t>C</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>D</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>A</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>B</t>
+    <phoneticPr fontId="1"/>
+  </si>
 </sst>
 </file>
 
@@ -455,10 +471,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="標準" xfId="0" builtinId="0"/>
@@ -5485,7 +5502,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3C7A3EDD-6597-4754-A609-A225833ECC81}">
-  <dimension ref="A2:H424"/>
+  <dimension ref="A2:H434"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <sheetData>
     <row r="2" spans="1:4">
@@ -10459,7 +10476,7 @@
         <f t="shared" si="12"/>
         <v>109</v>
       </c>
-      <c r="B423" t="s">
+      <c r="B423" s="3" t="s">
         <v>83</v>
       </c>
       <c r="C423">
@@ -10471,10 +10488,130 @@
         <f t="shared" si="12"/>
         <v>110</v>
       </c>
-      <c r="B424" t="s">
+      <c r="B424" s="3" t="s">
         <v>86</v>
       </c>
       <c r="C424">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="425" spans="1:3">
+      <c r="A425">
+        <f t="shared" si="12"/>
+        <v>111</v>
+      </c>
+      <c r="B425" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="C425" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="426" spans="1:3">
+      <c r="A426">
+        <f t="shared" ref="A426:A436" si="13">A425+1</f>
+        <v>112</v>
+      </c>
+      <c r="B426" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="C426" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="427" spans="1:3">
+      <c r="A427">
+        <f t="shared" si="13"/>
+        <v>113</v>
+      </c>
+      <c r="B427" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="C427" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="428" spans="1:3">
+      <c r="A428">
+        <f t="shared" si="13"/>
+        <v>114</v>
+      </c>
+      <c r="B428" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="C428" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="429" spans="1:3">
+      <c r="A429">
+        <f t="shared" si="13"/>
+        <v>115</v>
+      </c>
+      <c r="B429" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="C429" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="430" spans="1:3">
+      <c r="A430">
+        <f t="shared" si="13"/>
+        <v>116</v>
+      </c>
+      <c r="B430" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="C430" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="431" spans="1:3">
+      <c r="A431">
+        <f t="shared" si="13"/>
+        <v>117</v>
+      </c>
+      <c r="B431" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="C431" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="432" spans="1:3">
+      <c r="A432">
+        <f t="shared" si="13"/>
+        <v>118</v>
+      </c>
+      <c r="B432" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="C432" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="433" spans="1:3">
+      <c r="A433">
+        <f t="shared" si="13"/>
+        <v>119</v>
+      </c>
+      <c r="B433" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="C433" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="434" spans="1:3">
+      <c r="A434">
+        <f t="shared" si="13"/>
+        <v>120</v>
+      </c>
+      <c r="B434" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="C434" s="3">
         <v>1</v>
       </c>
     </row>

--- a/l_r/2nd.xlsx
+++ b/l_r/2nd.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PycharmProjects\english\english-study\l_r\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{29C57A3F-DA83-4590-9A3E-976FCE2013BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{509091F0-3AA9-4020-80BE-99E95171B250}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-270" yWindow="480" windowWidth="21600" windowHeight="14385" firstSheet="1" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="1" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="summary" sheetId="3" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="567" uniqueCount="91">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="577" uniqueCount="95">
   <si>
     <t>問題番号</t>
     <rPh sb="0" eb="2">
@@ -424,6 +424,22 @@
     <t>B</t>
     <phoneticPr fontId="1"/>
   </si>
+  <si>
+    <t>C</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>B</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>A</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>D</t>
+    <phoneticPr fontId="1"/>
+  </si>
 </sst>
 </file>
 
@@ -471,11 +487,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="標準" xfId="0" builtinId="0"/>
@@ -5502,7 +5517,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3C7A3EDD-6597-4754-A609-A225833ECC81}">
-  <dimension ref="A2:H434"/>
+  <dimension ref="A2:H444"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <sheetData>
     <row r="2" spans="1:4">
@@ -10476,7 +10491,7 @@
         <f t="shared" si="12"/>
         <v>109</v>
       </c>
-      <c r="B423" s="3" t="s">
+      <c r="B423" t="s">
         <v>83</v>
       </c>
       <c r="C423">
@@ -10488,7 +10503,7 @@
         <f t="shared" si="12"/>
         <v>110</v>
       </c>
-      <c r="B424" s="3" t="s">
+      <c r="B424" t="s">
         <v>86</v>
       </c>
       <c r="C424">
@@ -10500,22 +10515,22 @@
         <f t="shared" si="12"/>
         <v>111</v>
       </c>
-      <c r="B425" s="3" t="s">
+      <c r="B425" t="s">
         <v>87</v>
       </c>
-      <c r="C425" s="3">
+      <c r="C425">
         <v>1</v>
       </c>
     </row>
     <row r="426" spans="1:3">
       <c r="A426">
-        <f t="shared" ref="A426:A436" si="13">A425+1</f>
+        <f t="shared" ref="A426:A448" si="13">A425+1</f>
         <v>112</v>
       </c>
-      <c r="B426" s="3" t="s">
+      <c r="B426" t="s">
         <v>88</v>
       </c>
-      <c r="C426" s="3">
+      <c r="C426">
         <v>0</v>
       </c>
     </row>
@@ -10524,10 +10539,10 @@
         <f t="shared" si="13"/>
         <v>113</v>
       </c>
-      <c r="B427" s="3" t="s">
+      <c r="B427" t="s">
         <v>89</v>
       </c>
-      <c r="C427" s="3">
+      <c r="C427">
         <v>1</v>
       </c>
     </row>
@@ -10536,10 +10551,10 @@
         <f t="shared" si="13"/>
         <v>114</v>
       </c>
-      <c r="B428" s="3" t="s">
+      <c r="B428" t="s">
         <v>88</v>
       </c>
-      <c r="C428" s="3">
+      <c r="C428">
         <v>0</v>
       </c>
     </row>
@@ -10548,10 +10563,10 @@
         <f t="shared" si="13"/>
         <v>115</v>
       </c>
-      <c r="B429" s="3" t="s">
+      <c r="B429" t="s">
         <v>88</v>
       </c>
-      <c r="C429" s="3">
+      <c r="C429">
         <v>1</v>
       </c>
     </row>
@@ -10560,10 +10575,10 @@
         <f t="shared" si="13"/>
         <v>116</v>
       </c>
-      <c r="B430" s="3" t="s">
+      <c r="B430" t="s">
         <v>88</v>
       </c>
-      <c r="C430" s="3">
+      <c r="C430">
         <v>0</v>
       </c>
     </row>
@@ -10572,10 +10587,10 @@
         <f t="shared" si="13"/>
         <v>117</v>
       </c>
-      <c r="B431" s="3" t="s">
+      <c r="B431" t="s">
         <v>89</v>
       </c>
-      <c r="C431" s="3">
+      <c r="C431">
         <v>1</v>
       </c>
     </row>
@@ -10584,10 +10599,10 @@
         <f t="shared" si="13"/>
         <v>118</v>
       </c>
-      <c r="B432" s="3" t="s">
+      <c r="B432" t="s">
         <v>87</v>
       </c>
-      <c r="C432" s="3">
+      <c r="C432">
         <v>1</v>
       </c>
     </row>
@@ -10596,10 +10611,10 @@
         <f t="shared" si="13"/>
         <v>119</v>
       </c>
-      <c r="B433" s="3" t="s">
+      <c r="B433" t="s">
         <v>88</v>
       </c>
-      <c r="C433" s="3">
+      <c r="C433">
         <v>1</v>
       </c>
     </row>
@@ -10608,10 +10623,130 @@
         <f t="shared" si="13"/>
         <v>120</v>
       </c>
-      <c r="B434" s="3" t="s">
+      <c r="B434" t="s">
         <v>90</v>
       </c>
-      <c r="C434" s="3">
+      <c r="C434">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="435" spans="1:3">
+      <c r="A435">
+        <f t="shared" si="13"/>
+        <v>121</v>
+      </c>
+      <c r="B435" t="s">
+        <v>91</v>
+      </c>
+      <c r="C435">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="436" spans="1:3">
+      <c r="A436">
+        <f t="shared" si="13"/>
+        <v>122</v>
+      </c>
+      <c r="B436" t="s">
+        <v>92</v>
+      </c>
+      <c r="C436">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="437" spans="1:3">
+      <c r="A437">
+        <f t="shared" si="13"/>
+        <v>123</v>
+      </c>
+      <c r="B437" t="s">
+        <v>92</v>
+      </c>
+      <c r="C437">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="438" spans="1:3">
+      <c r="A438">
+        <f t="shared" si="13"/>
+        <v>124</v>
+      </c>
+      <c r="B438" t="s">
+        <v>93</v>
+      </c>
+      <c r="C438">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="439" spans="1:3">
+      <c r="A439">
+        <f t="shared" si="13"/>
+        <v>125</v>
+      </c>
+      <c r="B439" t="s">
+        <v>93</v>
+      </c>
+      <c r="C439">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="440" spans="1:3">
+      <c r="A440">
+        <f t="shared" si="13"/>
+        <v>126</v>
+      </c>
+      <c r="B440" t="s">
+        <v>94</v>
+      </c>
+      <c r="C440">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="441" spans="1:3">
+      <c r="A441">
+        <f t="shared" si="13"/>
+        <v>127</v>
+      </c>
+      <c r="B441" t="s">
+        <v>92</v>
+      </c>
+      <c r="C441">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="442" spans="1:3">
+      <c r="A442">
+        <f t="shared" si="13"/>
+        <v>128</v>
+      </c>
+      <c r="B442" t="s">
+        <v>92</v>
+      </c>
+      <c r="C442">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="443" spans="1:3">
+      <c r="A443">
+        <f t="shared" si="13"/>
+        <v>129</v>
+      </c>
+      <c r="B443" t="s">
+        <v>94</v>
+      </c>
+      <c r="C443">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="444" spans="1:3">
+      <c r="A444">
+        <f t="shared" si="13"/>
+        <v>130</v>
+      </c>
+      <c r="B444" t="s">
+        <v>91</v>
+      </c>
+      <c r="C444">
         <v>1</v>
       </c>
     </row>

--- a/l_r/2nd.xlsx
+++ b/l_r/2nd.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PycharmProjects\english\english-study\l_r\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{509091F0-3AA9-4020-80BE-99E95171B250}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F16BA2D2-E058-43EE-A231-BF21C791E930}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="1" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-90" yWindow="0" windowWidth="15060" windowHeight="15585" firstSheet="1" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="summary" sheetId="3" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="577" uniqueCount="95">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="586" uniqueCount="99">
   <si>
     <t>問題番号</t>
     <rPh sb="0" eb="2">
@@ -438,6 +438,22 @@
   </si>
   <si>
     <t>D</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>B</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>C</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>D</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>A</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -5517,7 +5533,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3C7A3EDD-6597-4754-A609-A225833ECC81}">
-  <dimension ref="A2:H444"/>
+  <dimension ref="A2:H453"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <sheetData>
     <row r="2" spans="1:4">
@@ -10524,7 +10540,7 @@
     </row>
     <row r="426" spans="1:3">
       <c r="A426">
-        <f t="shared" ref="A426:A448" si="13">A425+1</f>
+        <f t="shared" ref="A426:A452" si="13">A425+1</f>
         <v>112</v>
       </c>
       <c r="B426" t="s">
@@ -10747,6 +10763,105 @@
         <v>91</v>
       </c>
       <c r="C444">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="445" spans="1:3">
+      <c r="A445">
+        <v>104</v>
+      </c>
+      <c r="B445" t="s">
+        <v>95</v>
+      </c>
+      <c r="C445">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="446" spans="1:3">
+      <c r="A446">
+        <v>105</v>
+      </c>
+      <c r="B446" t="s">
+        <v>96</v>
+      </c>
+      <c r="C446">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="447" spans="1:3">
+      <c r="A447">
+        <v>106</v>
+      </c>
+      <c r="B447" t="s">
+        <v>95</v>
+      </c>
+      <c r="C447">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="448" spans="1:3">
+      <c r="A448">
+        <v>107</v>
+      </c>
+      <c r="B448" t="s">
+        <v>97</v>
+      </c>
+      <c r="C448">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="449" spans="1:3">
+      <c r="A449">
+        <v>108</v>
+      </c>
+      <c r="B449" t="s">
+        <v>97</v>
+      </c>
+      <c r="C449">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="450" spans="1:3">
+      <c r="A450">
+        <v>112</v>
+      </c>
+      <c r="B450" t="s">
+        <v>98</v>
+      </c>
+      <c r="C450">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="451" spans="1:3">
+      <c r="A451">
+        <v>114</v>
+      </c>
+      <c r="B451" t="s">
+        <v>97</v>
+      </c>
+      <c r="C451">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="452" spans="1:3">
+      <c r="A452">
+        <v>116</v>
+      </c>
+      <c r="B452" t="s">
+        <v>96</v>
+      </c>
+      <c r="C452">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="453" spans="1:3">
+      <c r="A453">
+        <v>127</v>
+      </c>
+      <c r="B453" t="s">
+        <v>96</v>
+      </c>
+      <c r="C453">
         <v>1</v>
       </c>
     </row>
